--- a/data/FYP_Malaysia_Tourism_Dataset.xlsx
+++ b/data/FYP_Malaysia_Tourism_Dataset.xlsx
@@ -2,10 +2,11 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Attractions Entry" sheetId="1" r:id="R06523b966d864640"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists and Codes" sheetId="2" r:id="Rbd6b7a2c769d4cba"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data Dictionary" sheetId="3" r:id="Rd4865bc6f3804148"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="How to Use" sheetId="4" r:id="Rc6f11728ef234460"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Attractions Entry" sheetId="1" r:id="Rf3d69818a78f4571"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists and Codes" sheetId="2" r:id="Ra73948db219545cb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data Dictionary" sheetId="3" r:id="Re4e98c32be8c4de4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="How to Use" sheetId="4" r:id="R8d2cc4dca20541d8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Coverage Summary" sheetId="5" r:id="R84be7af093b44d6f"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -60,7 +61,7 @@
       <x:name val="Carlito"/>
     </x:font>
   </x:fonts>
-  <x:fills count="10">
+  <x:fills count="14">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -107,8 +108,28 @@
         <x:fgColor rgb="FFF2F2F2"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF17365D"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF2CC"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFD9EAF7"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF2F75B5"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
-  <x:borders count="21">
+  <x:borders count="22">
     <x:border/>
     <x:border>
       <x:left style="medium">
@@ -294,11 +315,25 @@
         <x:color rgb="FFCBD5E1"/>
       </x:bottom>
     </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFD9E2F3"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FFD9E2F3"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFD9E2F3"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFD9E2F3"/>
+      </x:bottom>
+    </x:border>
   </x:borders>
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="177">
+  <x:cellXfs count="201">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -736,6 +771,58 @@
     <x:xf numFmtId="206" fontId="2" fillId="6" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="top"/>
     </x:xf>
+    <x:xf numFmtId="202" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="203" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="2" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="2" fillId="7" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="2" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="2" fillId="7" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="202" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="13" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="13" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -743,8 +830,153 @@
 </x:styleSheet>
 </file>
 
+<file path=xl/drawings/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:lstStyle xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:r>
+              <a:t>Attraction Coverage by State / Territory</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+    </c:title>
+    <c:plotArea>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>Attractions</c:v>
+          </c:tx>
+          <c:cat>
+            <c:strRef>
+              <c:f>'Coverage Summary'!$A$5:$A$20</c:f>
+              <c:strCache>
+                <c:ptCount val="0"/>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'Coverage Summary'!$B$5:$B$20</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="0"/>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+        </c:ser>
+        <c:axId val="48650112"/>
+        <c:axId val="48672768"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="48650112"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+              <a:solidFill>
+                <a:srgbClr val="CCCCCC"/>
+              </a:solidFill>
+              <a:prstDash val="dash"/>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="48672768"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="48672768"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+              <a:solidFill>
+                <a:srgbClr val="CCCCCC"/>
+              </a:solidFill>
+              <a:prstDash val="dash"/>
+            </a:ln>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:crossAx val="48650112"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+  </c:chart>
+  <c:spPr>
+    <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
+      <a:solidFill>
+        <a:srgbClr val="D9D9D9"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </c:spPr>
+</c:chartSpace>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="1" name="Chart"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" x="0" y="0"/>
+        <a:ext xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R2314a90e7e3a4167"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="AttractionsTable" displayName="AttractionsTable" ref="A3:Y53" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="AttractionsTable" displayName="AttractionsTable" ref="A3:Y163" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:tableColumns count="25">
     <x:tableColumn id="1" name="Attraction ID"/>
     <x:tableColumn id="2" name="Attraction Name"/>
@@ -1328,7 +1560,7 @@
         <x:v>Johor Bahru</x:v>
       </x:c>
       <x:c r="E5" s="79" t="str">
-        <x:v>Zoo and Wildlife</x:v>
+        <x:v>Wildlife</x:v>
       </x:c>
       <x:c r="F5" s="100" t="str">
         <x:v>Wildlife; animals; family recreation; children; education; photography; zoo</x:v>
@@ -1470,7 +1702,7 @@
         <x:v>Sungkai</x:v>
       </x:c>
       <x:c r="E7" s="79" t="str">
-        <x:v>Nature</x:v>
+        <x:v>Wellness and Relaxation</x:v>
       </x:c>
       <x:c r="F7" s="100" t="str">
         <x:v>Hot springs; relaxation; wellness; spa; swimming; water park; private jacuzzi; water reflexology; egg boiling; water slides; forest; family recreation</x:v>
@@ -3416,7 +3648,7 @@
         <x:v>Layang-Layangan / Labuan Island</x:v>
       </x:c>
       <x:c r="E33" s="79" t="str">
-        <x:v>Islands and Beaches</x:v>
+        <x:v>Beach and Island</x:v>
       </x:c>
       <x:c r="F33" s="100" t="str">
         <x:v>Beach; island coastline; South China Sea; west coast; sunset; United Nations Beach; UN'08; COBSEA; clean beach; seaside walk; cycling; beach volleyball; picnic; horse riding; live music; restaurants; nature; sand crabs; beach wildlife; family recreation; couples; photography; relaxation; Peace Park; Surrender Point</x:v>
@@ -3494,7 +3726,7 @@
         <x:v>Presint 11 / Putrajaya</x:v>
       </x:c>
       <x:c r="E34" s="79" t="str">
-        <x:v>Nature and Adventure</x:v>
+        <x:v>Nature</x:v>
       </x:c>
       <x:c r="F34" s="100" t="str">
         <x:v>Urban park; landscaped garden; conifer garden; highland landscape; gymnosperms; pine trees; juniper; thuja; cycads; European Garden; Oriental Garden; English Garden; three hills; jogging; brisk walking; cycling; picnic; playground; viewpoints; photography; wedding photography; OOTD; botanical education; research; guided visit; family recreation; wheelchair-friendly; gazebos; lawns; nature; relaxation</x:v>
@@ -3572,7 +3804,7 @@
         <x:v>Presint 13 / Putrajaya</x:v>
       </x:c>
       <x:c r="E35" s="79" t="str">
-        <x:v>Nature and Adventure</x:v>
+        <x:v>Nature</x:v>
       </x:c>
       <x:c r="F35" s="100" t="str">
         <x:v>Constructed freshwater wetland; wetland park; urban ecology; green lung; 24 wetland cells; open lake; natural water filtration; birdwatching; migratory birds; local birds; freshwater fish; aquatic wildlife; flora and fauna; Nature Interpretation Centre; Wetland Studio; Lookout Tower; Flamingo Pond; Swan Lake; walking trails; lakeside promenade; jogging; brisk walking; cycling; picnic; photography; guided visit; environmental education; research; camping; glamping; fishing; kayaking; buggy; adventure activities; family recreation; wheelchair-friendly</x:v>
@@ -3637,533 +3869,8459 @@
       </x:c>
     </x:row>
     <x:row r="36">
-      <x:c r="A36" s="76"/>
-      <x:c r="B36" s="79"/>
-      <x:c r="C36" s="79"/>
-      <x:c r="D36" s="79"/>
-      <x:c r="E36" s="79"/>
-      <x:c r="F36" s="100"/>
-      <x:c r="G36" s="79"/>
-      <x:c r="H36" s="100"/>
-      <x:c r="I36" s="85"/>
+      <x:c r="A36" s="76" t="str">
+        <x:v>A033</x:v>
+      </x:c>
+      <x:c r="B36" s="79" t="str">
+        <x:v>LEGOLAND Malaysia Resort</x:v>
+      </x:c>
+      <x:c r="C36" s="79" t="str">
+        <x:v>Johor</x:v>
+      </x:c>
+      <x:c r="D36" s="100" t="str">
+        <x:v>Iskandar Puteri</x:v>
+      </x:c>
+      <x:c r="E36" s="100" t="str">
+        <x:v>Family Attraction</x:v>
+      </x:c>
+      <x:c r="F36" s="100" t="str">
+        <x:v>theme park; family; children; rides; indoor; outdoor</x:v>
+      </x:c>
+      <x:c r="G36" s="100" t="str">
+        <x:v>Both</x:v>
+      </x:c>
+      <x:c r="H36" s="100" t="str">
+        <x:v>AI-generated candidate attraction in Iskandar Puteri, Johor. The place name, category, description and visitor details require source verification before production use.</x:v>
+      </x:c>
+      <x:c r="I36" s="85" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
       <x:c r="J36" s="88"/>
       <x:c r="K36" s="88"/>
       <x:c r="L36" s="88"/>
-      <x:c r="M36" s="103"/>
-      <x:c r="N36" s="85"/>
-      <x:c r="O36" s="85"/>
-      <x:c r="P36" s="85"/>
-      <x:c r="Q36" s="103"/>
+      <x:c r="M36" s="103" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="N36" s="103" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="O36" s="103" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="P36" s="103" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="Q36" s="103" t="str">
+        <x:v>Accessibility information has not been verified. Confirm terrain, steps, seating, toilets and mobility access with an official source before recommending it as elderly-friendly.</x:v>
+      </x:c>
       <x:c r="R36" s="91"/>
       <x:c r="S36" s="91"/>
       <x:c r="T36" s="103"/>
-      <x:c r="U36" s="100"/>
-      <x:c r="V36" s="82"/>
-      <x:c r="W36" s="79"/>
-      <x:c r="X36" s="97" t="str">
+      <x:c r="U36" s="100" t="str">
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=LEGOLAND%20Malaysia%20Resort%2C%20Johor%2C%20Malaysia</x:v>
+      </x:c>
+      <x:c r="V36" s="180" t="n">
+        <x:v>46240</x:v>
+      </x:c>
+      <x:c r="W36" s="100" t="str">
+        <x:v>Unverified</x:v>
+      </x:c>
+      <x:c r="X36" s="181" t="n">
         <x:f>IF(B36="","",COUNTA(B36:W36)/22)</x:f>
-      </x:c>
-      <x:c r="Y36" s="106"/>
+        <x:v>0.7272727272727273</x:v>
+      </x:c>
+      <x:c r="Y36" s="106" t="str">
+        <x:v>Generated by ChatGPT as a candidate on 2026-08-06. The Google Maps link is for discovery only and is not a verified factual source. Replace it with an official or authoritative source during review.</x:v>
+      </x:c>
     </x:row>
     <x:row r="37">
-      <x:c r="A37" s="76"/>
-      <x:c r="B37" s="79"/>
-      <x:c r="C37" s="79"/>
-      <x:c r="D37" s="79"/>
-      <x:c r="E37" s="79"/>
-      <x:c r="F37" s="100"/>
-      <x:c r="G37" s="79"/>
-      <x:c r="H37" s="100"/>
-      <x:c r="I37" s="85"/>
+      <x:c r="A37" s="76" t="str">
+        <x:v>A034</x:v>
+      </x:c>
+      <x:c r="B37" s="79" t="str">
+        <x:v>Adventure Waterpark Desaru Coast</x:v>
+      </x:c>
+      <x:c r="C37" s="79" t="str">
+        <x:v>Johor</x:v>
+      </x:c>
+      <x:c r="D37" s="100" t="str">
+        <x:v>Bandar Penawar</x:v>
+      </x:c>
+      <x:c r="E37" s="100" t="str">
+        <x:v>Theme Park</x:v>
+      </x:c>
+      <x:c r="F37" s="100" t="str">
+        <x:v>water park; family; children; adventure; recreation</x:v>
+      </x:c>
+      <x:c r="G37" s="100" t="str">
+        <x:v>Outdoor</x:v>
+      </x:c>
+      <x:c r="H37" s="100" t="str">
+        <x:v>AI-generated candidate attraction in Bandar Penawar, Johor. The place name, category, description and visitor details require source verification before production use.</x:v>
+      </x:c>
+      <x:c r="I37" s="85" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
       <x:c r="J37" s="88"/>
       <x:c r="K37" s="88"/>
       <x:c r="L37" s="88"/>
-      <x:c r="M37" s="103"/>
-      <x:c r="N37" s="85"/>
-      <x:c r="O37" s="85"/>
-      <x:c r="P37" s="85"/>
-      <x:c r="Q37" s="103"/>
+      <x:c r="M37" s="103" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="N37" s="103" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="O37" s="103" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="P37" s="103" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="Q37" s="103" t="str">
+        <x:v>Accessibility information has not been verified. Confirm terrain, steps, seating, toilets and mobility access with an official source before recommending it as elderly-friendly.</x:v>
+      </x:c>
       <x:c r="R37" s="91"/>
       <x:c r="S37" s="91"/>
       <x:c r="T37" s="103"/>
-      <x:c r="U37" s="100"/>
-      <x:c r="V37" s="82"/>
-      <x:c r="W37" s="79"/>
-      <x:c r="X37" s="97" t="str">
+      <x:c r="U37" s="100" t="str">
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Adventure%20Waterpark%20Desaru%20Coast%2C%20Johor%2C%20Malaysia</x:v>
+      </x:c>
+      <x:c r="V37" s="180" t="n">
+        <x:v>46240</x:v>
+      </x:c>
+      <x:c r="W37" s="100" t="str">
+        <x:v>Unverified</x:v>
+      </x:c>
+      <x:c r="X37" s="181" t="n">
         <x:f>IF(B37="","",COUNTA(B37:W37)/22)</x:f>
-      </x:c>
-      <x:c r="Y37" s="106"/>
+        <x:v>0.7272727272727273</x:v>
+      </x:c>
+      <x:c r="Y37" s="106" t="str">
+        <x:v>Generated by ChatGPT as a candidate on 2026-08-06. The Google Maps link is for discovery only and is not a verified factual source. Replace it with an official or authoritative source during review.</x:v>
+      </x:c>
     </x:row>
     <x:row r="38">
-      <x:c r="A38" s="76"/>
-      <x:c r="B38" s="79"/>
-      <x:c r="C38" s="79"/>
-      <x:c r="D38" s="79"/>
-      <x:c r="E38" s="79"/>
-      <x:c r="F38" s="100"/>
-      <x:c r="G38" s="79"/>
-      <x:c r="H38" s="100"/>
-      <x:c r="I38" s="85"/>
+      <x:c r="A38" s="76" t="str">
+        <x:v>A035</x:v>
+      </x:c>
+      <x:c r="B38" s="79" t="str">
+        <x:v>Desaru Beach</x:v>
+      </x:c>
+      <x:c r="C38" s="79" t="str">
+        <x:v>Johor</x:v>
+      </x:c>
+      <x:c r="D38" s="100" t="str">
+        <x:v>Kota Tinggi</x:v>
+      </x:c>
+      <x:c r="E38" s="100" t="str">
+        <x:v>Beach and Island</x:v>
+      </x:c>
+      <x:c r="F38" s="100" t="str">
+        <x:v>beach; relaxation; scenery; family; seaside</x:v>
+      </x:c>
+      <x:c r="G38" s="100" t="str">
+        <x:v>Outdoor</x:v>
+      </x:c>
+      <x:c r="H38" s="100" t="str">
+        <x:v>AI-generated candidate attraction in Kota Tinggi, Johor. The place name, category, description and visitor details require source verification before production use.</x:v>
+      </x:c>
+      <x:c r="I38" s="85" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
       <x:c r="J38" s="88"/>
       <x:c r="K38" s="88"/>
       <x:c r="L38" s="88"/>
-      <x:c r="M38" s="103"/>
-      <x:c r="N38" s="85"/>
-      <x:c r="O38" s="85"/>
-      <x:c r="P38" s="85"/>
-      <x:c r="Q38" s="103"/>
+      <x:c r="M38" s="103" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="N38" s="103" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="O38" s="103" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="P38" s="103" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="Q38" s="103" t="str">
+        <x:v>Accessibility information has not been verified. Confirm terrain, steps, seating, toilets and mobility access with an official source before recommending it as elderly-friendly.</x:v>
+      </x:c>
       <x:c r="R38" s="91"/>
       <x:c r="S38" s="91"/>
       <x:c r="T38" s="103"/>
-      <x:c r="U38" s="100"/>
-      <x:c r="V38" s="82"/>
-      <x:c r="W38" s="79"/>
-      <x:c r="X38" s="97" t="str">
+      <x:c r="U38" s="100" t="str">
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Desaru%20Beach%2C%20Johor%2C%20Malaysia</x:v>
+      </x:c>
+      <x:c r="V38" s="180" t="n">
+        <x:v>46240</x:v>
+      </x:c>
+      <x:c r="W38" s="100" t="str">
+        <x:v>Unverified</x:v>
+      </x:c>
+      <x:c r="X38" s="181" t="n">
         <x:f>IF(B38="","",COUNTA(B38:W38)/22)</x:f>
-      </x:c>
-      <x:c r="Y38" s="106"/>
+        <x:v>0.7272727272727273</x:v>
+      </x:c>
+      <x:c r="Y38" s="106" t="str">
+        <x:v>Generated by ChatGPT as a candidate on 2026-08-06. The Google Maps link is for discovery only and is not a verified factual source. Replace it with an official or authoritative source during review.</x:v>
+      </x:c>
     </x:row>
     <x:row r="39">
-      <x:c r="A39" s="76"/>
-      <x:c r="B39" s="79"/>
-      <x:c r="C39" s="79"/>
-      <x:c r="D39" s="79"/>
-      <x:c r="E39" s="79"/>
-      <x:c r="F39" s="100"/>
-      <x:c r="G39" s="79"/>
-      <x:c r="H39" s="100"/>
-      <x:c r="I39" s="85"/>
+      <x:c r="A39" s="76" t="str">
+        <x:v>A036</x:v>
+      </x:c>
+      <x:c r="B39" s="79" t="str">
+        <x:v>Tanjung Piai National Park</x:v>
+      </x:c>
+      <x:c r="C39" s="79" t="str">
+        <x:v>Johor</x:v>
+      </x:c>
+      <x:c r="D39" s="100" t="str">
+        <x:v>Pontian</x:v>
+      </x:c>
+      <x:c r="E39" s="100" t="str">
+        <x:v>Nature</x:v>
+      </x:c>
+      <x:c r="F39" s="100" t="str">
+        <x:v>nature; mangrove; boardwalk; birdwatching; scenery; relaxation</x:v>
+      </x:c>
+      <x:c r="G39" s="100" t="str">
+        <x:v>Outdoor</x:v>
+      </x:c>
+      <x:c r="H39" s="100" t="str">
+        <x:v>AI-generated candidate attraction in Pontian, Johor. The place name, category, description and visitor details require source verification before production use.</x:v>
+      </x:c>
+      <x:c r="I39" s="85" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
       <x:c r="J39" s="88"/>
       <x:c r="K39" s="88"/>
       <x:c r="L39" s="88"/>
-      <x:c r="M39" s="103"/>
-      <x:c r="N39" s="85"/>
-      <x:c r="O39" s="85"/>
-      <x:c r="P39" s="85"/>
-      <x:c r="Q39" s="103"/>
+      <x:c r="M39" s="103" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="N39" s="103" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="O39" s="103" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="P39" s="103" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="Q39" s="103" t="str">
+        <x:v>Accessibility information has not been verified. Confirm terrain, steps, seating, toilets and mobility access with an official source before recommending it as elderly-friendly.</x:v>
+      </x:c>
       <x:c r="R39" s="91"/>
       <x:c r="S39" s="91"/>
       <x:c r="T39" s="103"/>
-      <x:c r="U39" s="100"/>
-      <x:c r="V39" s="82"/>
-      <x:c r="W39" s="79"/>
-      <x:c r="X39" s="97" t="str">
+      <x:c r="U39" s="100" t="str">
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Tanjung%20Piai%20National%20Park%2C%20Johor%2C%20Malaysia</x:v>
+      </x:c>
+      <x:c r="V39" s="180" t="n">
+        <x:v>46240</x:v>
+      </x:c>
+      <x:c r="W39" s="100" t="str">
+        <x:v>Unverified</x:v>
+      </x:c>
+      <x:c r="X39" s="181" t="n">
         <x:f>IF(B39="","",COUNTA(B39:W39)/22)</x:f>
-      </x:c>
-      <x:c r="Y39" s="106"/>
+        <x:v>0.7272727272727273</x:v>
+      </x:c>
+      <x:c r="Y39" s="106" t="str">
+        <x:v>Generated by ChatGPT as a candidate on 2026-08-06. The Google Maps link is for discovery only and is not a verified factual source. Replace it with an official or authoritative source during review.</x:v>
+      </x:c>
     </x:row>
     <x:row r="40">
-      <x:c r="A40" s="76"/>
-      <x:c r="B40" s="79"/>
-      <x:c r="C40" s="79"/>
-      <x:c r="D40" s="79"/>
-      <x:c r="E40" s="79"/>
-      <x:c r="F40" s="100"/>
-      <x:c r="G40" s="79"/>
-      <x:c r="H40" s="100"/>
-      <x:c r="I40" s="85"/>
+      <x:c r="A40" s="76" t="str">
+        <x:v>A037</x:v>
+      </x:c>
+      <x:c r="B40" s="79" t="str">
+        <x:v>Gunung Pulai Recreational Forest</x:v>
+      </x:c>
+      <x:c r="C40" s="79" t="str">
+        <x:v>Johor</x:v>
+      </x:c>
+      <x:c r="D40" s="100" t="str">
+        <x:v>Kulai</x:v>
+      </x:c>
+      <x:c r="E40" s="100" t="str">
+        <x:v>Nature</x:v>
+      </x:c>
+      <x:c r="F40" s="100" t="str">
+        <x:v>nature; forest; hiking; waterfall; adventure</x:v>
+      </x:c>
+      <x:c r="G40" s="100" t="str">
+        <x:v>Outdoor</x:v>
+      </x:c>
+      <x:c r="H40" s="100" t="str">
+        <x:v>AI-generated candidate attraction in Kulai, Johor. The place name, category, description and visitor details require source verification before production use.</x:v>
+      </x:c>
+      <x:c r="I40" s="85" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
       <x:c r="J40" s="88"/>
       <x:c r="K40" s="88"/>
       <x:c r="L40" s="88"/>
-      <x:c r="M40" s="103"/>
-      <x:c r="N40" s="85"/>
-      <x:c r="O40" s="85"/>
-      <x:c r="P40" s="85"/>
-      <x:c r="Q40" s="103"/>
+      <x:c r="M40" s="103" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="N40" s="103" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="O40" s="103" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="P40" s="103" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="Q40" s="103" t="str">
+        <x:v>Accessibility information has not been verified. Confirm terrain, steps, seating, toilets and mobility access with an official source before recommending it as elderly-friendly.</x:v>
+      </x:c>
       <x:c r="R40" s="91"/>
       <x:c r="S40" s="91"/>
       <x:c r="T40" s="103"/>
-      <x:c r="U40" s="100"/>
-      <x:c r="V40" s="82"/>
-      <x:c r="W40" s="79"/>
-      <x:c r="X40" s="97" t="str">
+      <x:c r="U40" s="100" t="str">
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Gunung%20Pulai%20Recreational%20Forest%2C%20Johor%2C%20Malaysia</x:v>
+      </x:c>
+      <x:c r="V40" s="180" t="n">
+        <x:v>46240</x:v>
+      </x:c>
+      <x:c r="W40" s="100" t="str">
+        <x:v>Unverified</x:v>
+      </x:c>
+      <x:c r="X40" s="181" t="n">
         <x:f>IF(B40="","",COUNTA(B40:W40)/22)</x:f>
-      </x:c>
-      <x:c r="Y40" s="106"/>
+        <x:v>0.7272727272727273</x:v>
+      </x:c>
+      <x:c r="Y40" s="106" t="str">
+        <x:v>Generated by ChatGPT as a candidate on 2026-08-06. The Google Maps link is for discovery only and is not a verified factual source. Replace it with an official or authoritative source during review.</x:v>
+      </x:c>
     </x:row>
     <x:row r="41">
-      <x:c r="A41" s="76"/>
-      <x:c r="B41" s="79"/>
-      <x:c r="C41" s="79"/>
-      <x:c r="D41" s="79"/>
-      <x:c r="E41" s="79"/>
-      <x:c r="F41" s="100"/>
-      <x:c r="G41" s="79"/>
-      <x:c r="H41" s="100"/>
-      <x:c r="I41" s="85"/>
+      <x:c r="A41" s="76" t="str">
+        <x:v>A038</x:v>
+      </x:c>
+      <x:c r="B41" s="79" t="str">
+        <x:v>Kota Tinggi Firefly Park</x:v>
+      </x:c>
+      <x:c r="C41" s="79" t="str">
+        <x:v>Johor</x:v>
+      </x:c>
+      <x:c r="D41" s="100" t="str">
+        <x:v>Kota Tinggi</x:v>
+      </x:c>
+      <x:c r="E41" s="100" t="str">
+        <x:v>Wildlife</x:v>
+      </x:c>
+      <x:c r="F41" s="100" t="str">
+        <x:v>wildlife; fireflies; river cruise; nature; family</x:v>
+      </x:c>
+      <x:c r="G41" s="100" t="str">
+        <x:v>Outdoor</x:v>
+      </x:c>
+      <x:c r="H41" s="100" t="str">
+        <x:v>AI-generated candidate attraction in Kota Tinggi, Johor. The place name, category, description and visitor details require source verification before production use.</x:v>
+      </x:c>
+      <x:c r="I41" s="85" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
       <x:c r="J41" s="88"/>
       <x:c r="K41" s="88"/>
       <x:c r="L41" s="88"/>
-      <x:c r="M41" s="103"/>
-      <x:c r="N41" s="85"/>
-      <x:c r="O41" s="85"/>
-      <x:c r="P41" s="85"/>
-      <x:c r="Q41" s="103"/>
+      <x:c r="M41" s="103" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="N41" s="103" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="O41" s="103" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="P41" s="103" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="Q41" s="103" t="str">
+        <x:v>Accessibility information has not been verified. Confirm terrain, steps, seating, toilets and mobility access with an official source before recommending it as elderly-friendly.</x:v>
+      </x:c>
       <x:c r="R41" s="91"/>
       <x:c r="S41" s="91"/>
       <x:c r="T41" s="103"/>
-      <x:c r="U41" s="100"/>
-      <x:c r="V41" s="82"/>
-      <x:c r="W41" s="79"/>
-      <x:c r="X41" s="97" t="str">
+      <x:c r="U41" s="100" t="str">
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Kota%20Tinggi%20Firefly%20Park%2C%20Johor%2C%20Malaysia</x:v>
+      </x:c>
+      <x:c r="V41" s="180" t="n">
+        <x:v>46240</x:v>
+      </x:c>
+      <x:c r="W41" s="100" t="str">
+        <x:v>Unverified</x:v>
+      </x:c>
+      <x:c r="X41" s="181" t="n">
         <x:f>IF(B41="","",COUNTA(B41:W41)/22)</x:f>
-      </x:c>
-      <x:c r="Y41" s="106"/>
+        <x:v>0.7272727272727273</x:v>
+      </x:c>
+      <x:c r="Y41" s="106" t="str">
+        <x:v>Generated by ChatGPT as a candidate on 2026-08-06. The Google Maps link is for discovery only and is not a verified factual source. Replace it with an official or authoritative source during review.</x:v>
+      </x:c>
     </x:row>
     <x:row r="42">
-      <x:c r="A42" s="76"/>
-      <x:c r="B42" s="79"/>
-      <x:c r="C42" s="79"/>
-      <x:c r="D42" s="79"/>
-      <x:c r="E42" s="79"/>
-      <x:c r="F42" s="100"/>
-      <x:c r="G42" s="79"/>
-      <x:c r="H42" s="100"/>
-      <x:c r="I42" s="85"/>
+      <x:c r="A42" s="76" t="str">
+        <x:v>A039</x:v>
+      </x:c>
+      <x:c r="B42" s="79" t="str">
+        <x:v>Johor Bahru Old Chinese Temple</x:v>
+      </x:c>
+      <x:c r="C42" s="79" t="str">
+        <x:v>Johor</x:v>
+      </x:c>
+      <x:c r="D42" s="100" t="str">
+        <x:v>Johor Bahru</x:v>
+      </x:c>
+      <x:c r="E42" s="100" t="str">
+        <x:v>Culture</x:v>
+      </x:c>
+      <x:c r="F42" s="100" t="str">
+        <x:v>culture; temple; heritage; history; architecture</x:v>
+      </x:c>
+      <x:c r="G42" s="100" t="str">
+        <x:v>Both</x:v>
+      </x:c>
+      <x:c r="H42" s="100" t="str">
+        <x:v>AI-generated candidate attraction in Johor Bahru, Johor. The place name, category, description and visitor details require source verification before production use.</x:v>
+      </x:c>
+      <x:c r="I42" s="85" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
       <x:c r="J42" s="88"/>
       <x:c r="K42" s="88"/>
       <x:c r="L42" s="88"/>
-      <x:c r="M42" s="103"/>
-      <x:c r="N42" s="85"/>
-      <x:c r="O42" s="85"/>
-      <x:c r="P42" s="85"/>
-      <x:c r="Q42" s="103"/>
+      <x:c r="M42" s="103" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="N42" s="103" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="O42" s="103" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="P42" s="103" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="Q42" s="103" t="str">
+        <x:v>Accessibility information has not been verified. Confirm terrain, steps, seating, toilets and mobility access with an official source before recommending it as elderly-friendly.</x:v>
+      </x:c>
       <x:c r="R42" s="91"/>
       <x:c r="S42" s="91"/>
       <x:c r="T42" s="103"/>
-      <x:c r="U42" s="100"/>
-      <x:c r="V42" s="82"/>
-      <x:c r="W42" s="79"/>
-      <x:c r="X42" s="97" t="str">
+      <x:c r="U42" s="100" t="str">
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Johor%20Bahru%20Old%20Chinese%20Temple%2C%20Johor%2C%20Malaysia</x:v>
+      </x:c>
+      <x:c r="V42" s="180" t="n">
+        <x:v>46240</x:v>
+      </x:c>
+      <x:c r="W42" s="100" t="str">
+        <x:v>Unverified</x:v>
+      </x:c>
+      <x:c r="X42" s="181" t="n">
         <x:f>IF(B42="","",COUNTA(B42:W42)/22)</x:f>
-      </x:c>
-      <x:c r="Y42" s="106"/>
+        <x:v>0.7272727272727273</x:v>
+      </x:c>
+      <x:c r="Y42" s="106" t="str">
+        <x:v>Generated by ChatGPT as a candidate on 2026-08-06. The Google Maps link is for discovery only and is not a verified factual source. Replace it with an official or authoritative source during review.</x:v>
+      </x:c>
     </x:row>
     <x:row r="43">
-      <x:c r="A43" s="76"/>
-      <x:c r="B43" s="79"/>
-      <x:c r="C43" s="79"/>
-      <x:c r="D43" s="79"/>
-      <x:c r="E43" s="79"/>
-      <x:c r="F43" s="100"/>
-      <x:c r="G43" s="79"/>
-      <x:c r="H43" s="100"/>
-      <x:c r="I43" s="85"/>
+      <x:c r="A43" s="76" t="str">
+        <x:v>A040</x:v>
+      </x:c>
+      <x:c r="B43" s="79" t="str">
+        <x:v>Langkawi Sky Bridge</x:v>
+      </x:c>
+      <x:c r="C43" s="79" t="str">
+        <x:v>Kedah</x:v>
+      </x:c>
+      <x:c r="D43" s="100" t="str">
+        <x:v>Langkawi</x:v>
+      </x:c>
+      <x:c r="E43" s="100" t="str">
+        <x:v>Adventure</x:v>
+      </x:c>
+      <x:c r="F43" s="100" t="str">
+        <x:v>scenery; cable car; bridge; nature; photography; adventure</x:v>
+      </x:c>
+      <x:c r="G43" s="100" t="str">
+        <x:v>Outdoor</x:v>
+      </x:c>
+      <x:c r="H43" s="100" t="str">
+        <x:v>AI-generated candidate attraction in Langkawi, Kedah. The place name, category, description and visitor details require source verification before production use.</x:v>
+      </x:c>
+      <x:c r="I43" s="85" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
       <x:c r="J43" s="88"/>
       <x:c r="K43" s="88"/>
       <x:c r="L43" s="88"/>
-      <x:c r="M43" s="103"/>
-      <x:c r="N43" s="85"/>
-      <x:c r="O43" s="85"/>
-      <x:c r="P43" s="85"/>
-      <x:c r="Q43" s="103"/>
+      <x:c r="M43" s="103" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="N43" s="103" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="O43" s="103" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="P43" s="103" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="Q43" s="103" t="str">
+        <x:v>Accessibility information has not been verified. Confirm terrain, steps, seating, toilets and mobility access with an official source before recommending it as elderly-friendly.</x:v>
+      </x:c>
       <x:c r="R43" s="91"/>
       <x:c r="S43" s="91"/>
       <x:c r="T43" s="103"/>
-      <x:c r="U43" s="100"/>
-      <x:c r="V43" s="82"/>
-      <x:c r="W43" s="79"/>
-      <x:c r="X43" s="97" t="str">
+      <x:c r="U43" s="100" t="str">
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Langkawi%20Sky%20Bridge%2C%20Kedah%2C%20Malaysia</x:v>
+      </x:c>
+      <x:c r="V43" s="180" t="n">
+        <x:v>46240</x:v>
+      </x:c>
+      <x:c r="W43" s="100" t="str">
+        <x:v>Unverified</x:v>
+      </x:c>
+      <x:c r="X43" s="181" t="n">
         <x:f>IF(B43="","",COUNTA(B43:W43)/22)</x:f>
-      </x:c>
-      <x:c r="Y43" s="106"/>
+        <x:v>0.7272727272727273</x:v>
+      </x:c>
+      <x:c r="Y43" s="106" t="str">
+        <x:v>Generated by ChatGPT as a candidate on 2026-08-06. The Google Maps link is for discovery only and is not a verified factual source. Replace it with an official or authoritative source during review.</x:v>
+      </x:c>
     </x:row>
     <x:row r="44">
-      <x:c r="A44" s="76"/>
-      <x:c r="B44" s="79"/>
-      <x:c r="C44" s="79"/>
-      <x:c r="D44" s="79"/>
-      <x:c r="E44" s="79"/>
-      <x:c r="F44" s="100"/>
-      <x:c r="G44" s="79"/>
-      <x:c r="H44" s="100"/>
-      <x:c r="I44" s="85"/>
+      <x:c r="A44" s="76" t="str">
+        <x:v>A041</x:v>
+      </x:c>
+      <x:c r="B44" s="79" t="str">
+        <x:v>Kilim Karst Geoforest Park</x:v>
+      </x:c>
+      <x:c r="C44" s="79" t="str">
+        <x:v>Kedah</x:v>
+      </x:c>
+      <x:c r="D44" s="100" t="str">
+        <x:v>Langkawi</x:v>
+      </x:c>
+      <x:c r="E44" s="100" t="str">
+        <x:v>Nature</x:v>
+      </x:c>
+      <x:c r="F44" s="100" t="str">
+        <x:v>mangrove; boat tour; geopark; wildlife; scenery; nature</x:v>
+      </x:c>
+      <x:c r="G44" s="100" t="str">
+        <x:v>Outdoor</x:v>
+      </x:c>
+      <x:c r="H44" s="100" t="str">
+        <x:v>AI-generated candidate attraction in Langkawi, Kedah. The place name, category, description and visitor details require source verification before production use.</x:v>
+      </x:c>
+      <x:c r="I44" s="85" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
       <x:c r="J44" s="88"/>
       <x:c r="K44" s="88"/>
       <x:c r="L44" s="88"/>
-      <x:c r="M44" s="103"/>
-      <x:c r="N44" s="85"/>
-      <x:c r="O44" s="85"/>
-      <x:c r="P44" s="85"/>
-      <x:c r="Q44" s="103"/>
+      <x:c r="M44" s="103" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="N44" s="103" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="O44" s="103" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="P44" s="103" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="Q44" s="103" t="str">
+        <x:v>Accessibility information has not been verified. Confirm terrain, steps, seating, toilets and mobility access with an official source before recommending it as elderly-friendly.</x:v>
+      </x:c>
       <x:c r="R44" s="91"/>
       <x:c r="S44" s="91"/>
       <x:c r="T44" s="103"/>
-      <x:c r="U44" s="100"/>
-      <x:c r="V44" s="82"/>
-      <x:c r="W44" s="79"/>
-      <x:c r="X44" s="97" t="str">
+      <x:c r="U44" s="100" t="str">
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Kilim%20Karst%20Geoforest%20Park%2C%20Kedah%2C%20Malaysia</x:v>
+      </x:c>
+      <x:c r="V44" s="180" t="n">
+        <x:v>46240</x:v>
+      </x:c>
+      <x:c r="W44" s="100" t="str">
+        <x:v>Unverified</x:v>
+      </x:c>
+      <x:c r="X44" s="181" t="n">
         <x:f>IF(B44="","",COUNTA(B44:W44)/22)</x:f>
-      </x:c>
-      <x:c r="Y44" s="106"/>
+        <x:v>0.7272727272727273</x:v>
+      </x:c>
+      <x:c r="Y44" s="106" t="str">
+        <x:v>Generated by ChatGPT as a candidate on 2026-08-06. The Google Maps link is for discovery only and is not a verified factual source. Replace it with an official or authoritative source during review.</x:v>
+      </x:c>
     </x:row>
     <x:row r="45">
-      <x:c r="A45" s="76"/>
-      <x:c r="B45" s="79"/>
-      <x:c r="C45" s="79"/>
-      <x:c r="D45" s="79"/>
-      <x:c r="E45" s="79"/>
-      <x:c r="F45" s="100"/>
-      <x:c r="G45" s="79"/>
-      <x:c r="H45" s="100"/>
-      <x:c r="I45" s="85"/>
+      <x:c r="A45" s="76" t="str">
+        <x:v>A042</x:v>
+      </x:c>
+      <x:c r="B45" s="79" t="str">
+        <x:v>Pantai Cenang</x:v>
+      </x:c>
+      <x:c r="C45" s="79" t="str">
+        <x:v>Kedah</x:v>
+      </x:c>
+      <x:c r="D45" s="100" t="str">
+        <x:v>Langkawi</x:v>
+      </x:c>
+      <x:c r="E45" s="100" t="str">
+        <x:v>Beach and Island</x:v>
+      </x:c>
+      <x:c r="F45" s="100" t="str">
+        <x:v>beach; relaxation; water sports; shopping; food</x:v>
+      </x:c>
+      <x:c r="G45" s="100" t="str">
+        <x:v>Outdoor</x:v>
+      </x:c>
+      <x:c r="H45" s="100" t="str">
+        <x:v>AI-generated candidate attraction in Langkawi, Kedah. The place name, category, description and visitor details require source verification before production use.</x:v>
+      </x:c>
+      <x:c r="I45" s="85" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
       <x:c r="J45" s="88"/>
       <x:c r="K45" s="88"/>
       <x:c r="L45" s="88"/>
-      <x:c r="M45" s="103"/>
-      <x:c r="N45" s="85"/>
-      <x:c r="O45" s="85"/>
-      <x:c r="P45" s="85"/>
-      <x:c r="Q45" s="103"/>
+      <x:c r="M45" s="103" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="N45" s="103" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="O45" s="103" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="P45" s="103" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="Q45" s="103" t="str">
+        <x:v>Accessibility information has not been verified. Confirm terrain, steps, seating, toilets and mobility access with an official source before recommending it as elderly-friendly.</x:v>
+      </x:c>
       <x:c r="R45" s="91"/>
       <x:c r="S45" s="91"/>
       <x:c r="T45" s="103"/>
-      <x:c r="U45" s="100"/>
-      <x:c r="V45" s="82"/>
-      <x:c r="W45" s="79"/>
-      <x:c r="X45" s="97" t="str">
+      <x:c r="U45" s="100" t="str">
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Pantai%20Cenang%2C%20Kedah%2C%20Malaysia</x:v>
+      </x:c>
+      <x:c r="V45" s="180" t="n">
+        <x:v>46240</x:v>
+      </x:c>
+      <x:c r="W45" s="100" t="str">
+        <x:v>Unverified</x:v>
+      </x:c>
+      <x:c r="X45" s="181" t="n">
         <x:f>IF(B45="","",COUNTA(B45:W45)/22)</x:f>
-      </x:c>
-      <x:c r="Y45" s="106"/>
+        <x:v>0.7272727272727273</x:v>
+      </x:c>
+      <x:c r="Y45" s="106" t="str">
+        <x:v>Generated by ChatGPT as a candidate on 2026-08-06. The Google Maps link is for discovery only and is not a verified factual source. Replace it with an official or authoritative source during review.</x:v>
+      </x:c>
     </x:row>
     <x:row r="46">
-      <x:c r="A46" s="76"/>
-      <x:c r="B46" s="79"/>
-      <x:c r="C46" s="79"/>
-      <x:c r="D46" s="79"/>
-      <x:c r="E46" s="79"/>
-      <x:c r="F46" s="100"/>
-      <x:c r="G46" s="79"/>
-      <x:c r="H46" s="100"/>
-      <x:c r="I46" s="85"/>
+      <x:c r="A46" s="76" t="str">
+        <x:v>A043</x:v>
+      </x:c>
+      <x:c r="B46" s="79" t="str">
+        <x:v>Langkawi Wildlife Park</x:v>
+      </x:c>
+      <x:c r="C46" s="79" t="str">
+        <x:v>Kedah</x:v>
+      </x:c>
+      <x:c r="D46" s="100" t="str">
+        <x:v>Langkawi</x:v>
+      </x:c>
+      <x:c r="E46" s="100" t="str">
+        <x:v>Wildlife</x:v>
+      </x:c>
+      <x:c r="F46" s="100" t="str">
+        <x:v>wildlife; animals; family; children; education</x:v>
+      </x:c>
+      <x:c r="G46" s="100" t="str">
+        <x:v>Both</x:v>
+      </x:c>
+      <x:c r="H46" s="100" t="str">
+        <x:v>AI-generated candidate attraction in Langkawi, Kedah. The place name, category, description and visitor details require source verification before production use.</x:v>
+      </x:c>
+      <x:c r="I46" s="85" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
       <x:c r="J46" s="88"/>
       <x:c r="K46" s="88"/>
       <x:c r="L46" s="88"/>
-      <x:c r="M46" s="103"/>
-      <x:c r="N46" s="85"/>
-      <x:c r="O46" s="85"/>
-      <x:c r="P46" s="85"/>
-      <x:c r="Q46" s="103"/>
+      <x:c r="M46" s="103" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="N46" s="103" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="O46" s="103" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="P46" s="103" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="Q46" s="103" t="str">
+        <x:v>Accessibility information has not been verified. Confirm terrain, steps, seating, toilets and mobility access with an official source before recommending it as elderly-friendly.</x:v>
+      </x:c>
       <x:c r="R46" s="91"/>
       <x:c r="S46" s="91"/>
       <x:c r="T46" s="103"/>
-      <x:c r="U46" s="100"/>
-      <x:c r="V46" s="82"/>
-      <x:c r="W46" s="79"/>
-      <x:c r="X46" s="97" t="str">
+      <x:c r="U46" s="100" t="str">
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Langkawi%20Wildlife%20Park%2C%20Kedah%2C%20Malaysia</x:v>
+      </x:c>
+      <x:c r="V46" s="180" t="n">
+        <x:v>46240</x:v>
+      </x:c>
+      <x:c r="W46" s="100" t="str">
+        <x:v>Unverified</x:v>
+      </x:c>
+      <x:c r="X46" s="181" t="n">
         <x:f>IF(B46="","",COUNTA(B46:W46)/22)</x:f>
-      </x:c>
-      <x:c r="Y46" s="106"/>
+        <x:v>0.7272727272727273</x:v>
+      </x:c>
+      <x:c r="Y46" s="106" t="str">
+        <x:v>Generated by ChatGPT as a candidate on 2026-08-06. The Google Maps link is for discovery only and is not a verified factual source. Replace it with an official or authoritative source during review.</x:v>
+      </x:c>
     </x:row>
     <x:row r="47">
-      <x:c r="A47" s="76"/>
-      <x:c r="B47" s="79"/>
-      <x:c r="C47" s="79"/>
-      <x:c r="D47" s="79"/>
-      <x:c r="E47" s="79"/>
-      <x:c r="F47" s="100"/>
-      <x:c r="G47" s="79"/>
-      <x:c r="H47" s="100"/>
-      <x:c r="I47" s="85"/>
+      <x:c r="A47" s="76" t="str">
+        <x:v>A044</x:v>
+      </x:c>
+      <x:c r="B47" s="79" t="str">
+        <x:v>Underwater World Langkawi</x:v>
+      </x:c>
+      <x:c r="C47" s="79" t="str">
+        <x:v>Kedah</x:v>
+      </x:c>
+      <x:c r="D47" s="100" t="str">
+        <x:v>Langkawi</x:v>
+      </x:c>
+      <x:c r="E47" s="100" t="str">
+        <x:v>Family Attraction</x:v>
+      </x:c>
+      <x:c r="F47" s="100" t="str">
+        <x:v>aquarium; marine life; family; children; indoor</x:v>
+      </x:c>
+      <x:c r="G47" s="100" t="str">
+        <x:v>Indoor</x:v>
+      </x:c>
+      <x:c r="H47" s="100" t="str">
+        <x:v>AI-generated candidate attraction in Langkawi, Kedah. The place name, category, description and visitor details require source verification before production use.</x:v>
+      </x:c>
+      <x:c r="I47" s="85" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
       <x:c r="J47" s="88"/>
       <x:c r="K47" s="88"/>
       <x:c r="L47" s="88"/>
-      <x:c r="M47" s="103"/>
-      <x:c r="N47" s="85"/>
-      <x:c r="O47" s="85"/>
-      <x:c r="P47" s="85"/>
-      <x:c r="Q47" s="103"/>
+      <x:c r="M47" s="103" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="N47" s="103" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="O47" s="103" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="P47" s="103" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="Q47" s="103" t="str">
+        <x:v>Accessibility information has not been verified. Confirm terrain, steps, seating, toilets and mobility access with an official source before recommending it as elderly-friendly.</x:v>
+      </x:c>
       <x:c r="R47" s="91"/>
       <x:c r="S47" s="91"/>
       <x:c r="T47" s="103"/>
-      <x:c r="U47" s="100"/>
-      <x:c r="V47" s="82"/>
-      <x:c r="W47" s="79"/>
-      <x:c r="X47" s="97" t="str">
+      <x:c r="U47" s="100" t="str">
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Underwater%20World%20Langkawi%2C%20Kedah%2C%20Malaysia</x:v>
+      </x:c>
+      <x:c r="V47" s="180" t="n">
+        <x:v>46240</x:v>
+      </x:c>
+      <x:c r="W47" s="100" t="str">
+        <x:v>Unverified</x:v>
+      </x:c>
+      <x:c r="X47" s="181" t="n">
         <x:f>IF(B47="","",COUNTA(B47:W47)/22)</x:f>
-      </x:c>
-      <x:c r="Y47" s="106"/>
+        <x:v>0.7272727272727273</x:v>
+      </x:c>
+      <x:c r="Y47" s="106" t="str">
+        <x:v>Generated by ChatGPT as a candidate on 2026-08-06. The Google Maps link is for discovery only and is not a verified factual source. Replace it with an official or authoritative source during review.</x:v>
+      </x:c>
     </x:row>
     <x:row r="48">
-      <x:c r="A48" s="76"/>
-      <x:c r="B48" s="79"/>
-      <x:c r="C48" s="79"/>
-      <x:c r="D48" s="79"/>
-      <x:c r="E48" s="79"/>
-      <x:c r="F48" s="100"/>
-      <x:c r="G48" s="79"/>
-      <x:c r="H48" s="100"/>
-      <x:c r="I48" s="85"/>
+      <x:c r="A48" s="76" t="str">
+        <x:v>A045</x:v>
+      </x:c>
+      <x:c r="B48" s="79" t="str">
+        <x:v>Lembah Bujang Archaeological Museum</x:v>
+      </x:c>
+      <x:c r="C48" s="79" t="str">
+        <x:v>Kedah</x:v>
+      </x:c>
+      <x:c r="D48" s="100" t="str">
+        <x:v>Merbok</x:v>
+      </x:c>
+      <x:c r="E48" s="100" t="str">
+        <x:v>Museum and Gallery</x:v>
+      </x:c>
+      <x:c r="F48" s="100" t="str">
+        <x:v>museum; archaeology; heritage; history; culture</x:v>
+      </x:c>
+      <x:c r="G48" s="100" t="str">
+        <x:v>Both</x:v>
+      </x:c>
+      <x:c r="H48" s="100" t="str">
+        <x:v>AI-generated candidate attraction in Merbok, Kedah. The place name, category, description and visitor details require source verification before production use.</x:v>
+      </x:c>
+      <x:c r="I48" s="85" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
       <x:c r="J48" s="88"/>
       <x:c r="K48" s="88"/>
       <x:c r="L48" s="88"/>
-      <x:c r="M48" s="103"/>
-      <x:c r="N48" s="85"/>
-      <x:c r="O48" s="85"/>
-      <x:c r="P48" s="85"/>
-      <x:c r="Q48" s="103"/>
+      <x:c r="M48" s="103" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="N48" s="103" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="O48" s="103" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="P48" s="103" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="Q48" s="103" t="str">
+        <x:v>Accessibility information has not been verified. Confirm terrain, steps, seating, toilets and mobility access with an official source before recommending it as elderly-friendly.</x:v>
+      </x:c>
       <x:c r="R48" s="91"/>
       <x:c r="S48" s="91"/>
       <x:c r="T48" s="103"/>
-      <x:c r="U48" s="100"/>
-      <x:c r="V48" s="82"/>
-      <x:c r="W48" s="79"/>
-      <x:c r="X48" s="97" t="str">
+      <x:c r="U48" s="100" t="str">
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Lembah%20Bujang%20Archaeological%20Museum%2C%20Kedah%2C%20Malaysia</x:v>
+      </x:c>
+      <x:c r="V48" s="180" t="n">
+        <x:v>46240</x:v>
+      </x:c>
+      <x:c r="W48" s="100" t="str">
+        <x:v>Unverified</x:v>
+      </x:c>
+      <x:c r="X48" s="181" t="n">
         <x:f>IF(B48="","",COUNTA(B48:W48)/22)</x:f>
-      </x:c>
-      <x:c r="Y48" s="106"/>
+        <x:v>0.7272727272727273</x:v>
+      </x:c>
+      <x:c r="Y48" s="106" t="str">
+        <x:v>Generated by ChatGPT as a candidate on 2026-08-06. The Google Maps link is for discovery only and is not a verified factual source. Replace it with an official or authoritative source during review.</x:v>
+      </x:c>
     </x:row>
     <x:row r="49">
-      <x:c r="A49" s="76"/>
-      <x:c r="B49" s="79"/>
-      <x:c r="C49" s="79"/>
-      <x:c r="D49" s="79"/>
-      <x:c r="E49" s="79"/>
-      <x:c r="F49" s="100"/>
-      <x:c r="G49" s="79"/>
-      <x:c r="H49" s="100"/>
-      <x:c r="I49" s="85"/>
+      <x:c r="A49" s="76" t="str">
+        <x:v>A046</x:v>
+      </x:c>
+      <x:c r="B49" s="79" t="str">
+        <x:v>Gunung Jerai</x:v>
+      </x:c>
+      <x:c r="C49" s="79" t="str">
+        <x:v>Kedah</x:v>
+      </x:c>
+      <x:c r="D49" s="100" t="str">
+        <x:v>Yan</x:v>
+      </x:c>
+      <x:c r="E49" s="100" t="str">
+        <x:v>Nature</x:v>
+      </x:c>
+      <x:c r="F49" s="100" t="str">
+        <x:v>mountain; scenery; nature; hiking; relaxation</x:v>
+      </x:c>
+      <x:c r="G49" s="100" t="str">
+        <x:v>Outdoor</x:v>
+      </x:c>
+      <x:c r="H49" s="100" t="str">
+        <x:v>AI-generated candidate attraction in Yan, Kedah. The place name, category, description and visitor details require source verification before production use.</x:v>
+      </x:c>
+      <x:c r="I49" s="85" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
       <x:c r="J49" s="88"/>
       <x:c r="K49" s="88"/>
       <x:c r="L49" s="88"/>
-      <x:c r="M49" s="103"/>
-      <x:c r="N49" s="85"/>
-      <x:c r="O49" s="85"/>
-      <x:c r="P49" s="85"/>
-      <x:c r="Q49" s="103"/>
+      <x:c r="M49" s="103" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="N49" s="103" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="O49" s="103" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="P49" s="103" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="Q49" s="103" t="str">
+        <x:v>Accessibility information has not been verified. Confirm terrain, steps, seating, toilets and mobility access with an official source before recommending it as elderly-friendly.</x:v>
+      </x:c>
       <x:c r="R49" s="91"/>
       <x:c r="S49" s="91"/>
       <x:c r="T49" s="103"/>
-      <x:c r="U49" s="100"/>
-      <x:c r="V49" s="82"/>
-      <x:c r="W49" s="79"/>
-      <x:c r="X49" s="97" t="str">
+      <x:c r="U49" s="100" t="str">
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Gunung%20Jerai%2C%20Kedah%2C%20Malaysia</x:v>
+      </x:c>
+      <x:c r="V49" s="180" t="n">
+        <x:v>46240</x:v>
+      </x:c>
+      <x:c r="W49" s="100" t="str">
+        <x:v>Unverified</x:v>
+      </x:c>
+      <x:c r="X49" s="181" t="n">
         <x:f>IF(B49="","",COUNTA(B49:W49)/22)</x:f>
-      </x:c>
-      <x:c r="Y49" s="106"/>
+        <x:v>0.7272727272727273</x:v>
+      </x:c>
+      <x:c r="Y49" s="106" t="str">
+        <x:v>Generated by ChatGPT as a candidate on 2026-08-06. The Google Maps link is for discovery only and is not a verified factual source. Replace it with an official or authoritative source during review.</x:v>
+      </x:c>
     </x:row>
     <x:row r="50">
-      <x:c r="A50" s="76"/>
-      <x:c r="B50" s="79"/>
-      <x:c r="C50" s="79"/>
-      <x:c r="D50" s="79"/>
-      <x:c r="E50" s="79"/>
-      <x:c r="F50" s="100"/>
-      <x:c r="G50" s="79"/>
-      <x:c r="H50" s="100"/>
-      <x:c r="I50" s="85"/>
+      <x:c r="A50" s="76" t="str">
+        <x:v>A047</x:v>
+      </x:c>
+      <x:c r="B50" s="79" t="str">
+        <x:v>Pekan Rabu</x:v>
+      </x:c>
+      <x:c r="C50" s="79" t="str">
+        <x:v>Kedah</x:v>
+      </x:c>
+      <x:c r="D50" s="100" t="str">
+        <x:v>Alor Setar</x:v>
+      </x:c>
+      <x:c r="E50" s="100" t="str">
+        <x:v>Shopping</x:v>
+      </x:c>
+      <x:c r="F50" s="100" t="str">
+        <x:v>market; shopping; local food; handicrafts; culture</x:v>
+      </x:c>
+      <x:c r="G50" s="100" t="str">
+        <x:v>Both</x:v>
+      </x:c>
+      <x:c r="H50" s="100" t="str">
+        <x:v>AI-generated candidate attraction in Alor Setar, Kedah. The place name, category, description and visitor details require source verification before production use.</x:v>
+      </x:c>
+      <x:c r="I50" s="85" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
       <x:c r="J50" s="88"/>
       <x:c r="K50" s="88"/>
       <x:c r="L50" s="88"/>
-      <x:c r="M50" s="103"/>
-      <x:c r="N50" s="85"/>
-      <x:c r="O50" s="85"/>
-      <x:c r="P50" s="85"/>
-      <x:c r="Q50" s="103"/>
+      <x:c r="M50" s="103" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="N50" s="103" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="O50" s="103" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="P50" s="103" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="Q50" s="103" t="str">
+        <x:v>Accessibility information has not been verified. Confirm terrain, steps, seating, toilets and mobility access with an official source before recommending it as elderly-friendly.</x:v>
+      </x:c>
       <x:c r="R50" s="91"/>
       <x:c r="S50" s="91"/>
       <x:c r="T50" s="103"/>
-      <x:c r="U50" s="100"/>
-      <x:c r="V50" s="82"/>
-      <x:c r="W50" s="79"/>
-      <x:c r="X50" s="97" t="str">
+      <x:c r="U50" s="100" t="str">
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Pekan%20Rabu%2C%20Kedah%2C%20Malaysia</x:v>
+      </x:c>
+      <x:c r="V50" s="180" t="n">
+        <x:v>46240</x:v>
+      </x:c>
+      <x:c r="W50" s="100" t="str">
+        <x:v>Unverified</x:v>
+      </x:c>
+      <x:c r="X50" s="181" t="n">
         <x:f>IF(B50="","",COUNTA(B50:W50)/22)</x:f>
-      </x:c>
-      <x:c r="Y50" s="106"/>
+        <x:v>0.7272727272727273</x:v>
+      </x:c>
+      <x:c r="Y50" s="106" t="str">
+        <x:v>Generated by ChatGPT as a candidate on 2026-08-06. The Google Maps link is for discovery only and is not a verified factual source. Replace it with an official or authoritative source during review.</x:v>
+      </x:c>
     </x:row>
     <x:row r="51">
-      <x:c r="A51" s="76"/>
-      <x:c r="B51" s="79"/>
-      <x:c r="C51" s="79"/>
-      <x:c r="D51" s="79"/>
-      <x:c r="E51" s="79"/>
-      <x:c r="F51" s="100"/>
-      <x:c r="G51" s="79"/>
-      <x:c r="H51" s="100"/>
-      <x:c r="I51" s="85"/>
+      <x:c r="A51" s="76" t="str">
+        <x:v>A048</x:v>
+      </x:c>
+      <x:c r="B51" s="79" t="str">
+        <x:v>Siti Khadijah Market</x:v>
+      </x:c>
+      <x:c r="C51" s="79" t="str">
+        <x:v>Kelantan</x:v>
+      </x:c>
+      <x:c r="D51" s="100" t="str">
+        <x:v>Kota Bharu</x:v>
+      </x:c>
+      <x:c r="E51" s="100" t="str">
+        <x:v>Food</x:v>
+      </x:c>
+      <x:c r="F51" s="100" t="str">
+        <x:v>market; local food; shopping; culture; handicrafts</x:v>
+      </x:c>
+      <x:c r="G51" s="100" t="str">
+        <x:v>Indoor</x:v>
+      </x:c>
+      <x:c r="H51" s="100" t="str">
+        <x:v>AI-generated candidate attraction in Kota Bharu, Kelantan. The place name, category, description and visitor details require source verification before production use.</x:v>
+      </x:c>
+      <x:c r="I51" s="85" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
       <x:c r="J51" s="88"/>
       <x:c r="K51" s="88"/>
       <x:c r="L51" s="88"/>
-      <x:c r="M51" s="103"/>
-      <x:c r="N51" s="85"/>
-      <x:c r="O51" s="85"/>
-      <x:c r="P51" s="85"/>
-      <x:c r="Q51" s="103"/>
+      <x:c r="M51" s="103" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="N51" s="103" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="O51" s="103" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="P51" s="103" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="Q51" s="103" t="str">
+        <x:v>Accessibility information has not been verified. Confirm terrain, steps, seating, toilets and mobility access with an official source before recommending it as elderly-friendly.</x:v>
+      </x:c>
       <x:c r="R51" s="91"/>
       <x:c r="S51" s="91"/>
       <x:c r="T51" s="103"/>
-      <x:c r="U51" s="100"/>
-      <x:c r="V51" s="82"/>
-      <x:c r="W51" s="79"/>
-      <x:c r="X51" s="97" t="str">
+      <x:c r="U51" s="100" t="str">
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Siti%20Khadijah%20Market%2C%20Kelantan%2C%20Malaysia</x:v>
+      </x:c>
+      <x:c r="V51" s="180" t="n">
+        <x:v>46240</x:v>
+      </x:c>
+      <x:c r="W51" s="100" t="str">
+        <x:v>Unverified</x:v>
+      </x:c>
+      <x:c r="X51" s="181" t="n">
         <x:f>IF(B51="","",COUNTA(B51:W51)/22)</x:f>
-      </x:c>
-      <x:c r="Y51" s="106"/>
+        <x:v>0.7272727272727273</x:v>
+      </x:c>
+      <x:c r="Y51" s="106" t="str">
+        <x:v>Generated by ChatGPT as a candidate on 2026-08-06. The Google Maps link is for discovery only and is not a verified factual source. Replace it with an official or authoritative source during review.</x:v>
+      </x:c>
     </x:row>
     <x:row r="52">
-      <x:c r="A52" s="76"/>
-      <x:c r="B52" s="79"/>
-      <x:c r="C52" s="79"/>
-      <x:c r="D52" s="79"/>
-      <x:c r="E52" s="79"/>
-      <x:c r="F52" s="100"/>
-      <x:c r="G52" s="79"/>
-      <x:c r="H52" s="100"/>
-      <x:c r="I52" s="85"/>
+      <x:c r="A52" s="76" t="str">
+        <x:v>A049</x:v>
+      </x:c>
+      <x:c r="B52" s="79" t="str">
+        <x:v>Istana Jahar</x:v>
+      </x:c>
+      <x:c r="C52" s="79" t="str">
+        <x:v>Kelantan</x:v>
+      </x:c>
+      <x:c r="D52" s="100" t="str">
+        <x:v>Kota Bharu</x:v>
+      </x:c>
+      <x:c r="E52" s="100" t="str">
+        <x:v>Museum and Gallery</x:v>
+      </x:c>
+      <x:c r="F52" s="100" t="str">
+        <x:v>museum; royal heritage; culture; history; architecture</x:v>
+      </x:c>
+      <x:c r="G52" s="100" t="str">
+        <x:v>Both</x:v>
+      </x:c>
+      <x:c r="H52" s="100" t="str">
+        <x:v>AI-generated candidate attraction in Kota Bharu, Kelantan. The place name, category, description and visitor details require source verification before production use.</x:v>
+      </x:c>
+      <x:c r="I52" s="85" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
       <x:c r="J52" s="88"/>
       <x:c r="K52" s="88"/>
       <x:c r="L52" s="88"/>
-      <x:c r="M52" s="103"/>
-      <x:c r="N52" s="85"/>
-      <x:c r="O52" s="85"/>
-      <x:c r="P52" s="85"/>
-      <x:c r="Q52" s="103"/>
+      <x:c r="M52" s="103" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="N52" s="103" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="O52" s="103" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="P52" s="103" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="Q52" s="103" t="str">
+        <x:v>Accessibility information has not been verified. Confirm terrain, steps, seating, toilets and mobility access with an official source before recommending it as elderly-friendly.</x:v>
+      </x:c>
       <x:c r="R52" s="91"/>
       <x:c r="S52" s="91"/>
       <x:c r="T52" s="103"/>
-      <x:c r="U52" s="100"/>
-      <x:c r="V52" s="82"/>
-      <x:c r="W52" s="79"/>
-      <x:c r="X52" s="97" t="str">
+      <x:c r="U52" s="100" t="str">
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Istana%20Jahar%2C%20Kelantan%2C%20Malaysia</x:v>
+      </x:c>
+      <x:c r="V52" s="180" t="n">
+        <x:v>46240</x:v>
+      </x:c>
+      <x:c r="W52" s="100" t="str">
+        <x:v>Unverified</x:v>
+      </x:c>
+      <x:c r="X52" s="181" t="n">
         <x:f>IF(B52="","",COUNTA(B52:W52)/22)</x:f>
-      </x:c>
-      <x:c r="Y52" s="106"/>
+        <x:v>0.7272727272727273</x:v>
+      </x:c>
+      <x:c r="Y52" s="106" t="str">
+        <x:v>Generated by ChatGPT as a candidate on 2026-08-06. The Google Maps link is for discovery only and is not a verified factual source. Replace it with an official or authoritative source during review.</x:v>
+      </x:c>
     </x:row>
     <x:row r="53">
-      <x:c r="A53" s="77"/>
-      <x:c r="B53" s="80"/>
-      <x:c r="C53" s="80"/>
-      <x:c r="D53" s="80"/>
-      <x:c r="E53" s="80"/>
-      <x:c r="F53" s="101"/>
-      <x:c r="G53" s="80"/>
-      <x:c r="H53" s="101"/>
-      <x:c r="I53" s="86"/>
+      <x:c r="A53" s="77" t="str">
+        <x:v>A050</x:v>
+      </x:c>
+      <x:c r="B53" s="80" t="str">
+        <x:v>Handicraft Village and Craft Museum</x:v>
+      </x:c>
+      <x:c r="C53" s="80" t="str">
+        <x:v>Kelantan</x:v>
+      </x:c>
+      <x:c r="D53" s="101" t="str">
+        <x:v>Kota Bharu</x:v>
+      </x:c>
+      <x:c r="E53" s="101" t="str">
+        <x:v>Culture</x:v>
+      </x:c>
+      <x:c r="F53" s="101" t="str">
+        <x:v>handicrafts; museum; culture; shopping; heritage</x:v>
+      </x:c>
+      <x:c r="G53" s="101" t="str">
+        <x:v>Both</x:v>
+      </x:c>
+      <x:c r="H53" s="101" t="str">
+        <x:v>AI-generated candidate attraction in Kota Bharu, Kelantan. The place name, category, description and visitor details require source verification before production use.</x:v>
+      </x:c>
+      <x:c r="I53" s="86" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
       <x:c r="J53" s="89"/>
       <x:c r="K53" s="89"/>
       <x:c r="L53" s="89"/>
-      <x:c r="M53" s="104"/>
-      <x:c r="N53" s="86"/>
-      <x:c r="O53" s="86"/>
-      <x:c r="P53" s="86"/>
-      <x:c r="Q53" s="104"/>
+      <x:c r="M53" s="104" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="N53" s="104" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="O53" s="104" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="P53" s="104" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="Q53" s="104" t="str">
+        <x:v>Accessibility information has not been verified. Confirm terrain, steps, seating, toilets and mobility access with an official source before recommending it as elderly-friendly.</x:v>
+      </x:c>
       <x:c r="R53" s="92"/>
       <x:c r="S53" s="92"/>
       <x:c r="T53" s="104"/>
-      <x:c r="U53" s="101"/>
-      <x:c r="V53" s="83"/>
-      <x:c r="W53" s="80"/>
-      <x:c r="X53" s="98" t="str">
+      <x:c r="U53" s="101" t="str">
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Handicraft%20Village%20and%20Craft%20Museum%2C%20Kelantan%2C%20Malaysia</x:v>
+      </x:c>
+      <x:c r="V53" s="182" t="n">
+        <x:v>46240</x:v>
+      </x:c>
+      <x:c r="W53" s="101" t="str">
+        <x:v>Unverified</x:v>
+      </x:c>
+      <x:c r="X53" s="183" t="n">
         <x:f>IF(B53="","",COUNTA(B53:W53)/22)</x:f>
-      </x:c>
-      <x:c r="Y53" s="107"/>
+        <x:v>0.7272727272727273</x:v>
+      </x:c>
+      <x:c r="Y53" s="107" t="str">
+        <x:v>Generated by ChatGPT as a candidate on 2026-08-06. The Google Maps link is for discovery only and is not a verified factual source. Replace it with an official or authoritative source during review.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="54">
+      <x:c r="A54" t="str">
+        <x:v>A051</x:v>
+      </x:c>
+      <x:c r="B54" t="str">
+        <x:v>Wat Photivihan</x:v>
+      </x:c>
+      <x:c r="C54" t="str">
+        <x:v>Kelantan</x:v>
+      </x:c>
+      <x:c r="D54" s="179" t="str">
+        <x:v>Tumpat</x:v>
+      </x:c>
+      <x:c r="E54" s="179" t="str">
+        <x:v>Religious Site</x:v>
+      </x:c>
+      <x:c r="F54" s="179" t="str">
+        <x:v>temple; culture; religion; architecture; photography</x:v>
+      </x:c>
+      <x:c r="G54" s="179" t="str">
+        <x:v>Both</x:v>
+      </x:c>
+      <x:c r="H54" s="179" t="str">
+        <x:v>AI-generated candidate attraction in Tumpat, Kelantan. The place name, category, description and visitor details require source verification before production use.</x:v>
+      </x:c>
+      <x:c r="I54" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="J54"/>
+      <x:c r="K54"/>
+      <x:c r="L54"/>
+      <x:c r="M54" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="N54" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="O54" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="P54" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="Q54" s="179" t="str">
+        <x:v>Accessibility information has not been verified. Confirm terrain, steps, seating, toilets and mobility access with an official source before recommending it as elderly-friendly.</x:v>
+      </x:c>
+      <x:c r="R54"/>
+      <x:c r="S54"/>
+      <x:c r="T54" s="179"/>
+      <x:c r="U54" s="179" t="str">
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Wat%20Photivihan%2C%20Kelantan%2C%20Malaysia</x:v>
+      </x:c>
+      <x:c r="V54" s="184" t="n">
+        <x:v>46240</x:v>
+      </x:c>
+      <x:c r="W54" s="179" t="str">
+        <x:v>Unverified</x:v>
+      </x:c>
+      <x:c r="X54" s="185" t="n">
+        <x:f>IF(B54="","",COUNTA(B54:W54)/22)</x:f>
+        <x:v>0.7272727272727273</x:v>
+      </x:c>
+      <x:c r="Y54" s="179" t="str">
+        <x:v>Generated by ChatGPT as a candidate on 2026-08-06. The Google Maps link is for discovery only and is not a verified factual source. Replace it with an official or authoritative source during review.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="55">
+      <x:c r="A55" t="str">
+        <x:v>A052</x:v>
+      </x:c>
+      <x:c r="B55" t="str">
+        <x:v>Pantai Cahaya Bulan</x:v>
+      </x:c>
+      <x:c r="C55" t="str">
+        <x:v>Kelantan</x:v>
+      </x:c>
+      <x:c r="D55" s="179" t="str">
+        <x:v>Kota Bharu</x:v>
+      </x:c>
+      <x:c r="E55" s="179" t="str">
+        <x:v>Beach and Island</x:v>
+      </x:c>
+      <x:c r="F55" s="179" t="str">
+        <x:v>beach; relaxation; food; family; scenery</x:v>
+      </x:c>
+      <x:c r="G55" s="179" t="str">
+        <x:v>Outdoor</x:v>
+      </x:c>
+      <x:c r="H55" s="179" t="str">
+        <x:v>AI-generated candidate attraction in Kota Bharu, Kelantan. The place name, category, description and visitor details require source verification before production use.</x:v>
+      </x:c>
+      <x:c r="I55" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="J55"/>
+      <x:c r="K55"/>
+      <x:c r="L55"/>
+      <x:c r="M55" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="N55" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="O55" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="P55" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="Q55" s="179" t="str">
+        <x:v>Accessibility information has not been verified. Confirm terrain, steps, seating, toilets and mobility access with an official source before recommending it as elderly-friendly.</x:v>
+      </x:c>
+      <x:c r="R55"/>
+      <x:c r="S55"/>
+      <x:c r="T55" s="179"/>
+      <x:c r="U55" s="179" t="str">
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Pantai%20Cahaya%20Bulan%2C%20Kelantan%2C%20Malaysia</x:v>
+      </x:c>
+      <x:c r="V55" s="184" t="n">
+        <x:v>46240</x:v>
+      </x:c>
+      <x:c r="W55" s="179" t="str">
+        <x:v>Unverified</x:v>
+      </x:c>
+      <x:c r="X55" s="185" t="n">
+        <x:f>IF(B55="","",COUNTA(B55:W55)/22)</x:f>
+        <x:v>0.7272727272727273</x:v>
+      </x:c>
+      <x:c r="Y55" s="179" t="str">
+        <x:v>Generated by ChatGPT as a candidate on 2026-08-06. The Google Maps link is for discovery only and is not a verified factual source. Replace it with an official or authoritative source during review.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="56">
+      <x:c r="A56" t="str">
+        <x:v>A053</x:v>
+      </x:c>
+      <x:c r="B56" t="str">
+        <x:v>Pantai Irama</x:v>
+      </x:c>
+      <x:c r="C56" t="str">
+        <x:v>Kelantan</x:v>
+      </x:c>
+      <x:c r="D56" s="179" t="str">
+        <x:v>Bachok</x:v>
+      </x:c>
+      <x:c r="E56" s="179" t="str">
+        <x:v>Beach and Island</x:v>
+      </x:c>
+      <x:c r="F56" s="179" t="str">
+        <x:v>beach; relaxation; family; scenery; picnic</x:v>
+      </x:c>
+      <x:c r="G56" s="179" t="str">
+        <x:v>Outdoor</x:v>
+      </x:c>
+      <x:c r="H56" s="179" t="str">
+        <x:v>AI-generated candidate attraction in Bachok, Kelantan. The place name, category, description and visitor details require source verification before production use.</x:v>
+      </x:c>
+      <x:c r="I56" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="J56"/>
+      <x:c r="K56"/>
+      <x:c r="L56"/>
+      <x:c r="M56" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="N56" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="O56" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="P56" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="Q56" s="179" t="str">
+        <x:v>Accessibility information has not been verified. Confirm terrain, steps, seating, toilets and mobility access with an official source before recommending it as elderly-friendly.</x:v>
+      </x:c>
+      <x:c r="R56"/>
+      <x:c r="S56"/>
+      <x:c r="T56" s="179"/>
+      <x:c r="U56" s="179" t="str">
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Pantai%20Irama%2C%20Kelantan%2C%20Malaysia</x:v>
+      </x:c>
+      <x:c r="V56" s="184" t="n">
+        <x:v>46240</x:v>
+      </x:c>
+      <x:c r="W56" s="179" t="str">
+        <x:v>Unverified</x:v>
+      </x:c>
+      <x:c r="X56" s="185" t="n">
+        <x:f>IF(B56="","",COUNTA(B56:W56)/22)</x:f>
+        <x:v>0.7272727272727273</x:v>
+      </x:c>
+      <x:c r="Y56" s="179" t="str">
+        <x:v>Generated by ChatGPT as a candidate on 2026-08-06. The Google Maps link is for discovery only and is not a verified factual source. Replace it with an official or authoritative source during review.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="57">
+      <x:c r="A57" t="str">
+        <x:v>A054</x:v>
+      </x:c>
+      <x:c r="B57" t="str">
+        <x:v>Gunung Stong State Park</x:v>
+      </x:c>
+      <x:c r="C57" t="str">
+        <x:v>Kelantan</x:v>
+      </x:c>
+      <x:c r="D57" s="179" t="str">
+        <x:v>Dabong</x:v>
+      </x:c>
+      <x:c r="E57" s="179" t="str">
+        <x:v>Adventure</x:v>
+      </x:c>
+      <x:c r="F57" s="179" t="str">
+        <x:v>hiking; waterfall; forest; camping; adventure; nature</x:v>
+      </x:c>
+      <x:c r="G57" s="179" t="str">
+        <x:v>Outdoor</x:v>
+      </x:c>
+      <x:c r="H57" s="179" t="str">
+        <x:v>AI-generated candidate attraction in Dabong, Kelantan. The place name, category, description and visitor details require source verification before production use.</x:v>
+      </x:c>
+      <x:c r="I57" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="J57"/>
+      <x:c r="K57"/>
+      <x:c r="L57"/>
+      <x:c r="M57" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="N57" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="O57" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="P57" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="Q57" s="179" t="str">
+        <x:v>Accessibility information has not been verified. Confirm terrain, steps, seating, toilets and mobility access with an official source before recommending it as elderly-friendly.</x:v>
+      </x:c>
+      <x:c r="R57"/>
+      <x:c r="S57"/>
+      <x:c r="T57" s="179"/>
+      <x:c r="U57" s="179" t="str">
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Gunung%20Stong%20State%20Park%2C%20Kelantan%2C%20Malaysia</x:v>
+      </x:c>
+      <x:c r="V57" s="184" t="n">
+        <x:v>46240</x:v>
+      </x:c>
+      <x:c r="W57" s="179" t="str">
+        <x:v>Unverified</x:v>
+      </x:c>
+      <x:c r="X57" s="185" t="n">
+        <x:f>IF(B57="","",COUNTA(B57:W57)/22)</x:f>
+        <x:v>0.7272727272727273</x:v>
+      </x:c>
+      <x:c r="Y57" s="179" t="str">
+        <x:v>Generated by ChatGPT as a candidate on 2026-08-06. The Google Maps link is for discovery only and is not a verified factual source. Replace it with an official or authoritative source during review.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="58">
+      <x:c r="A58" t="str">
+        <x:v>A055</x:v>
+      </x:c>
+      <x:c r="B58" t="str">
+        <x:v>Min House Camp</x:v>
+      </x:c>
+      <x:c r="C58" t="str">
+        <x:v>Kelantan</x:v>
+      </x:c>
+      <x:c r="D58" s="179" t="str">
+        <x:v>Kota Bharu</x:v>
+      </x:c>
+      <x:c r="E58" s="179" t="str">
+        <x:v>Nature</x:v>
+      </x:c>
+      <x:c r="F58" s="179" t="str">
+        <x:v>nature; river; fireflies; local culture; relaxation</x:v>
+      </x:c>
+      <x:c r="G58" s="179" t="str">
+        <x:v>Outdoor</x:v>
+      </x:c>
+      <x:c r="H58" s="179" t="str">
+        <x:v>AI-generated candidate attraction in Kota Bharu, Kelantan. The place name, category, description and visitor details require source verification before production use.</x:v>
+      </x:c>
+      <x:c r="I58" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="J58"/>
+      <x:c r="K58"/>
+      <x:c r="L58"/>
+      <x:c r="M58" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="N58" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="O58" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="P58" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="Q58" s="179" t="str">
+        <x:v>Accessibility information has not been verified. Confirm terrain, steps, seating, toilets and mobility access with an official source before recommending it as elderly-friendly.</x:v>
+      </x:c>
+      <x:c r="R58"/>
+      <x:c r="S58"/>
+      <x:c r="T58" s="179"/>
+      <x:c r="U58" s="179" t="str">
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Min%20House%20Camp%2C%20Kelantan%2C%20Malaysia</x:v>
+      </x:c>
+      <x:c r="V58" s="184" t="n">
+        <x:v>46240</x:v>
+      </x:c>
+      <x:c r="W58" s="179" t="str">
+        <x:v>Unverified</x:v>
+      </x:c>
+      <x:c r="X58" s="185" t="n">
+        <x:f>IF(B58="","",COUNTA(B58:W58)/22)</x:f>
+        <x:v>0.7272727272727273</x:v>
+      </x:c>
+      <x:c r="Y58" s="179" t="str">
+        <x:v>Generated by ChatGPT as a candidate on 2026-08-06. The Google Maps link is for discovery only and is not a verified factual source. Replace it with an official or authoritative source during review.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="59">
+      <x:c r="A59" t="str">
+        <x:v>A056</x:v>
+      </x:c>
+      <x:c r="B59" t="str">
+        <x:v>Muhammadi Mosque</x:v>
+      </x:c>
+      <x:c r="C59" t="str">
+        <x:v>Kelantan</x:v>
+      </x:c>
+      <x:c r="D59" s="179" t="str">
+        <x:v>Kota Bharu</x:v>
+      </x:c>
+      <x:c r="E59" s="179" t="str">
+        <x:v>Religious Site</x:v>
+      </x:c>
+      <x:c r="F59" s="179" t="str">
+        <x:v>mosque; religion; heritage; architecture; culture</x:v>
+      </x:c>
+      <x:c r="G59" s="179" t="str">
+        <x:v>Both</x:v>
+      </x:c>
+      <x:c r="H59" s="179" t="str">
+        <x:v>AI-generated candidate attraction in Kota Bharu, Kelantan. The place name, category, description and visitor details require source verification before production use.</x:v>
+      </x:c>
+      <x:c r="I59" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="J59"/>
+      <x:c r="K59"/>
+      <x:c r="L59"/>
+      <x:c r="M59" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="N59" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="O59" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="P59" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="Q59" s="179" t="str">
+        <x:v>Accessibility information has not been verified. Confirm terrain, steps, seating, toilets and mobility access with an official source before recommending it as elderly-friendly.</x:v>
+      </x:c>
+      <x:c r="R59"/>
+      <x:c r="S59"/>
+      <x:c r="T59" s="179"/>
+      <x:c r="U59" s="179" t="str">
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Muhammadi%20Mosque%2C%20Kelantan%2C%20Malaysia</x:v>
+      </x:c>
+      <x:c r="V59" s="184" t="n">
+        <x:v>46240</x:v>
+      </x:c>
+      <x:c r="W59" s="179" t="str">
+        <x:v>Unverified</x:v>
+      </x:c>
+      <x:c r="X59" s="185" t="n">
+        <x:f>IF(B59="","",COUNTA(B59:W59)/22)</x:f>
+        <x:v>0.7272727272727273</x:v>
+      </x:c>
+      <x:c r="Y59" s="179" t="str">
+        <x:v>Generated by ChatGPT as a candidate on 2026-08-06. The Google Maps link is for discovery only and is not a verified factual source. Replace it with an official or authoritative source during review.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="60">
+      <x:c r="A60" t="str">
+        <x:v>A057</x:v>
+      </x:c>
+      <x:c r="B60" t="str">
+        <x:v>A Famosa</x:v>
+      </x:c>
+      <x:c r="C60" t="str">
+        <x:v>Melaka</x:v>
+      </x:c>
+      <x:c r="D60" s="179" t="str">
+        <x:v>Melaka City</x:v>
+      </x:c>
+      <x:c r="E60" s="179" t="str">
+        <x:v>Heritage and History</x:v>
+      </x:c>
+      <x:c r="F60" s="179" t="str">
+        <x:v>fort; heritage; history; architecture; photography</x:v>
+      </x:c>
+      <x:c r="G60" s="179" t="str">
+        <x:v>Outdoor</x:v>
+      </x:c>
+      <x:c r="H60" s="179" t="str">
+        <x:v>AI-generated candidate attraction in Melaka City, Melaka. The place name, category, description and visitor details require source verification before production use.</x:v>
+      </x:c>
+      <x:c r="I60" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="J60"/>
+      <x:c r="K60"/>
+      <x:c r="L60"/>
+      <x:c r="M60" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="N60" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="O60" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="P60" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="Q60" s="179" t="str">
+        <x:v>Accessibility information has not been verified. Confirm terrain, steps, seating, toilets and mobility access with an official source before recommending it as elderly-friendly.</x:v>
+      </x:c>
+      <x:c r="R60"/>
+      <x:c r="S60"/>
+      <x:c r="T60" s="179"/>
+      <x:c r="U60" s="179" t="str">
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=A%20Famosa%2C%20Melaka%2C%20Malaysia</x:v>
+      </x:c>
+      <x:c r="V60" s="184" t="n">
+        <x:v>46240</x:v>
+      </x:c>
+      <x:c r="W60" s="179" t="str">
+        <x:v>Unverified</x:v>
+      </x:c>
+      <x:c r="X60" s="185" t="n">
+        <x:f>IF(B60="","",COUNTA(B60:W60)/22)</x:f>
+        <x:v>0.7272727272727273</x:v>
+      </x:c>
+      <x:c r="Y60" s="179" t="str">
+        <x:v>Generated by ChatGPT as a candidate on 2026-08-06. The Google Maps link is for discovery only and is not a verified factual source. Replace it with an official or authoritative source during review.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="61">
+      <x:c r="A61" t="str">
+        <x:v>A058</x:v>
+      </x:c>
+      <x:c r="B61" t="str">
+        <x:v>The Stadthuys</x:v>
+      </x:c>
+      <x:c r="C61" t="str">
+        <x:v>Melaka</x:v>
+      </x:c>
+      <x:c r="D61" s="179" t="str">
+        <x:v>Melaka City</x:v>
+      </x:c>
+      <x:c r="E61" s="179" t="str">
+        <x:v>Museum and Gallery</x:v>
+      </x:c>
+      <x:c r="F61" s="179" t="str">
+        <x:v>museum; colonial heritage; history; architecture</x:v>
+      </x:c>
+      <x:c r="G61" s="179" t="str">
+        <x:v>Both</x:v>
+      </x:c>
+      <x:c r="H61" s="179" t="str">
+        <x:v>AI-generated candidate attraction in Melaka City, Melaka. The place name, category, description and visitor details require source verification before production use.</x:v>
+      </x:c>
+      <x:c r="I61" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="J61"/>
+      <x:c r="K61"/>
+      <x:c r="L61"/>
+      <x:c r="M61" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="N61" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="O61" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="P61" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="Q61" s="179" t="str">
+        <x:v>Accessibility information has not been verified. Confirm terrain, steps, seating, toilets and mobility access with an official source before recommending it as elderly-friendly.</x:v>
+      </x:c>
+      <x:c r="R61"/>
+      <x:c r="S61"/>
+      <x:c r="T61" s="179"/>
+      <x:c r="U61" s="179" t="str">
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=The%20Stadthuys%2C%20Melaka%2C%20Malaysia</x:v>
+      </x:c>
+      <x:c r="V61" s="184" t="n">
+        <x:v>46240</x:v>
+      </x:c>
+      <x:c r="W61" s="179" t="str">
+        <x:v>Unverified</x:v>
+      </x:c>
+      <x:c r="X61" s="185" t="n">
+        <x:f>IF(B61="","",COUNTA(B61:W61)/22)</x:f>
+        <x:v>0.7272727272727273</x:v>
+      </x:c>
+      <x:c r="Y61" s="179" t="str">
+        <x:v>Generated by ChatGPT as a candidate on 2026-08-06. The Google Maps link is for discovery only and is not a verified factual source. Replace it with an official or authoritative source during review.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="62">
+      <x:c r="A62" t="str">
+        <x:v>A059</x:v>
+      </x:c>
+      <x:c r="B62" t="str">
+        <x:v>Jonker Walk</x:v>
+      </x:c>
+      <x:c r="C62" t="str">
+        <x:v>Melaka</x:v>
+      </x:c>
+      <x:c r="D62" s="179" t="str">
+        <x:v>Melaka City</x:v>
+      </x:c>
+      <x:c r="E62" s="179" t="str">
+        <x:v>Shopping</x:v>
+      </x:c>
+      <x:c r="F62" s="179" t="str">
+        <x:v>night market; shopping; local food; heritage; culture</x:v>
+      </x:c>
+      <x:c r="G62" s="179" t="str">
+        <x:v>Outdoor</x:v>
+      </x:c>
+      <x:c r="H62" s="179" t="str">
+        <x:v>AI-generated candidate attraction in Melaka City, Melaka. The place name, category, description and visitor details require source verification before production use.</x:v>
+      </x:c>
+      <x:c r="I62" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="J62"/>
+      <x:c r="K62"/>
+      <x:c r="L62"/>
+      <x:c r="M62" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="N62" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="O62" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="P62" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="Q62" s="179" t="str">
+        <x:v>Accessibility information has not been verified. Confirm terrain, steps, seating, toilets and mobility access with an official source before recommending it as elderly-friendly.</x:v>
+      </x:c>
+      <x:c r="R62"/>
+      <x:c r="S62"/>
+      <x:c r="T62" s="179"/>
+      <x:c r="U62" s="179" t="str">
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Jonker%20Walk%2C%20Melaka%2C%20Malaysia</x:v>
+      </x:c>
+      <x:c r="V62" s="184" t="n">
+        <x:v>46240</x:v>
+      </x:c>
+      <x:c r="W62" s="179" t="str">
+        <x:v>Unverified</x:v>
+      </x:c>
+      <x:c r="X62" s="185" t="n">
+        <x:f>IF(B62="","",COUNTA(B62:W62)/22)</x:f>
+        <x:v>0.7272727272727273</x:v>
+      </x:c>
+      <x:c r="Y62" s="179" t="str">
+        <x:v>Generated by ChatGPT as a candidate on 2026-08-06. The Google Maps link is for discovery only and is not a verified factual source. Replace it with an official or authoritative source during review.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="63">
+      <x:c r="A63" t="str">
+        <x:v>A060</x:v>
+      </x:c>
+      <x:c r="B63" t="str">
+        <x:v>Melaka River Cruise</x:v>
+      </x:c>
+      <x:c r="C63" t="str">
+        <x:v>Melaka</x:v>
+      </x:c>
+      <x:c r="D63" s="179" t="str">
+        <x:v>Melaka City</x:v>
+      </x:c>
+      <x:c r="E63" s="179" t="str">
+        <x:v>Urban Attraction</x:v>
+      </x:c>
+      <x:c r="F63" s="179" t="str">
+        <x:v>river cruise; sightseeing; relaxation; heritage; night activity</x:v>
+      </x:c>
+      <x:c r="G63" s="179" t="str">
+        <x:v>Outdoor</x:v>
+      </x:c>
+      <x:c r="H63" s="179" t="str">
+        <x:v>AI-generated candidate attraction in Melaka City, Melaka. The place name, category, description and visitor details require source verification before production use.</x:v>
+      </x:c>
+      <x:c r="I63" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="J63"/>
+      <x:c r="K63"/>
+      <x:c r="L63"/>
+      <x:c r="M63" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="N63" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="O63" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="P63" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="Q63" s="179" t="str">
+        <x:v>Accessibility information has not been verified. Confirm terrain, steps, seating, toilets and mobility access with an official source before recommending it as elderly-friendly.</x:v>
+      </x:c>
+      <x:c r="R63"/>
+      <x:c r="S63"/>
+      <x:c r="T63" s="179"/>
+      <x:c r="U63" s="179" t="str">
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Melaka%20River%20Cruise%2C%20Melaka%2C%20Malaysia</x:v>
+      </x:c>
+      <x:c r="V63" s="184" t="n">
+        <x:v>46240</x:v>
+      </x:c>
+      <x:c r="W63" s="179" t="str">
+        <x:v>Unverified</x:v>
+      </x:c>
+      <x:c r="X63" s="185" t="n">
+        <x:f>IF(B63="","",COUNTA(B63:W63)/22)</x:f>
+        <x:v>0.7272727272727273</x:v>
+      </x:c>
+      <x:c r="Y63" s="179" t="str">
+        <x:v>Generated by ChatGPT as a candidate on 2026-08-06. The Google Maps link is for discovery only and is not a verified factual source. Replace it with an official or authoritative source during review.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="64">
+      <x:c r="A64" t="str">
+        <x:v>A061</x:v>
+      </x:c>
+      <x:c r="B64" t="str">
+        <x:v>Melaka Sultanate Palace Museum</x:v>
+      </x:c>
+      <x:c r="C64" t="str">
+        <x:v>Melaka</x:v>
+      </x:c>
+      <x:c r="D64" s="179" t="str">
+        <x:v>Melaka City</x:v>
+      </x:c>
+      <x:c r="E64" s="179" t="str">
+        <x:v>Museum and Gallery</x:v>
+      </x:c>
+      <x:c r="F64" s="179" t="str">
+        <x:v>museum; Malay history; culture; heritage</x:v>
+      </x:c>
+      <x:c r="G64" s="179" t="str">
+        <x:v>Both</x:v>
+      </x:c>
+      <x:c r="H64" s="179" t="str">
+        <x:v>AI-generated candidate attraction in Melaka City, Melaka. The place name, category, description and visitor details require source verification before production use.</x:v>
+      </x:c>
+      <x:c r="I64" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="J64"/>
+      <x:c r="K64"/>
+      <x:c r="L64"/>
+      <x:c r="M64" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="N64" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="O64" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="P64" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="Q64" s="179" t="str">
+        <x:v>Accessibility information has not been verified. Confirm terrain, steps, seating, toilets and mobility access with an official source before recommending it as elderly-friendly.</x:v>
+      </x:c>
+      <x:c r="R64"/>
+      <x:c r="S64"/>
+      <x:c r="T64" s="179"/>
+      <x:c r="U64" s="179" t="str">
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Melaka%20Sultanate%20Palace%20Museum%2C%20Melaka%2C%20Malaysia</x:v>
+      </x:c>
+      <x:c r="V64" s="184" t="n">
+        <x:v>46240</x:v>
+      </x:c>
+      <x:c r="W64" s="179" t="str">
+        <x:v>Unverified</x:v>
+      </x:c>
+      <x:c r="X64" s="185" t="n">
+        <x:f>IF(B64="","",COUNTA(B64:W64)/22)</x:f>
+        <x:v>0.7272727272727273</x:v>
+      </x:c>
+      <x:c r="Y64" s="179" t="str">
+        <x:v>Generated by ChatGPT as a candidate on 2026-08-06. The Google Maps link is for discovery only and is not a verified factual source. Replace it with an official or authoritative source during review.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="65">
+      <x:c r="A65" t="str">
+        <x:v>A062</x:v>
+      </x:c>
+      <x:c r="B65" t="str">
+        <x:v>Baba and Nyonya Heritage Museum</x:v>
+      </x:c>
+      <x:c r="C65" t="str">
+        <x:v>Melaka</x:v>
+      </x:c>
+      <x:c r="D65" s="179" t="str">
+        <x:v>Melaka City</x:v>
+      </x:c>
+      <x:c r="E65" s="179" t="str">
+        <x:v>Museum and Gallery</x:v>
+      </x:c>
+      <x:c r="F65" s="179" t="str">
+        <x:v>Peranakan culture; museum; heritage; history</x:v>
+      </x:c>
+      <x:c r="G65" s="179" t="str">
+        <x:v>Indoor</x:v>
+      </x:c>
+      <x:c r="H65" s="179" t="str">
+        <x:v>AI-generated candidate attraction in Melaka City, Melaka. The place name, category, description and visitor details require source verification before production use.</x:v>
+      </x:c>
+      <x:c r="I65" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="J65"/>
+      <x:c r="K65"/>
+      <x:c r="L65"/>
+      <x:c r="M65" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="N65" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="O65" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="P65" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="Q65" s="179" t="str">
+        <x:v>Accessibility information has not been verified. Confirm terrain, steps, seating, toilets and mobility access with an official source before recommending it as elderly-friendly.</x:v>
+      </x:c>
+      <x:c r="R65"/>
+      <x:c r="S65"/>
+      <x:c r="T65" s="179"/>
+      <x:c r="U65" s="179" t="str">
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Baba%20and%20Nyonya%20Heritage%20Museum%2C%20Melaka%2C%20Malaysia</x:v>
+      </x:c>
+      <x:c r="V65" s="184" t="n">
+        <x:v>46240</x:v>
+      </x:c>
+      <x:c r="W65" s="179" t="str">
+        <x:v>Unverified</x:v>
+      </x:c>
+      <x:c r="X65" s="185" t="n">
+        <x:f>IF(B65="","",COUNTA(B65:W65)/22)</x:f>
+        <x:v>0.7272727272727273</x:v>
+      </x:c>
+      <x:c r="Y65" s="179" t="str">
+        <x:v>Generated by ChatGPT as a candidate on 2026-08-06. The Google Maps link is for discovery only and is not a verified factual source. Replace it with an official or authoritative source during review.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="66">
+      <x:c r="A66" t="str">
+        <x:v>A063</x:v>
+      </x:c>
+      <x:c r="B66" t="str">
+        <x:v>Cheng Hoon Teng Temple</x:v>
+      </x:c>
+      <x:c r="C66" t="str">
+        <x:v>Melaka</x:v>
+      </x:c>
+      <x:c r="D66" s="179" t="str">
+        <x:v>Melaka City</x:v>
+      </x:c>
+      <x:c r="E66" s="179" t="str">
+        <x:v>Religious Site</x:v>
+      </x:c>
+      <x:c r="F66" s="179" t="str">
+        <x:v>temple; culture; heritage; architecture</x:v>
+      </x:c>
+      <x:c r="G66" s="179" t="str">
+        <x:v>Both</x:v>
+      </x:c>
+      <x:c r="H66" s="179" t="str">
+        <x:v>AI-generated candidate attraction in Melaka City, Melaka. The place name, category, description and visitor details require source verification before production use.</x:v>
+      </x:c>
+      <x:c r="I66" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="J66"/>
+      <x:c r="K66"/>
+      <x:c r="L66"/>
+      <x:c r="M66" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="N66" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="O66" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="P66" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="Q66" s="179" t="str">
+        <x:v>Accessibility information has not been verified. Confirm terrain, steps, seating, toilets and mobility access with an official source before recommending it as elderly-friendly.</x:v>
+      </x:c>
+      <x:c r="R66"/>
+      <x:c r="S66"/>
+      <x:c r="T66" s="179"/>
+      <x:c r="U66" s="179" t="str">
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Cheng%20Hoon%20Teng%20Temple%2C%20Melaka%2C%20Malaysia</x:v>
+      </x:c>
+      <x:c r="V66" s="184" t="n">
+        <x:v>46240</x:v>
+      </x:c>
+      <x:c r="W66" s="179" t="str">
+        <x:v>Unverified</x:v>
+      </x:c>
+      <x:c r="X66" s="185" t="n">
+        <x:f>IF(B66="","",COUNTA(B66:W66)/22)</x:f>
+        <x:v>0.7272727272727273</x:v>
+      </x:c>
+      <x:c r="Y66" s="179" t="str">
+        <x:v>Generated by ChatGPT as a candidate on 2026-08-06. The Google Maps link is for discovery only and is not a verified factual source. Replace it with an official or authoritative source during review.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="67">
+      <x:c r="A67" t="str">
+        <x:v>A064</x:v>
+      </x:c>
+      <x:c r="B67" t="str">
+        <x:v>Melaka Botanical Garden</x:v>
+      </x:c>
+      <x:c r="C67" t="str">
+        <x:v>Melaka</x:v>
+      </x:c>
+      <x:c r="D67" s="179" t="str">
+        <x:v>Ayer Keroh</x:v>
+      </x:c>
+      <x:c r="E67" s="179" t="str">
+        <x:v>Park and Recreation</x:v>
+      </x:c>
+      <x:c r="F67" s="179" t="str">
+        <x:v>garden; nature; walking; relaxation; family</x:v>
+      </x:c>
+      <x:c r="G67" s="179" t="str">
+        <x:v>Outdoor</x:v>
+      </x:c>
+      <x:c r="H67" s="179" t="str">
+        <x:v>AI-generated candidate attraction in Ayer Keroh, Melaka. The place name, category, description and visitor details require source verification before production use.</x:v>
+      </x:c>
+      <x:c r="I67" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="J67"/>
+      <x:c r="K67"/>
+      <x:c r="L67"/>
+      <x:c r="M67" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="N67" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="O67" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="P67" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="Q67" s="179" t="str">
+        <x:v>Accessibility information has not been verified. Confirm terrain, steps, seating, toilets and mobility access with an official source before recommending it as elderly-friendly.</x:v>
+      </x:c>
+      <x:c r="R67"/>
+      <x:c r="S67"/>
+      <x:c r="T67" s="179"/>
+      <x:c r="U67" s="179" t="str">
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Melaka%20Botanical%20Garden%2C%20Melaka%2C%20Malaysia</x:v>
+      </x:c>
+      <x:c r="V67" s="184" t="n">
+        <x:v>46240</x:v>
+      </x:c>
+      <x:c r="W67" s="179" t="str">
+        <x:v>Unverified</x:v>
+      </x:c>
+      <x:c r="X67" s="185" t="n">
+        <x:f>IF(B67="","",COUNTA(B67:W67)/22)</x:f>
+        <x:v>0.7272727272727273</x:v>
+      </x:c>
+      <x:c r="Y67" s="179" t="str">
+        <x:v>Generated by ChatGPT as a candidate on 2026-08-06. The Google Maps link is for discovery only and is not a verified factual source. Replace it with an official or authoritative source during review.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="68">
+      <x:c r="A68" t="str">
+        <x:v>A065</x:v>
+      </x:c>
+      <x:c r="B68" t="str">
+        <x:v>Army Museum Port Dickson</x:v>
+      </x:c>
+      <x:c r="C68" t="str">
+        <x:v>Negeri Sembilan</x:v>
+      </x:c>
+      <x:c r="D68" s="179" t="str">
+        <x:v>Port Dickson</x:v>
+      </x:c>
+      <x:c r="E68" s="179" t="str">
+        <x:v>Museum and Gallery</x:v>
+      </x:c>
+      <x:c r="F68" s="179" t="str">
+        <x:v>museum; military history; education; heritage</x:v>
+      </x:c>
+      <x:c r="G68" s="179" t="str">
+        <x:v>Both</x:v>
+      </x:c>
+      <x:c r="H68" s="179" t="str">
+        <x:v>AI-generated candidate attraction in Port Dickson, Negeri Sembilan. The place name, category, description and visitor details require source verification before production use.</x:v>
+      </x:c>
+      <x:c r="I68" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="J68"/>
+      <x:c r="K68"/>
+      <x:c r="L68"/>
+      <x:c r="M68" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="N68" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="O68" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="P68" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="Q68" s="179" t="str">
+        <x:v>Accessibility information has not been verified. Confirm terrain, steps, seating, toilets and mobility access with an official source before recommending it as elderly-friendly.</x:v>
+      </x:c>
+      <x:c r="R68"/>
+      <x:c r="S68"/>
+      <x:c r="T68" s="179"/>
+      <x:c r="U68" s="179" t="str">
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Army%20Museum%20Port%20Dickson%2C%20Negeri%20Sembilan%2C%20Malaysia</x:v>
+      </x:c>
+      <x:c r="V68" s="184" t="n">
+        <x:v>46240</x:v>
+      </x:c>
+      <x:c r="W68" s="179" t="str">
+        <x:v>Unverified</x:v>
+      </x:c>
+      <x:c r="X68" s="185" t="n">
+        <x:f>IF(B68="","",COUNTA(B68:W68)/22)</x:f>
+        <x:v>0.7272727272727273</x:v>
+      </x:c>
+      <x:c r="Y68" s="179" t="str">
+        <x:v>Generated by ChatGPT as a candidate on 2026-08-06. The Google Maps link is for discovery only and is not a verified factual source. Replace it with an official or authoritative source during review.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="69">
+      <x:c r="A69" t="str">
+        <x:v>A066</x:v>
+      </x:c>
+      <x:c r="B69" t="str">
+        <x:v>Cape Rachado Lighthouse</x:v>
+      </x:c>
+      <x:c r="C69" t="str">
+        <x:v>Negeri Sembilan</x:v>
+      </x:c>
+      <x:c r="D69" s="179" t="str">
+        <x:v>Port Dickson</x:v>
+      </x:c>
+      <x:c r="E69" s="179" t="str">
+        <x:v>Heritage and History</x:v>
+      </x:c>
+      <x:c r="F69" s="179" t="str">
+        <x:v>lighthouse; hiking; history; scenery; nature</x:v>
+      </x:c>
+      <x:c r="G69" s="179" t="str">
+        <x:v>Outdoor</x:v>
+      </x:c>
+      <x:c r="H69" s="179" t="str">
+        <x:v>AI-generated candidate attraction in Port Dickson, Negeri Sembilan. The place name, category, description and visitor details require source verification before production use.</x:v>
+      </x:c>
+      <x:c r="I69" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="J69"/>
+      <x:c r="K69"/>
+      <x:c r="L69"/>
+      <x:c r="M69" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="N69" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="O69" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="P69" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="Q69" s="179" t="str">
+        <x:v>Accessibility information has not been verified. Confirm terrain, steps, seating, toilets and mobility access with an official source before recommending it as elderly-friendly.</x:v>
+      </x:c>
+      <x:c r="R69"/>
+      <x:c r="S69"/>
+      <x:c r="T69" s="179"/>
+      <x:c r="U69" s="179" t="str">
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Cape%20Rachado%20Lighthouse%2C%20Negeri%20Sembilan%2C%20Malaysia</x:v>
+      </x:c>
+      <x:c r="V69" s="184" t="n">
+        <x:v>46240</x:v>
+      </x:c>
+      <x:c r="W69" s="179" t="str">
+        <x:v>Unverified</x:v>
+      </x:c>
+      <x:c r="X69" s="185" t="n">
+        <x:f>IF(B69="","",COUNTA(B69:W69)/22)</x:f>
+        <x:v>0.7272727272727273</x:v>
+      </x:c>
+      <x:c r="Y69" s="179" t="str">
+        <x:v>Generated by ChatGPT as a candidate on 2026-08-06. The Google Maps link is for discovery only and is not a verified factual source. Replace it with an official or authoritative source during review.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="70">
+      <x:c r="A70" t="str">
+        <x:v>A067</x:v>
+      </x:c>
+      <x:c r="B70" t="str">
+        <x:v>Lukut Museum and Fort</x:v>
+      </x:c>
+      <x:c r="C70" t="str">
+        <x:v>Negeri Sembilan</x:v>
+      </x:c>
+      <x:c r="D70" s="179" t="str">
+        <x:v>Lukut</x:v>
+      </x:c>
+      <x:c r="E70" s="179" t="str">
+        <x:v>Museum and Gallery</x:v>
+      </x:c>
+      <x:c r="F70" s="179" t="str">
+        <x:v>museum; fort; history; heritage; archaeology</x:v>
+      </x:c>
+      <x:c r="G70" s="179" t="str">
+        <x:v>Both</x:v>
+      </x:c>
+      <x:c r="H70" s="179" t="str">
+        <x:v>AI-generated candidate attraction in Lukut, Negeri Sembilan. The place name, category, description and visitor details require source verification before production use.</x:v>
+      </x:c>
+      <x:c r="I70" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="J70"/>
+      <x:c r="K70"/>
+      <x:c r="L70"/>
+      <x:c r="M70" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="N70" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="O70" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="P70" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="Q70" s="179" t="str">
+        <x:v>Accessibility information has not been verified. Confirm terrain, steps, seating, toilets and mobility access with an official source before recommending it as elderly-friendly.</x:v>
+      </x:c>
+      <x:c r="R70"/>
+      <x:c r="S70"/>
+      <x:c r="T70" s="179"/>
+      <x:c r="U70" s="179" t="str">
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Lukut%20Museum%20and%20Fort%2C%20Negeri%20Sembilan%2C%20Malaysia</x:v>
+      </x:c>
+      <x:c r="V70" s="184" t="n">
+        <x:v>46240</x:v>
+      </x:c>
+      <x:c r="W70" s="179" t="str">
+        <x:v>Unverified</x:v>
+      </x:c>
+      <x:c r="X70" s="185" t="n">
+        <x:f>IF(B70="","",COUNTA(B70:W70)/22)</x:f>
+        <x:v>0.7272727272727273</x:v>
+      </x:c>
+      <x:c r="Y70" s="179" t="str">
+        <x:v>Generated by ChatGPT as a candidate on 2026-08-06. The Google Maps link is for discovery only and is not a verified factual source. Replace it with an official or authoritative source during review.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="71">
+      <x:c r="A71" t="str">
+        <x:v>A068</x:v>
+      </x:c>
+      <x:c r="B71" t="str">
+        <x:v>Royal Museum of Seri Menanti</x:v>
+      </x:c>
+      <x:c r="C71" t="str">
+        <x:v>Negeri Sembilan</x:v>
+      </x:c>
+      <x:c r="D71" s="179" t="str">
+        <x:v>Kuala Pilah</x:v>
+      </x:c>
+      <x:c r="E71" s="179" t="str">
+        <x:v>Museum and Gallery</x:v>
+      </x:c>
+      <x:c r="F71" s="179" t="str">
+        <x:v>royal museum; Minangkabau; culture; heritage; architecture</x:v>
+      </x:c>
+      <x:c r="G71" s="179" t="str">
+        <x:v>Both</x:v>
+      </x:c>
+      <x:c r="H71" s="179" t="str">
+        <x:v>AI-generated candidate attraction in Kuala Pilah, Negeri Sembilan. The place name, category, description and visitor details require source verification before production use.</x:v>
+      </x:c>
+      <x:c r="I71" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="J71"/>
+      <x:c r="K71"/>
+      <x:c r="L71"/>
+      <x:c r="M71" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="N71" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="O71" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="P71" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="Q71" s="179" t="str">
+        <x:v>Accessibility information has not been verified. Confirm terrain, steps, seating, toilets and mobility access with an official source before recommending it as elderly-friendly.</x:v>
+      </x:c>
+      <x:c r="R71"/>
+      <x:c r="S71"/>
+      <x:c r="T71" s="179"/>
+      <x:c r="U71" s="179" t="str">
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Royal%20Museum%20of%20Seri%20Menanti%2C%20Negeri%20Sembilan%2C%20Malaysia</x:v>
+      </x:c>
+      <x:c r="V71" s="184" t="n">
+        <x:v>46240</x:v>
+      </x:c>
+      <x:c r="W71" s="179" t="str">
+        <x:v>Unverified</x:v>
+      </x:c>
+      <x:c r="X71" s="185" t="n">
+        <x:f>IF(B71="","",COUNTA(B71:W71)/22)</x:f>
+        <x:v>0.7272727272727273</x:v>
+      </x:c>
+      <x:c r="Y71" s="179" t="str">
+        <x:v>Generated by ChatGPT as a candidate on 2026-08-06. The Google Maps link is for discovery only and is not a verified factual source. Replace it with an official or authoritative source during review.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="72">
+      <x:c r="A72" t="str">
+        <x:v>A069</x:v>
+      </x:c>
+      <x:c r="B72" t="str">
+        <x:v>Jelita Ostrich Farm</x:v>
+      </x:c>
+      <x:c r="C72" t="str">
+        <x:v>Negeri Sembilan</x:v>
+      </x:c>
+      <x:c r="D72" s="179" t="str">
+        <x:v>Seremban</x:v>
+      </x:c>
+      <x:c r="E72" s="179" t="str">
+        <x:v>Family Attraction</x:v>
+      </x:c>
+      <x:c r="F72" s="179" t="str">
+        <x:v>ostrich; animals; farm; family; children</x:v>
+      </x:c>
+      <x:c r="G72" s="179" t="str">
+        <x:v>Outdoor</x:v>
+      </x:c>
+      <x:c r="H72" s="179" t="str">
+        <x:v>AI-generated candidate attraction in Seremban, Negeri Sembilan. The place name, category, description and visitor details require source verification before production use.</x:v>
+      </x:c>
+      <x:c r="I72" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="J72"/>
+      <x:c r="K72"/>
+      <x:c r="L72"/>
+      <x:c r="M72" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="N72" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="O72" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="P72" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="Q72" s="179" t="str">
+        <x:v>Accessibility information has not been verified. Confirm terrain, steps, seating, toilets and mobility access with an official source before recommending it as elderly-friendly.</x:v>
+      </x:c>
+      <x:c r="R72"/>
+      <x:c r="S72"/>
+      <x:c r="T72" s="179"/>
+      <x:c r="U72" s="179" t="str">
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Jelita%20Ostrich%20Farm%2C%20Negeri%20Sembilan%2C%20Malaysia</x:v>
+      </x:c>
+      <x:c r="V72" s="184" t="n">
+        <x:v>46240</x:v>
+      </x:c>
+      <x:c r="W72" s="179" t="str">
+        <x:v>Unverified</x:v>
+      </x:c>
+      <x:c r="X72" s="185" t="n">
+        <x:f>IF(B72="","",COUNTA(B72:W72)/22)</x:f>
+        <x:v>0.7272727272727273</x:v>
+      </x:c>
+      <x:c r="Y72" s="179" t="str">
+        <x:v>Generated by ChatGPT as a candidate on 2026-08-06. The Google Maps link is for discovery only and is not a verified factual source. Replace it with an official or authoritative source during review.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="73">
+      <x:c r="A73" t="str">
+        <x:v>A070</x:v>
+      </x:c>
+      <x:c r="B73" t="str">
+        <x:v>Gunung Angsi</x:v>
+      </x:c>
+      <x:c r="C73" t="str">
+        <x:v>Negeri Sembilan</x:v>
+      </x:c>
+      <x:c r="D73" s="179" t="str">
+        <x:v>Kuala Pilah</x:v>
+      </x:c>
+      <x:c r="E73" s="179" t="str">
+        <x:v>Adventure</x:v>
+      </x:c>
+      <x:c r="F73" s="179" t="str">
+        <x:v>hiking; mountain; forest; adventure; nature</x:v>
+      </x:c>
+      <x:c r="G73" s="179" t="str">
+        <x:v>Outdoor</x:v>
+      </x:c>
+      <x:c r="H73" s="179" t="str">
+        <x:v>AI-generated candidate attraction in Kuala Pilah, Negeri Sembilan. The place name, category, description and visitor details require source verification before production use.</x:v>
+      </x:c>
+      <x:c r="I73" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="J73"/>
+      <x:c r="K73"/>
+      <x:c r="L73"/>
+      <x:c r="M73" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="N73" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="O73" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="P73" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="Q73" s="179" t="str">
+        <x:v>Accessibility information has not been verified. Confirm terrain, steps, seating, toilets and mobility access with an official source before recommending it as elderly-friendly.</x:v>
+      </x:c>
+      <x:c r="R73"/>
+      <x:c r="S73"/>
+      <x:c r="T73" s="179"/>
+      <x:c r="U73" s="179" t="str">
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Gunung%20Angsi%2C%20Negeri%20Sembilan%2C%20Malaysia</x:v>
+      </x:c>
+      <x:c r="V73" s="184" t="n">
+        <x:v>46240</x:v>
+      </x:c>
+      <x:c r="W73" s="179" t="str">
+        <x:v>Unverified</x:v>
+      </x:c>
+      <x:c r="X73" s="185" t="n">
+        <x:f>IF(B73="","",COUNTA(B73:W73)/22)</x:f>
+        <x:v>0.7272727272727273</x:v>
+      </x:c>
+      <x:c r="Y73" s="179" t="str">
+        <x:v>Generated by ChatGPT as a candidate on 2026-08-06. The Google Maps link is for discovery only and is not a verified factual source. Replace it with an official or authoritative source during review.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="74">
+      <x:c r="A74" t="str">
+        <x:v>A071</x:v>
+      </x:c>
+      <x:c r="B74" t="str">
+        <x:v>Taman Tasik Seremban</x:v>
+      </x:c>
+      <x:c r="C74" t="str">
+        <x:v>Negeri Sembilan</x:v>
+      </x:c>
+      <x:c r="D74" s="179" t="str">
+        <x:v>Seremban</x:v>
+      </x:c>
+      <x:c r="E74" s="179" t="str">
+        <x:v>Park and Recreation</x:v>
+      </x:c>
+      <x:c r="F74" s="179" t="str">
+        <x:v>lake; walking; relaxation; family; urban park</x:v>
+      </x:c>
+      <x:c r="G74" s="179" t="str">
+        <x:v>Outdoor</x:v>
+      </x:c>
+      <x:c r="H74" s="179" t="str">
+        <x:v>AI-generated candidate attraction in Seremban, Negeri Sembilan. The place name, category, description and visitor details require source verification before production use.</x:v>
+      </x:c>
+      <x:c r="I74" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="J74"/>
+      <x:c r="K74"/>
+      <x:c r="L74"/>
+      <x:c r="M74" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="N74" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="O74" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="P74" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="Q74" s="179" t="str">
+        <x:v>Accessibility information has not been verified. Confirm terrain, steps, seating, toilets and mobility access with an official source before recommending it as elderly-friendly.</x:v>
+      </x:c>
+      <x:c r="R74"/>
+      <x:c r="S74"/>
+      <x:c r="T74" s="179"/>
+      <x:c r="U74" s="179" t="str">
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Taman%20Tasik%20Seremban%2C%20Negeri%20Sembilan%2C%20Malaysia</x:v>
+      </x:c>
+      <x:c r="V74" s="184" t="n">
+        <x:v>46240</x:v>
+      </x:c>
+      <x:c r="W74" s="179" t="str">
+        <x:v>Unverified</x:v>
+      </x:c>
+      <x:c r="X74" s="185" t="n">
+        <x:f>IF(B74="","",COUNTA(B74:W74)/22)</x:f>
+        <x:v>0.7272727272727273</x:v>
+      </x:c>
+      <x:c r="Y74" s="179" t="str">
+        <x:v>Generated by ChatGPT as a candidate on 2026-08-06. The Google Maps link is for discovery only and is not a verified factual source. Replace it with an official or authoritative source during review.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="75">
+      <x:c r="A75" t="str">
+        <x:v>A072</x:v>
+      </x:c>
+      <x:c r="B75" t="str">
+        <x:v>Jeram Toi Recreational Forest</x:v>
+      </x:c>
+      <x:c r="C75" t="str">
+        <x:v>Negeri Sembilan</x:v>
+      </x:c>
+      <x:c r="D75" s="179" t="str">
+        <x:v>Jelebu</x:v>
+      </x:c>
+      <x:c r="E75" s="179" t="str">
+        <x:v>Nature</x:v>
+      </x:c>
+      <x:c r="F75" s="179" t="str">
+        <x:v>waterfall; forest; picnic; nature; relaxation</x:v>
+      </x:c>
+      <x:c r="G75" s="179" t="str">
+        <x:v>Outdoor</x:v>
+      </x:c>
+      <x:c r="H75" s="179" t="str">
+        <x:v>AI-generated candidate attraction in Jelebu, Negeri Sembilan. The place name, category, description and visitor details require source verification before production use.</x:v>
+      </x:c>
+      <x:c r="I75" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="J75"/>
+      <x:c r="K75"/>
+      <x:c r="L75"/>
+      <x:c r="M75" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="N75" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="O75" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="P75" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="Q75" s="179" t="str">
+        <x:v>Accessibility information has not been verified. Confirm terrain, steps, seating, toilets and mobility access with an official source before recommending it as elderly-friendly.</x:v>
+      </x:c>
+      <x:c r="R75"/>
+      <x:c r="S75"/>
+      <x:c r="T75" s="179"/>
+      <x:c r="U75" s="179" t="str">
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Jeram%20Toi%20Recreational%20Forest%2C%20Negeri%20Sembilan%2C%20Malaysia</x:v>
+      </x:c>
+      <x:c r="V75" s="184" t="n">
+        <x:v>46240</x:v>
+      </x:c>
+      <x:c r="W75" s="179" t="str">
+        <x:v>Unverified</x:v>
+      </x:c>
+      <x:c r="X75" s="185" t="n">
+        <x:f>IF(B75="","",COUNTA(B75:W75)/22)</x:f>
+        <x:v>0.7272727272727273</x:v>
+      </x:c>
+      <x:c r="Y75" s="179" t="str">
+        <x:v>Generated by ChatGPT as a candidate on 2026-08-06. The Google Maps link is for discovery only and is not a verified factual source. Replace it with an official or authoritative source during review.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="76">
+      <x:c r="A76" t="str">
+        <x:v>A073</x:v>
+      </x:c>
+      <x:c r="B76" t="str">
+        <x:v>Taman Negara Kuala Tahan</x:v>
+      </x:c>
+      <x:c r="C76" t="str">
+        <x:v>Pahang</x:v>
+      </x:c>
+      <x:c r="D76" s="179" t="str">
+        <x:v>Jerantut</x:v>
+      </x:c>
+      <x:c r="E76" s="179" t="str">
+        <x:v>Adventure</x:v>
+      </x:c>
+      <x:c r="F76" s="179" t="str">
+        <x:v>rainforest; hiking; wildlife; canopy walk; adventure</x:v>
+      </x:c>
+      <x:c r="G76" s="179" t="str">
+        <x:v>Outdoor</x:v>
+      </x:c>
+      <x:c r="H76" s="179" t="str">
+        <x:v>AI-generated candidate attraction in Jerantut, Pahang. The place name, category, description and visitor details require source verification before production use.</x:v>
+      </x:c>
+      <x:c r="I76" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="J76"/>
+      <x:c r="K76"/>
+      <x:c r="L76"/>
+      <x:c r="M76" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="N76" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="O76" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="P76" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="Q76" s="179" t="str">
+        <x:v>Accessibility information has not been verified. Confirm terrain, steps, seating, toilets and mobility access with an official source before recommending it as elderly-friendly.</x:v>
+      </x:c>
+      <x:c r="R76"/>
+      <x:c r="S76"/>
+      <x:c r="T76" s="179"/>
+      <x:c r="U76" s="179" t="str">
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Taman%20Negara%20Kuala%20Tahan%2C%20Pahang%2C%20Malaysia</x:v>
+      </x:c>
+      <x:c r="V76" s="184" t="n">
+        <x:v>46240</x:v>
+      </x:c>
+      <x:c r="W76" s="179" t="str">
+        <x:v>Unverified</x:v>
+      </x:c>
+      <x:c r="X76" s="185" t="n">
+        <x:f>IF(B76="","",COUNTA(B76:W76)/22)</x:f>
+        <x:v>0.7272727272727273</x:v>
+      </x:c>
+      <x:c r="Y76" s="179" t="str">
+        <x:v>Generated by ChatGPT as a candidate on 2026-08-06. The Google Maps link is for discovery only and is not a verified factual source. Replace it with an official or authoritative source during review.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="77">
+      <x:c r="A77" t="str">
+        <x:v>A074</x:v>
+      </x:c>
+      <x:c r="B77" t="str">
+        <x:v>Fraser's Hill</x:v>
+      </x:c>
+      <x:c r="C77" t="str">
+        <x:v>Pahang</x:v>
+      </x:c>
+      <x:c r="D77" s="179" t="str">
+        <x:v>Raub</x:v>
+      </x:c>
+      <x:c r="E77" s="179" t="str">
+        <x:v>Wellness and Relaxation</x:v>
+      </x:c>
+      <x:c r="F77" s="179" t="str">
+        <x:v>cool climate; birdwatching; relaxation; nature; walking</x:v>
+      </x:c>
+      <x:c r="G77" s="179" t="str">
+        <x:v>Outdoor</x:v>
+      </x:c>
+      <x:c r="H77" s="179" t="str">
+        <x:v>AI-generated candidate attraction in Raub, Pahang. The place name, category, description and visitor details require source verification before production use.</x:v>
+      </x:c>
+      <x:c r="I77" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="J77"/>
+      <x:c r="K77"/>
+      <x:c r="L77"/>
+      <x:c r="M77" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="N77" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="O77" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="P77" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="Q77" s="179" t="str">
+        <x:v>Accessibility information has not been verified. Confirm terrain, steps, seating, toilets and mobility access with an official source before recommending it as elderly-friendly.</x:v>
+      </x:c>
+      <x:c r="R77"/>
+      <x:c r="S77"/>
+      <x:c r="T77" s="179"/>
+      <x:c r="U77" s="179" t="str">
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Fraser's%20Hill%2C%20Pahang%2C%20Malaysia</x:v>
+      </x:c>
+      <x:c r="V77" s="184" t="n">
+        <x:v>46240</x:v>
+      </x:c>
+      <x:c r="W77" s="179" t="str">
+        <x:v>Unverified</x:v>
+      </x:c>
+      <x:c r="X77" s="185" t="n">
+        <x:f>IF(B77="","",COUNTA(B77:W77)/22)</x:f>
+        <x:v>0.7272727272727273</x:v>
+      </x:c>
+      <x:c r="Y77" s="179" t="str">
+        <x:v>Generated by ChatGPT as a candidate on 2026-08-06. The Google Maps link is for discovery only and is not a verified factual source. Replace it with an official or authoritative source during review.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="78">
+      <x:c r="A78" t="str">
+        <x:v>A075</x:v>
+      </x:c>
+      <x:c r="B78" t="str">
+        <x:v>Cherating Beach</x:v>
+      </x:c>
+      <x:c r="C78" t="str">
+        <x:v>Pahang</x:v>
+      </x:c>
+      <x:c r="D78" s="179" t="str">
+        <x:v>Kuantan</x:v>
+      </x:c>
+      <x:c r="E78" s="179" t="str">
+        <x:v>Beach and Island</x:v>
+      </x:c>
+      <x:c r="F78" s="179" t="str">
+        <x:v>beach; relaxation; water sports; family; scenery</x:v>
+      </x:c>
+      <x:c r="G78" s="179" t="str">
+        <x:v>Outdoor</x:v>
+      </x:c>
+      <x:c r="H78" s="179" t="str">
+        <x:v>AI-generated candidate attraction in Kuantan, Pahang. The place name, category, description and visitor details require source verification before production use.</x:v>
+      </x:c>
+      <x:c r="I78" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="J78"/>
+      <x:c r="K78"/>
+      <x:c r="L78"/>
+      <x:c r="M78" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="N78" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="O78" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="P78" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="Q78" s="179" t="str">
+        <x:v>Accessibility information has not been verified. Confirm terrain, steps, seating, toilets and mobility access with an official source before recommending it as elderly-friendly.</x:v>
+      </x:c>
+      <x:c r="R78"/>
+      <x:c r="S78"/>
+      <x:c r="T78" s="179"/>
+      <x:c r="U78" s="179" t="str">
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Cherating%20Beach%2C%20Pahang%2C%20Malaysia</x:v>
+      </x:c>
+      <x:c r="V78" s="184" t="n">
+        <x:v>46240</x:v>
+      </x:c>
+      <x:c r="W78" s="179" t="str">
+        <x:v>Unverified</x:v>
+      </x:c>
+      <x:c r="X78" s="185" t="n">
+        <x:f>IF(B78="","",COUNTA(B78:W78)/22)</x:f>
+        <x:v>0.7272727272727273</x:v>
+      </x:c>
+      <x:c r="Y78" s="179" t="str">
+        <x:v>Generated by ChatGPT as a candidate on 2026-08-06. The Google Maps link is for discovery only and is not a verified factual source. Replace it with an official or authoritative source during review.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="79">
+      <x:c r="A79" t="str">
+        <x:v>A076</x:v>
+      </x:c>
+      <x:c r="B79" t="str">
+        <x:v>Kuala Gandah Elephant Conservation Centre</x:v>
+      </x:c>
+      <x:c r="C79" t="str">
+        <x:v>Pahang</x:v>
+      </x:c>
+      <x:c r="D79" s="179" t="str">
+        <x:v>Lanchang</x:v>
+      </x:c>
+      <x:c r="E79" s="179" t="str">
+        <x:v>Wildlife</x:v>
+      </x:c>
+      <x:c r="F79" s="179" t="str">
+        <x:v>elephants; conservation; wildlife; education; family</x:v>
+      </x:c>
+      <x:c r="G79" s="179" t="str">
+        <x:v>Outdoor</x:v>
+      </x:c>
+      <x:c r="H79" s="179" t="str">
+        <x:v>AI-generated candidate attraction in Lanchang, Pahang. The place name, category, description and visitor details require source verification before production use.</x:v>
+      </x:c>
+      <x:c r="I79" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="J79"/>
+      <x:c r="K79"/>
+      <x:c r="L79"/>
+      <x:c r="M79" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="N79" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="O79" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="P79" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="Q79" s="179" t="str">
+        <x:v>Accessibility information has not been verified. Confirm terrain, steps, seating, toilets and mobility access with an official source before recommending it as elderly-friendly.</x:v>
+      </x:c>
+      <x:c r="R79"/>
+      <x:c r="S79"/>
+      <x:c r="T79" s="179"/>
+      <x:c r="U79" s="179" t="str">
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Kuala%20Gandah%20Elephant%20Conservation%20Centre%2C%20Pahang%2C%20Malaysia</x:v>
+      </x:c>
+      <x:c r="V79" s="184" t="n">
+        <x:v>46240</x:v>
+      </x:c>
+      <x:c r="W79" s="179" t="str">
+        <x:v>Unverified</x:v>
+      </x:c>
+      <x:c r="X79" s="185" t="n">
+        <x:f>IF(B79="","",COUNTA(B79:W79)/22)</x:f>
+        <x:v>0.7272727272727273</x:v>
+      </x:c>
+      <x:c r="Y79" s="179" t="str">
+        <x:v>Generated by ChatGPT as a candidate on 2026-08-06. The Google Maps link is for discovery only and is not a verified factual source. Replace it with an official or authoritative source during review.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="80">
+      <x:c r="A80" t="str">
+        <x:v>A077</x:v>
+      </x:c>
+      <x:c r="B80" t="str">
+        <x:v>Sungai Pandan Waterfall</x:v>
+      </x:c>
+      <x:c r="C80" t="str">
+        <x:v>Pahang</x:v>
+      </x:c>
+      <x:c r="D80" s="179" t="str">
+        <x:v>Kuantan</x:v>
+      </x:c>
+      <x:c r="E80" s="179" t="str">
+        <x:v>Nature</x:v>
+      </x:c>
+      <x:c r="F80" s="179" t="str">
+        <x:v>waterfall; picnic; nature; relaxation; family</x:v>
+      </x:c>
+      <x:c r="G80" s="179" t="str">
+        <x:v>Outdoor</x:v>
+      </x:c>
+      <x:c r="H80" s="179" t="str">
+        <x:v>AI-generated candidate attraction in Kuantan, Pahang. The place name, category, description and visitor details require source verification before production use.</x:v>
+      </x:c>
+      <x:c r="I80" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="J80"/>
+      <x:c r="K80"/>
+      <x:c r="L80"/>
+      <x:c r="M80" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="N80" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="O80" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="P80" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="Q80" s="179" t="str">
+        <x:v>Accessibility information has not been verified. Confirm terrain, steps, seating, toilets and mobility access with an official source before recommending it as elderly-friendly.</x:v>
+      </x:c>
+      <x:c r="R80"/>
+      <x:c r="S80"/>
+      <x:c r="T80" s="179"/>
+      <x:c r="U80" s="179" t="str">
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Sungai%20Pandan%20Waterfall%2C%20Pahang%2C%20Malaysia</x:v>
+      </x:c>
+      <x:c r="V80" s="184" t="n">
+        <x:v>46240</x:v>
+      </x:c>
+      <x:c r="W80" s="179" t="str">
+        <x:v>Unverified</x:v>
+      </x:c>
+      <x:c r="X80" s="185" t="n">
+        <x:f>IF(B80="","",COUNTA(B80:W80)/22)</x:f>
+        <x:v>0.7272727272727273</x:v>
+      </x:c>
+      <x:c r="Y80" s="179" t="str">
+        <x:v>Generated by ChatGPT as a candidate on 2026-08-06. The Google Maps link is for discovery only and is not a verified factual source. Replace it with an official or authoritative source during review.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="81">
+      <x:c r="A81" t="str">
+        <x:v>A078</x:v>
+      </x:c>
+      <x:c r="B81" t="str">
+        <x:v>Colmar Tropicale</x:v>
+      </x:c>
+      <x:c r="C81" t="str">
+        <x:v>Pahang</x:v>
+      </x:c>
+      <x:c r="D81" s="179" t="str">
+        <x:v>Bentong</x:v>
+      </x:c>
+      <x:c r="E81" s="179" t="str">
+        <x:v>Family Attraction</x:v>
+      </x:c>
+      <x:c r="F81" s="179" t="str">
+        <x:v>architecture; family; photography; hill resort; relaxation</x:v>
+      </x:c>
+      <x:c r="G81" s="179" t="str">
+        <x:v>Both</x:v>
+      </x:c>
+      <x:c r="H81" s="179" t="str">
+        <x:v>AI-generated candidate attraction in Bentong, Pahang. The place name, category, description and visitor details require source verification before production use.</x:v>
+      </x:c>
+      <x:c r="I81" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="J81"/>
+      <x:c r="K81"/>
+      <x:c r="L81"/>
+      <x:c r="M81" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="N81" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="O81" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="P81" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="Q81" s="179" t="str">
+        <x:v>Accessibility information has not been verified. Confirm terrain, steps, seating, toilets and mobility access with an official source before recommending it as elderly-friendly.</x:v>
+      </x:c>
+      <x:c r="R81"/>
+      <x:c r="S81"/>
+      <x:c r="T81" s="179"/>
+      <x:c r="U81" s="179" t="str">
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Colmar%20Tropicale%2C%20Pahang%2C%20Malaysia</x:v>
+      </x:c>
+      <x:c r="V81" s="184" t="n">
+        <x:v>46240</x:v>
+      </x:c>
+      <x:c r="W81" s="179" t="str">
+        <x:v>Unverified</x:v>
+      </x:c>
+      <x:c r="X81" s="185" t="n">
+        <x:f>IF(B81="","",COUNTA(B81:W81)/22)</x:f>
+        <x:v>0.7272727272727273</x:v>
+      </x:c>
+      <x:c r="Y81" s="179" t="str">
+        <x:v>Generated by ChatGPT as a candidate on 2026-08-06. The Google Maps link is for discovery only and is not a verified factual source. Replace it with an official or authoritative source during review.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="82">
+      <x:c r="A82" t="str">
+        <x:v>A079</x:v>
+      </x:c>
+      <x:c r="B82" t="str">
+        <x:v>Teluk Cempedak</x:v>
+      </x:c>
+      <x:c r="C82" t="str">
+        <x:v>Pahang</x:v>
+      </x:c>
+      <x:c r="D82" s="179" t="str">
+        <x:v>Kuantan</x:v>
+      </x:c>
+      <x:c r="E82" s="179" t="str">
+        <x:v>Beach and Island</x:v>
+      </x:c>
+      <x:c r="F82" s="179" t="str">
+        <x:v>beach; relaxation; food; family; walking</x:v>
+      </x:c>
+      <x:c r="G82" s="179" t="str">
+        <x:v>Outdoor</x:v>
+      </x:c>
+      <x:c r="H82" s="179" t="str">
+        <x:v>AI-generated candidate attraction in Kuantan, Pahang. The place name, category, description and visitor details require source verification before production use.</x:v>
+      </x:c>
+      <x:c r="I82" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="J82"/>
+      <x:c r="K82"/>
+      <x:c r="L82"/>
+      <x:c r="M82" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="N82" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="O82" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="P82" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="Q82" s="179" t="str">
+        <x:v>Accessibility information has not been verified. Confirm terrain, steps, seating, toilets and mobility access with an official source before recommending it as elderly-friendly.</x:v>
+      </x:c>
+      <x:c r="R82"/>
+      <x:c r="S82"/>
+      <x:c r="T82" s="179"/>
+      <x:c r="U82" s="179" t="str">
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Teluk%20Cempedak%2C%20Pahang%2C%20Malaysia</x:v>
+      </x:c>
+      <x:c r="V82" s="184" t="n">
+        <x:v>46240</x:v>
+      </x:c>
+      <x:c r="W82" s="179" t="str">
+        <x:v>Unverified</x:v>
+      </x:c>
+      <x:c r="X82" s="185" t="n">
+        <x:f>IF(B82="","",COUNTA(B82:W82)/22)</x:f>
+        <x:v>0.7272727272727273</x:v>
+      </x:c>
+      <x:c r="Y82" s="179" t="str">
+        <x:v>Generated by ChatGPT as a candidate on 2026-08-06. The Google Maps link is for discovery only and is not a verified factual source. Replace it with an official or authoritative source during review.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="83">
+      <x:c r="A83" t="str">
+        <x:v>A080</x:v>
+      </x:c>
+      <x:c r="B83" t="str">
+        <x:v>Mossy Forest</x:v>
+      </x:c>
+      <x:c r="C83" t="str">
+        <x:v>Pahang</x:v>
+      </x:c>
+      <x:c r="D83" s="179" t="str">
+        <x:v>Cameron Highlands</x:v>
+      </x:c>
+      <x:c r="E83" s="179" t="str">
+        <x:v>Nature</x:v>
+      </x:c>
+      <x:c r="F83" s="179" t="str">
+        <x:v>forest; hiking; scenery; cool climate; nature</x:v>
+      </x:c>
+      <x:c r="G83" s="179" t="str">
+        <x:v>Outdoor</x:v>
+      </x:c>
+      <x:c r="H83" s="179" t="str">
+        <x:v>AI-generated candidate attraction in Cameron Highlands, Pahang. The place name, category, description and visitor details require source verification before production use.</x:v>
+      </x:c>
+      <x:c r="I83" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="J83"/>
+      <x:c r="K83"/>
+      <x:c r="L83"/>
+      <x:c r="M83" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="N83" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="O83" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="P83" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="Q83" s="179" t="str">
+        <x:v>Accessibility information has not been verified. Confirm terrain, steps, seating, toilets and mobility access with an official source before recommending it as elderly-friendly.</x:v>
+      </x:c>
+      <x:c r="R83"/>
+      <x:c r="S83"/>
+      <x:c r="T83" s="179"/>
+      <x:c r="U83" s="179" t="str">
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Mossy%20Forest%2C%20Pahang%2C%20Malaysia</x:v>
+      </x:c>
+      <x:c r="V83" s="184" t="n">
+        <x:v>46240</x:v>
+      </x:c>
+      <x:c r="W83" s="179" t="str">
+        <x:v>Unverified</x:v>
+      </x:c>
+      <x:c r="X83" s="185" t="n">
+        <x:f>IF(B83="","",COUNTA(B83:W83)/22)</x:f>
+        <x:v>0.7272727272727273</x:v>
+      </x:c>
+      <x:c r="Y83" s="179" t="str">
+        <x:v>Generated by ChatGPT as a candidate on 2026-08-06. The Google Maps link is for discovery only and is not a verified factual source. Replace it with an official or authoritative source during review.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="84">
+      <x:c r="A84" t="str">
+        <x:v>A081</x:v>
+      </x:c>
+      <x:c r="B84" t="str">
+        <x:v>George Town UNESCO World Heritage Site</x:v>
+      </x:c>
+      <x:c r="C84" t="str">
+        <x:v>Penang</x:v>
+      </x:c>
+      <x:c r="D84" s="179" t="str">
+        <x:v>George Town</x:v>
+      </x:c>
+      <x:c r="E84" s="179" t="str">
+        <x:v>Heritage and History</x:v>
+      </x:c>
+      <x:c r="F84" s="179" t="str">
+        <x:v>heritage; history; architecture; street art; culture; walking</x:v>
+      </x:c>
+      <x:c r="G84" s="179" t="str">
+        <x:v>Outdoor</x:v>
+      </x:c>
+      <x:c r="H84" s="179" t="str">
+        <x:v>AI-generated candidate attraction in George Town, Penang. The place name, category, description and visitor details require source verification before production use.</x:v>
+      </x:c>
+      <x:c r="I84" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="J84"/>
+      <x:c r="K84"/>
+      <x:c r="L84"/>
+      <x:c r="M84" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="N84" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="O84" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="P84" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="Q84" s="179" t="str">
+        <x:v>Accessibility information has not been verified. Confirm terrain, steps, seating, toilets and mobility access with an official source before recommending it as elderly-friendly.</x:v>
+      </x:c>
+      <x:c r="R84"/>
+      <x:c r="S84"/>
+      <x:c r="T84" s="179"/>
+      <x:c r="U84" s="179" t="str">
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=George%20Town%20UNESCO%20World%20Heritage%20Site%2C%20Penang%2C%20Malaysia</x:v>
+      </x:c>
+      <x:c r="V84" s="184" t="n">
+        <x:v>46240</x:v>
+      </x:c>
+      <x:c r="W84" s="179" t="str">
+        <x:v>Unverified</x:v>
+      </x:c>
+      <x:c r="X84" s="185" t="n">
+        <x:f>IF(B84="","",COUNTA(B84:W84)/22)</x:f>
+        <x:v>0.7272727272727273</x:v>
+      </x:c>
+      <x:c r="Y84" s="179" t="str">
+        <x:v>Generated by ChatGPT as a candidate on 2026-08-06. The Google Maps link is for discovery only and is not a verified factual source. Replace it with an official or authoritative source during review.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="85">
+      <x:c r="A85" t="str">
+        <x:v>A082</x:v>
+      </x:c>
+      <x:c r="B85" t="str">
+        <x:v>Penang Hill</x:v>
+      </x:c>
+      <x:c r="C85" t="str">
+        <x:v>Penang</x:v>
+      </x:c>
+      <x:c r="D85" s="179" t="str">
+        <x:v>George Town</x:v>
+      </x:c>
+      <x:c r="E85" s="179" t="str">
+        <x:v>Wellness and Relaxation</x:v>
+      </x:c>
+      <x:c r="F85" s="179" t="str">
+        <x:v>hill; scenery; cool climate; relaxation; nature; funicular</x:v>
+      </x:c>
+      <x:c r="G85" s="179" t="str">
+        <x:v>Both</x:v>
+      </x:c>
+      <x:c r="H85" s="179" t="str">
+        <x:v>AI-generated candidate attraction in George Town, Penang. The place name, category, description and visitor details require source verification before production use.</x:v>
+      </x:c>
+      <x:c r="I85" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="J85"/>
+      <x:c r="K85"/>
+      <x:c r="L85"/>
+      <x:c r="M85" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="N85" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="O85" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="P85" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="Q85" s="179" t="str">
+        <x:v>Accessibility information has not been verified. Confirm terrain, steps, seating, toilets and mobility access with an official source before recommending it as elderly-friendly.</x:v>
+      </x:c>
+      <x:c r="R85"/>
+      <x:c r="S85"/>
+      <x:c r="T85" s="179"/>
+      <x:c r="U85" s="179" t="str">
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Penang%20Hill%2C%20Penang%2C%20Malaysia</x:v>
+      </x:c>
+      <x:c r="V85" s="184" t="n">
+        <x:v>46240</x:v>
+      </x:c>
+      <x:c r="W85" s="179" t="str">
+        <x:v>Unverified</x:v>
+      </x:c>
+      <x:c r="X85" s="185" t="n">
+        <x:f>IF(B85="","",COUNTA(B85:W85)/22)</x:f>
+        <x:v>0.7272727272727273</x:v>
+      </x:c>
+      <x:c r="Y85" s="179" t="str">
+        <x:v>Generated by ChatGPT as a candidate on 2026-08-06. The Google Maps link is for discovery only and is not a verified factual source. Replace it with an official or authoritative source during review.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="86">
+      <x:c r="A86" t="str">
+        <x:v>A083</x:v>
+      </x:c>
+      <x:c r="B86" t="str">
+        <x:v>Kek Lok Si Temple</x:v>
+      </x:c>
+      <x:c r="C86" t="str">
+        <x:v>Penang</x:v>
+      </x:c>
+      <x:c r="D86" s="179" t="str">
+        <x:v>Air Itam</x:v>
+      </x:c>
+      <x:c r="E86" s="179" t="str">
+        <x:v>Religious Site</x:v>
+      </x:c>
+      <x:c r="F86" s="179" t="str">
+        <x:v>temple; culture; architecture; heritage; photography</x:v>
+      </x:c>
+      <x:c r="G86" s="179" t="str">
+        <x:v>Both</x:v>
+      </x:c>
+      <x:c r="H86" s="179" t="str">
+        <x:v>AI-generated candidate attraction in Air Itam, Penang. The place name, category, description and visitor details require source verification before production use.</x:v>
+      </x:c>
+      <x:c r="I86" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="J86"/>
+      <x:c r="K86"/>
+      <x:c r="L86"/>
+      <x:c r="M86" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="N86" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="O86" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="P86" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="Q86" s="179" t="str">
+        <x:v>Accessibility information has not been verified. Confirm terrain, steps, seating, toilets and mobility access with an official source before recommending it as elderly-friendly.</x:v>
+      </x:c>
+      <x:c r="R86"/>
+      <x:c r="S86"/>
+      <x:c r="T86" s="179"/>
+      <x:c r="U86" s="179" t="str">
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Kek%20Lok%20Si%20Temple%2C%20Penang%2C%20Malaysia</x:v>
+      </x:c>
+      <x:c r="V86" s="184" t="n">
+        <x:v>46240</x:v>
+      </x:c>
+      <x:c r="W86" s="179" t="str">
+        <x:v>Unverified</x:v>
+      </x:c>
+      <x:c r="X86" s="185" t="n">
+        <x:f>IF(B86="","",COUNTA(B86:W86)/22)</x:f>
+        <x:v>0.7272727272727273</x:v>
+      </x:c>
+      <x:c r="Y86" s="179" t="str">
+        <x:v>Generated by ChatGPT as a candidate on 2026-08-06. The Google Maps link is for discovery only and is not a verified factual source. Replace it with an official or authoritative source during review.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="87">
+      <x:c r="A87" t="str">
+        <x:v>A084</x:v>
+      </x:c>
+      <x:c r="B87" t="str">
+        <x:v>Tropical Spice Garden</x:v>
+      </x:c>
+      <x:c r="C87" t="str">
+        <x:v>Penang</x:v>
+      </x:c>
+      <x:c r="D87" s="179" t="str">
+        <x:v>Teluk Bahang</x:v>
+      </x:c>
+      <x:c r="E87" s="179" t="str">
+        <x:v>Nature</x:v>
+      </x:c>
+      <x:c r="F87" s="179" t="str">
+        <x:v>garden; nature; walking; education; relaxation</x:v>
+      </x:c>
+      <x:c r="G87" s="179" t="str">
+        <x:v>Outdoor</x:v>
+      </x:c>
+      <x:c r="H87" s="179" t="str">
+        <x:v>AI-generated candidate attraction in Teluk Bahang, Penang. The place name, category, description and visitor details require source verification before production use.</x:v>
+      </x:c>
+      <x:c r="I87" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="J87"/>
+      <x:c r="K87"/>
+      <x:c r="L87"/>
+      <x:c r="M87" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="N87" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="O87" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="P87" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="Q87" s="179" t="str">
+        <x:v>Accessibility information has not been verified. Confirm terrain, steps, seating, toilets and mobility access with an official source before recommending it as elderly-friendly.</x:v>
+      </x:c>
+      <x:c r="R87"/>
+      <x:c r="S87"/>
+      <x:c r="T87" s="179"/>
+      <x:c r="U87" s="179" t="str">
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Tropical%20Spice%20Garden%2C%20Penang%2C%20Malaysia</x:v>
+      </x:c>
+      <x:c r="V87" s="184" t="n">
+        <x:v>46240</x:v>
+      </x:c>
+      <x:c r="W87" s="179" t="str">
+        <x:v>Unverified</x:v>
+      </x:c>
+      <x:c r="X87" s="185" t="n">
+        <x:f>IF(B87="","",COUNTA(B87:W87)/22)</x:f>
+        <x:v>0.7272727272727273</x:v>
+      </x:c>
+      <x:c r="Y87" s="179" t="str">
+        <x:v>Generated by ChatGPT as a candidate on 2026-08-06. The Google Maps link is for discovery only and is not a verified factual source. Replace it with an official or authoritative source during review.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="88">
+      <x:c r="A88" t="str">
+        <x:v>A085</x:v>
+      </x:c>
+      <x:c r="B88" t="str">
+        <x:v>Entopia by Penang Butterfly Farm</x:v>
+      </x:c>
+      <x:c r="C88" t="str">
+        <x:v>Penang</x:v>
+      </x:c>
+      <x:c r="D88" s="179" t="str">
+        <x:v>Teluk Bahang</x:v>
+      </x:c>
+      <x:c r="E88" s="179" t="str">
+        <x:v>Wildlife</x:v>
+      </x:c>
+      <x:c r="F88" s="179" t="str">
+        <x:v>butterflies; insects; nature; family; children; education</x:v>
+      </x:c>
+      <x:c r="G88" s="179" t="str">
+        <x:v>Both</x:v>
+      </x:c>
+      <x:c r="H88" s="179" t="str">
+        <x:v>AI-generated candidate attraction in Teluk Bahang, Penang. The place name, category, description and visitor details require source verification before production use.</x:v>
+      </x:c>
+      <x:c r="I88" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="J88"/>
+      <x:c r="K88"/>
+      <x:c r="L88"/>
+      <x:c r="M88" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="N88" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="O88" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="P88" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="Q88" s="179" t="str">
+        <x:v>Accessibility information has not been verified. Confirm terrain, steps, seating, toilets and mobility access with an official source before recommending it as elderly-friendly.</x:v>
+      </x:c>
+      <x:c r="R88"/>
+      <x:c r="S88"/>
+      <x:c r="T88" s="179"/>
+      <x:c r="U88" s="179" t="str">
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Entopia%20by%20Penang%20Butterfly%20Farm%2C%20Penang%2C%20Malaysia</x:v>
+      </x:c>
+      <x:c r="V88" s="184" t="n">
+        <x:v>46240</x:v>
+      </x:c>
+      <x:c r="W88" s="179" t="str">
+        <x:v>Unverified</x:v>
+      </x:c>
+      <x:c r="X88" s="185" t="n">
+        <x:f>IF(B88="","",COUNTA(B88:W88)/22)</x:f>
+        <x:v>0.7272727272727273</x:v>
+      </x:c>
+      <x:c r="Y88" s="179" t="str">
+        <x:v>Generated by ChatGPT as a candidate on 2026-08-06. The Google Maps link is for discovery only and is not a verified factual source. Replace it with an official or authoritative source during review.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="89">
+      <x:c r="A89" t="str">
+        <x:v>A086</x:v>
+      </x:c>
+      <x:c r="B89" t="str">
+        <x:v>ESCAPE Penang</x:v>
+      </x:c>
+      <x:c r="C89" t="str">
+        <x:v>Penang</x:v>
+      </x:c>
+      <x:c r="D89" s="179" t="str">
+        <x:v>Teluk Bahang</x:v>
+      </x:c>
+      <x:c r="E89" s="179" t="str">
+        <x:v>Theme Park</x:v>
+      </x:c>
+      <x:c r="F89" s="179" t="str">
+        <x:v>theme park; adventure; family; water park; outdoor activities</x:v>
+      </x:c>
+      <x:c r="G89" s="179" t="str">
+        <x:v>Outdoor</x:v>
+      </x:c>
+      <x:c r="H89" s="179" t="str">
+        <x:v>AI-generated candidate attraction in Teluk Bahang, Penang. The place name, category, description and visitor details require source verification before production use.</x:v>
+      </x:c>
+      <x:c r="I89" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="J89"/>
+      <x:c r="K89"/>
+      <x:c r="L89"/>
+      <x:c r="M89" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="N89" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="O89" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="P89" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="Q89" s="179" t="str">
+        <x:v>Accessibility information has not been verified. Confirm terrain, steps, seating, toilets and mobility access with an official source before recommending it as elderly-friendly.</x:v>
+      </x:c>
+      <x:c r="R89"/>
+      <x:c r="S89"/>
+      <x:c r="T89" s="179"/>
+      <x:c r="U89" s="179" t="str">
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=ESCAPE%20Penang%2C%20Penang%2C%20Malaysia</x:v>
+      </x:c>
+      <x:c r="V89" s="184" t="n">
+        <x:v>46240</x:v>
+      </x:c>
+      <x:c r="W89" s="179" t="str">
+        <x:v>Unverified</x:v>
+      </x:c>
+      <x:c r="X89" s="185" t="n">
+        <x:f>IF(B89="","",COUNTA(B89:W89)/22)</x:f>
+        <x:v>0.7272727272727273</x:v>
+      </x:c>
+      <x:c r="Y89" s="179" t="str">
+        <x:v>Generated by ChatGPT as a candidate on 2026-08-06. The Google Maps link is for discovery only and is not a verified factual source. Replace it with an official or authoritative source during review.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="90">
+      <x:c r="A90" t="str">
+        <x:v>A087</x:v>
+      </x:c>
+      <x:c r="B90" t="str">
+        <x:v>Batu Ferringhi Beach</x:v>
+      </x:c>
+      <x:c r="C90" t="str">
+        <x:v>Penang</x:v>
+      </x:c>
+      <x:c r="D90" s="179" t="str">
+        <x:v>Batu Ferringhi</x:v>
+      </x:c>
+      <x:c r="E90" s="179" t="str">
+        <x:v>Beach and Island</x:v>
+      </x:c>
+      <x:c r="F90" s="179" t="str">
+        <x:v>beach; relaxation; water sports; food; shopping</x:v>
+      </x:c>
+      <x:c r="G90" s="179" t="str">
+        <x:v>Outdoor</x:v>
+      </x:c>
+      <x:c r="H90" s="179" t="str">
+        <x:v>AI-generated candidate attraction in Batu Ferringhi, Penang. The place name, category, description and visitor details require source verification before production use.</x:v>
+      </x:c>
+      <x:c r="I90" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="J90"/>
+      <x:c r="K90"/>
+      <x:c r="L90"/>
+      <x:c r="M90" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="N90" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="O90" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="P90" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="Q90" s="179" t="str">
+        <x:v>Accessibility information has not been verified. Confirm terrain, steps, seating, toilets and mobility access with an official source before recommending it as elderly-friendly.</x:v>
+      </x:c>
+      <x:c r="R90"/>
+      <x:c r="S90"/>
+      <x:c r="T90" s="179"/>
+      <x:c r="U90" s="179" t="str">
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Batu%20Ferringhi%20Beach%2C%20Penang%2C%20Malaysia</x:v>
+      </x:c>
+      <x:c r="V90" s="184" t="n">
+        <x:v>46240</x:v>
+      </x:c>
+      <x:c r="W90" s="179" t="str">
+        <x:v>Unverified</x:v>
+      </x:c>
+      <x:c r="X90" s="185" t="n">
+        <x:f>IF(B90="","",COUNTA(B90:W90)/22)</x:f>
+        <x:v>0.7272727272727273</x:v>
+      </x:c>
+      <x:c r="Y90" s="179" t="str">
+        <x:v>Generated by ChatGPT as a candidate on 2026-08-06. The Google Maps link is for discovery only and is not a verified factual source. Replace it with an official or authoritative source during review.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="91">
+      <x:c r="A91" t="str">
+        <x:v>A088</x:v>
+      </x:c>
+      <x:c r="B91" t="str">
+        <x:v>Penang Botanic Gardens</x:v>
+      </x:c>
+      <x:c r="C91" t="str">
+        <x:v>Penang</x:v>
+      </x:c>
+      <x:c r="D91" s="179" t="str">
+        <x:v>George Town</x:v>
+      </x:c>
+      <x:c r="E91" s="179" t="str">
+        <x:v>Park and Recreation</x:v>
+      </x:c>
+      <x:c r="F91" s="179" t="str">
+        <x:v>garden; walking; nature; relaxation; wildlife</x:v>
+      </x:c>
+      <x:c r="G91" s="179" t="str">
+        <x:v>Outdoor</x:v>
+      </x:c>
+      <x:c r="H91" s="179" t="str">
+        <x:v>AI-generated candidate attraction in George Town, Penang. The place name, category, description and visitor details require source verification before production use.</x:v>
+      </x:c>
+      <x:c r="I91" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="J91"/>
+      <x:c r="K91"/>
+      <x:c r="L91"/>
+      <x:c r="M91" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="N91" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="O91" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="P91" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="Q91" s="179" t="str">
+        <x:v>Accessibility information has not been verified. Confirm terrain, steps, seating, toilets and mobility access with an official source before recommending it as elderly-friendly.</x:v>
+      </x:c>
+      <x:c r="R91"/>
+      <x:c r="S91"/>
+      <x:c r="T91" s="179"/>
+      <x:c r="U91" s="179" t="str">
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Penang%20Botanic%20Gardens%2C%20Penang%2C%20Malaysia</x:v>
+      </x:c>
+      <x:c r="V91" s="184" t="n">
+        <x:v>46240</x:v>
+      </x:c>
+      <x:c r="W91" s="179" t="str">
+        <x:v>Unverified</x:v>
+      </x:c>
+      <x:c r="X91" s="185" t="n">
+        <x:f>IF(B91="","",COUNTA(B91:W91)/22)</x:f>
+        <x:v>0.7272727272727273</x:v>
+      </x:c>
+      <x:c r="Y91" s="179" t="str">
+        <x:v>Generated by ChatGPT as a candidate on 2026-08-06. The Google Maps link is for discovery only and is not a verified factual source. Replace it with an official or authoritative source during review.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="92">
+      <x:c r="A92" t="str">
+        <x:v>A089</x:v>
+      </x:c>
+      <x:c r="B92" t="str">
+        <x:v>Lost World of Tambun</x:v>
+      </x:c>
+      <x:c r="C92" t="str">
+        <x:v>Perak</x:v>
+      </x:c>
+      <x:c r="D92" s="179" t="str">
+        <x:v>Ipoh</x:v>
+      </x:c>
+      <x:c r="E92" s="179" t="str">
+        <x:v>Theme Park</x:v>
+      </x:c>
+      <x:c r="F92" s="179" t="str">
+        <x:v>theme park; hot springs; relaxation; family; water park</x:v>
+      </x:c>
+      <x:c r="G92" s="179" t="str">
+        <x:v>Both</x:v>
+      </x:c>
+      <x:c r="H92" s="179" t="str">
+        <x:v>AI-generated candidate attraction in Ipoh, Perak. The place name, category, description and visitor details require source verification before production use.</x:v>
+      </x:c>
+      <x:c r="I92" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="J92"/>
+      <x:c r="K92"/>
+      <x:c r="L92"/>
+      <x:c r="M92" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="N92" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="O92" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="P92" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="Q92" s="179" t="str">
+        <x:v>Accessibility information has not been verified. Confirm terrain, steps, seating, toilets and mobility access with an official source before recommending it as elderly-friendly.</x:v>
+      </x:c>
+      <x:c r="R92"/>
+      <x:c r="S92"/>
+      <x:c r="T92" s="179"/>
+      <x:c r="U92" s="179" t="str">
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Lost%20World%20of%20Tambun%2C%20Perak%2C%20Malaysia</x:v>
+      </x:c>
+      <x:c r="V92" s="184" t="n">
+        <x:v>46240</x:v>
+      </x:c>
+      <x:c r="W92" s="179" t="str">
+        <x:v>Unverified</x:v>
+      </x:c>
+      <x:c r="X92" s="185" t="n">
+        <x:f>IF(B92="","",COUNTA(B92:W92)/22)</x:f>
+        <x:v>0.7272727272727273</x:v>
+      </x:c>
+      <x:c r="Y92" s="179" t="str">
+        <x:v>Generated by ChatGPT as a candidate on 2026-08-06. The Google Maps link is for discovery only and is not a verified factual source. Replace it with an official or authoritative source during review.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="93">
+      <x:c r="A93" t="str">
+        <x:v>A090</x:v>
+      </x:c>
+      <x:c r="B93" t="str">
+        <x:v>Kellie's Castle</x:v>
+      </x:c>
+      <x:c r="C93" t="str">
+        <x:v>Perak</x:v>
+      </x:c>
+      <x:c r="D93" s="179" t="str">
+        <x:v>Batu Gajah</x:v>
+      </x:c>
+      <x:c r="E93" s="179" t="str">
+        <x:v>Heritage and History</x:v>
+      </x:c>
+      <x:c r="F93" s="179" t="str">
+        <x:v>castle; heritage; history; architecture; photography</x:v>
+      </x:c>
+      <x:c r="G93" s="179" t="str">
+        <x:v>Both</x:v>
+      </x:c>
+      <x:c r="H93" s="179" t="str">
+        <x:v>AI-generated candidate attraction in Batu Gajah, Perak. The place name, category, description and visitor details require source verification before production use.</x:v>
+      </x:c>
+      <x:c r="I93" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="J93"/>
+      <x:c r="K93"/>
+      <x:c r="L93"/>
+      <x:c r="M93" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="N93" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="O93" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="P93" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="Q93" s="179" t="str">
+        <x:v>Accessibility information has not been verified. Confirm terrain, steps, seating, toilets and mobility access with an official source before recommending it as elderly-friendly.</x:v>
+      </x:c>
+      <x:c r="R93"/>
+      <x:c r="S93"/>
+      <x:c r="T93" s="179"/>
+      <x:c r="U93" s="179" t="str">
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Kellie's%20Castle%2C%20Perak%2C%20Malaysia</x:v>
+      </x:c>
+      <x:c r="V93" s="184" t="n">
+        <x:v>46240</x:v>
+      </x:c>
+      <x:c r="W93" s="179" t="str">
+        <x:v>Unverified</x:v>
+      </x:c>
+      <x:c r="X93" s="185" t="n">
+        <x:f>IF(B93="","",COUNTA(B93:W93)/22)</x:f>
+        <x:v>0.7272727272727273</x:v>
+      </x:c>
+      <x:c r="Y93" s="179" t="str">
+        <x:v>Generated by ChatGPT as a candidate on 2026-08-06. The Google Maps link is for discovery only and is not a verified factual source. Replace it with an official or authoritative source during review.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="94">
+      <x:c r="A94" t="str">
+        <x:v>A091</x:v>
+      </x:c>
+      <x:c r="B94" t="str">
+        <x:v>Ipoh Old Town</x:v>
+      </x:c>
+      <x:c r="C94" t="str">
+        <x:v>Perak</x:v>
+      </x:c>
+      <x:c r="D94" s="179" t="str">
+        <x:v>Ipoh</x:v>
+      </x:c>
+      <x:c r="E94" s="179" t="str">
+        <x:v>Urban Attraction</x:v>
+      </x:c>
+      <x:c r="F94" s="179" t="str">
+        <x:v>heritage; street art; local food; history; walking</x:v>
+      </x:c>
+      <x:c r="G94" s="179" t="str">
+        <x:v>Outdoor</x:v>
+      </x:c>
+      <x:c r="H94" s="179" t="str">
+        <x:v>AI-generated candidate attraction in Ipoh, Perak. The place name, category, description and visitor details require source verification before production use.</x:v>
+      </x:c>
+      <x:c r="I94" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="J94"/>
+      <x:c r="K94"/>
+      <x:c r="L94"/>
+      <x:c r="M94" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="N94" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="O94" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="P94" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="Q94" s="179" t="str">
+        <x:v>Accessibility information has not been verified. Confirm terrain, steps, seating, toilets and mobility access with an official source before recommending it as elderly-friendly.</x:v>
+      </x:c>
+      <x:c r="R94"/>
+      <x:c r="S94"/>
+      <x:c r="T94" s="179"/>
+      <x:c r="U94" s="179" t="str">
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Ipoh%20Old%20Town%2C%20Perak%2C%20Malaysia</x:v>
+      </x:c>
+      <x:c r="V94" s="184" t="n">
+        <x:v>46240</x:v>
+      </x:c>
+      <x:c r="W94" s="179" t="str">
+        <x:v>Unverified</x:v>
+      </x:c>
+      <x:c r="X94" s="185" t="n">
+        <x:f>IF(B94="","",COUNTA(B94:W94)/22)</x:f>
+        <x:v>0.7272727272727273</x:v>
+      </x:c>
+      <x:c r="Y94" s="179" t="str">
+        <x:v>Generated by ChatGPT as a candidate on 2026-08-06. The Google Maps link is for discovery only and is not a verified factual source. Replace it with an official or authoritative source during review.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="95">
+      <x:c r="A95" t="str">
+        <x:v>A092</x:v>
+      </x:c>
+      <x:c r="B95" t="str">
+        <x:v>Royal Belum State Park</x:v>
+      </x:c>
+      <x:c r="C95" t="str">
+        <x:v>Perak</x:v>
+      </x:c>
+      <x:c r="D95" s="179" t="str">
+        <x:v>Gerik</x:v>
+      </x:c>
+      <x:c r="E95" s="179" t="str">
+        <x:v>Nature</x:v>
+      </x:c>
+      <x:c r="F95" s="179" t="str">
+        <x:v>rainforest; wildlife; boat trip; nature; adventure</x:v>
+      </x:c>
+      <x:c r="G95" s="179" t="str">
+        <x:v>Outdoor</x:v>
+      </x:c>
+      <x:c r="H95" s="179" t="str">
+        <x:v>AI-generated candidate attraction in Gerik, Perak. The place name, category, description and visitor details require source verification before production use.</x:v>
+      </x:c>
+      <x:c r="I95" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="J95"/>
+      <x:c r="K95"/>
+      <x:c r="L95"/>
+      <x:c r="M95" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="N95" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="O95" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="P95" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="Q95" s="179" t="str">
+        <x:v>Accessibility information has not been verified. Confirm terrain, steps, seating, toilets and mobility access with an official source before recommending it as elderly-friendly.</x:v>
+      </x:c>
+      <x:c r="R95"/>
+      <x:c r="S95"/>
+      <x:c r="T95" s="179"/>
+      <x:c r="U95" s="179" t="str">
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Royal%20Belum%20State%20Park%2C%20Perak%2C%20Malaysia</x:v>
+      </x:c>
+      <x:c r="V95" s="184" t="n">
+        <x:v>46240</x:v>
+      </x:c>
+      <x:c r="W95" s="179" t="str">
+        <x:v>Unverified</x:v>
+      </x:c>
+      <x:c r="X95" s="185" t="n">
+        <x:f>IF(B95="","",COUNTA(B95:W95)/22)</x:f>
+        <x:v>0.7272727272727273</x:v>
+      </x:c>
+      <x:c r="Y95" s="179" t="str">
+        <x:v>Generated by ChatGPT as a candidate on 2026-08-06. The Google Maps link is for discovery only and is not a verified factual source. Replace it with an official or authoritative source during review.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="96">
+      <x:c r="A96" t="str">
+        <x:v>A093</x:v>
+      </x:c>
+      <x:c r="B96" t="str">
+        <x:v>Taiping Lake Gardens</x:v>
+      </x:c>
+      <x:c r="C96" t="str">
+        <x:v>Perak</x:v>
+      </x:c>
+      <x:c r="D96" s="179" t="str">
+        <x:v>Taiping</x:v>
+      </x:c>
+      <x:c r="E96" s="179" t="str">
+        <x:v>Park and Recreation</x:v>
+      </x:c>
+      <x:c r="F96" s="179" t="str">
+        <x:v>lake; garden; walking; relaxation; family</x:v>
+      </x:c>
+      <x:c r="G96" s="179" t="str">
+        <x:v>Outdoor</x:v>
+      </x:c>
+      <x:c r="H96" s="179" t="str">
+        <x:v>AI-generated candidate attraction in Taiping, Perak. The place name, category, description and visitor details require source verification before production use.</x:v>
+      </x:c>
+      <x:c r="I96" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="J96"/>
+      <x:c r="K96"/>
+      <x:c r="L96"/>
+      <x:c r="M96" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="N96" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="O96" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="P96" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="Q96" s="179" t="str">
+        <x:v>Accessibility information has not been verified. Confirm terrain, steps, seating, toilets and mobility access with an official source before recommending it as elderly-friendly.</x:v>
+      </x:c>
+      <x:c r="R96"/>
+      <x:c r="S96"/>
+      <x:c r="T96" s="179"/>
+      <x:c r="U96" s="179" t="str">
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Taiping%20Lake%20Gardens%2C%20Perak%2C%20Malaysia</x:v>
+      </x:c>
+      <x:c r="V96" s="184" t="n">
+        <x:v>46240</x:v>
+      </x:c>
+      <x:c r="W96" s="179" t="str">
+        <x:v>Unverified</x:v>
+      </x:c>
+      <x:c r="X96" s="185" t="n">
+        <x:f>IF(B96="","",COUNTA(B96:W96)/22)</x:f>
+        <x:v>0.7272727272727273</x:v>
+      </x:c>
+      <x:c r="Y96" s="179" t="str">
+        <x:v>Generated by ChatGPT as a candidate on 2026-08-06. The Google Maps link is for discovery only and is not a verified factual source. Replace it with an official or authoritative source during review.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="97">
+      <x:c r="A97" t="str">
+        <x:v>A094</x:v>
+      </x:c>
+      <x:c r="B97" t="str">
+        <x:v>Perak Cave Temple</x:v>
+      </x:c>
+      <x:c r="C97" t="str">
+        <x:v>Perak</x:v>
+      </x:c>
+      <x:c r="D97" s="179" t="str">
+        <x:v>Ipoh</x:v>
+      </x:c>
+      <x:c r="E97" s="179" t="str">
+        <x:v>Religious Site</x:v>
+      </x:c>
+      <x:c r="F97" s="179" t="str">
+        <x:v>cave temple; culture; architecture; religion; scenery</x:v>
+      </x:c>
+      <x:c r="G97" s="179" t="str">
+        <x:v>Both</x:v>
+      </x:c>
+      <x:c r="H97" s="179" t="str">
+        <x:v>AI-generated candidate attraction in Ipoh, Perak. The place name, category, description and visitor details require source verification before production use.</x:v>
+      </x:c>
+      <x:c r="I97" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="J97"/>
+      <x:c r="K97"/>
+      <x:c r="L97"/>
+      <x:c r="M97" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="N97" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="O97" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="P97" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="Q97" s="179" t="str">
+        <x:v>Accessibility information has not been verified. Confirm terrain, steps, seating, toilets and mobility access with an official source before recommending it as elderly-friendly.</x:v>
+      </x:c>
+      <x:c r="R97"/>
+      <x:c r="S97"/>
+      <x:c r="T97" s="179"/>
+      <x:c r="U97" s="179" t="str">
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Perak%20Cave%20Temple%2C%20Perak%2C%20Malaysia</x:v>
+      </x:c>
+      <x:c r="V97" s="184" t="n">
+        <x:v>46240</x:v>
+      </x:c>
+      <x:c r="W97" s="179" t="str">
+        <x:v>Unverified</x:v>
+      </x:c>
+      <x:c r="X97" s="185" t="n">
+        <x:f>IF(B97="","",COUNTA(B97:W97)/22)</x:f>
+        <x:v>0.7272727272727273</x:v>
+      </x:c>
+      <x:c r="Y97" s="179" t="str">
+        <x:v>Generated by ChatGPT as a candidate on 2026-08-06. The Google Maps link is for discovery only and is not a verified factual source. Replace it with an official or authoritative source during review.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="98">
+      <x:c r="A98" t="str">
+        <x:v>A095</x:v>
+      </x:c>
+      <x:c r="B98" t="str">
+        <x:v>Matang Mangrove Forest Reserve</x:v>
+      </x:c>
+      <x:c r="C98" t="str">
+        <x:v>Perak</x:v>
+      </x:c>
+      <x:c r="D98" s="179" t="str">
+        <x:v>Kuala Sepetang</x:v>
+      </x:c>
+      <x:c r="E98" s="179" t="str">
+        <x:v>Nature</x:v>
+      </x:c>
+      <x:c r="F98" s="179" t="str">
+        <x:v>mangrove; nature; wildlife; education; river</x:v>
+      </x:c>
+      <x:c r="G98" s="179" t="str">
+        <x:v>Outdoor</x:v>
+      </x:c>
+      <x:c r="H98" s="179" t="str">
+        <x:v>AI-generated candidate attraction in Kuala Sepetang, Perak. The place name, category, description and visitor details require source verification before production use.</x:v>
+      </x:c>
+      <x:c r="I98" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="J98"/>
+      <x:c r="K98"/>
+      <x:c r="L98"/>
+      <x:c r="M98" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="N98" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="O98" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="P98" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="Q98" s="179" t="str">
+        <x:v>Accessibility information has not been verified. Confirm terrain, steps, seating, toilets and mobility access with an official source before recommending it as elderly-friendly.</x:v>
+      </x:c>
+      <x:c r="R98"/>
+      <x:c r="S98"/>
+      <x:c r="T98" s="179"/>
+      <x:c r="U98" s="179" t="str">
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Matang%20Mangrove%20Forest%20Reserve%2C%20Perak%2C%20Malaysia</x:v>
+      </x:c>
+      <x:c r="V98" s="184" t="n">
+        <x:v>46240</x:v>
+      </x:c>
+      <x:c r="W98" s="179" t="str">
+        <x:v>Unverified</x:v>
+      </x:c>
+      <x:c r="X98" s="185" t="n">
+        <x:f>IF(B98="","",COUNTA(B98:W98)/22)</x:f>
+        <x:v>0.7272727272727273</x:v>
+      </x:c>
+      <x:c r="Y98" s="179" t="str">
+        <x:v>Generated by ChatGPT as a candidate on 2026-08-06. The Google Maps link is for discovery only and is not a verified factual source. Replace it with an official or authoritative source during review.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="99">
+      <x:c r="A99" t="str">
+        <x:v>A096</x:v>
+      </x:c>
+      <x:c r="B99" t="str">
+        <x:v>Gua Tempurung</x:v>
+      </x:c>
+      <x:c r="C99" t="str">
+        <x:v>Perak</x:v>
+      </x:c>
+      <x:c r="D99" s="179" t="str">
+        <x:v>Gopeng</x:v>
+      </x:c>
+      <x:c r="E99" s="179" t="str">
+        <x:v>Adventure</x:v>
+      </x:c>
+      <x:c r="F99" s="179" t="str">
+        <x:v>cave; adventure; geology; hiking; nature</x:v>
+      </x:c>
+      <x:c r="G99" s="179" t="str">
+        <x:v>Outdoor</x:v>
+      </x:c>
+      <x:c r="H99" s="179" t="str">
+        <x:v>AI-generated candidate attraction in Gopeng, Perak. The place name, category, description and visitor details require source verification before production use.</x:v>
+      </x:c>
+      <x:c r="I99" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="J99"/>
+      <x:c r="K99"/>
+      <x:c r="L99"/>
+      <x:c r="M99" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="N99" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="O99" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="P99" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="Q99" s="179" t="str">
+        <x:v>Accessibility information has not been verified. Confirm terrain, steps, seating, toilets and mobility access with an official source before recommending it as elderly-friendly.</x:v>
+      </x:c>
+      <x:c r="R99"/>
+      <x:c r="S99"/>
+      <x:c r="T99" s="179"/>
+      <x:c r="U99" s="179" t="str">
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Gua%20Tempurung%2C%20Perak%2C%20Malaysia</x:v>
+      </x:c>
+      <x:c r="V99" s="184" t="n">
+        <x:v>46240</x:v>
+      </x:c>
+      <x:c r="W99" s="179" t="str">
+        <x:v>Unverified</x:v>
+      </x:c>
+      <x:c r="X99" s="185" t="n">
+        <x:f>IF(B99="","",COUNTA(B99:W99)/22)</x:f>
+        <x:v>0.7272727272727273</x:v>
+      </x:c>
+      <x:c r="Y99" s="179" t="str">
+        <x:v>Generated by ChatGPT as a candidate on 2026-08-06. The Google Maps link is for discovery only and is not a verified factual source. Replace it with an official or authoritative source during review.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="100">
+      <x:c r="A100" t="str">
+        <x:v>A097</x:v>
+      </x:c>
+      <x:c r="B100" t="str">
+        <x:v>Wang Kelian View Point</x:v>
+      </x:c>
+      <x:c r="C100" t="str">
+        <x:v>Perlis</x:v>
+      </x:c>
+      <x:c r="D100" s="179" t="str">
+        <x:v>Kaki Bukit</x:v>
+      </x:c>
+      <x:c r="E100" s="179" t="str">
+        <x:v>Nature</x:v>
+      </x:c>
+      <x:c r="F100" s="179" t="str">
+        <x:v>viewpoint; scenery; sunrise; nature; photography</x:v>
+      </x:c>
+      <x:c r="G100" s="179" t="str">
+        <x:v>Outdoor</x:v>
+      </x:c>
+      <x:c r="H100" s="179" t="str">
+        <x:v>AI-generated candidate attraction in Kaki Bukit, Perlis. The place name, category, description and visitor details require source verification before production use.</x:v>
+      </x:c>
+      <x:c r="I100" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="J100"/>
+      <x:c r="K100"/>
+      <x:c r="L100"/>
+      <x:c r="M100" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="N100" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="O100" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="P100" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="Q100" s="179" t="str">
+        <x:v>Accessibility information has not been verified. Confirm terrain, steps, seating, toilets and mobility access with an official source before recommending it as elderly-friendly.</x:v>
+      </x:c>
+      <x:c r="R100"/>
+      <x:c r="S100"/>
+      <x:c r="T100" s="179"/>
+      <x:c r="U100" s="179" t="str">
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Wang%20Kelian%20View%20Point%2C%20Perlis%2C%20Malaysia</x:v>
+      </x:c>
+      <x:c r="V100" s="184" t="n">
+        <x:v>46240</x:v>
+      </x:c>
+      <x:c r="W100" s="179" t="str">
+        <x:v>Unverified</x:v>
+      </x:c>
+      <x:c r="X100" s="185" t="n">
+        <x:f>IF(B100="","",COUNTA(B100:W100)/22)</x:f>
+        <x:v>0.7272727272727273</x:v>
+      </x:c>
+      <x:c r="Y100" s="179" t="str">
+        <x:v>Generated by ChatGPT as a candidate on 2026-08-06. The Google Maps link is for discovery only and is not a verified factual source. Replace it with an official or authoritative source during review.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="101">
+      <x:c r="A101" t="str">
+        <x:v>A098</x:v>
+      </x:c>
+      <x:c r="B101" t="str">
+        <x:v>Perlis State Park</x:v>
+      </x:c>
+      <x:c r="C101" t="str">
+        <x:v>Perlis</x:v>
+      </x:c>
+      <x:c r="D101" s="179" t="str">
+        <x:v>Wang Kelian</x:v>
+      </x:c>
+      <x:c r="E101" s="179" t="str">
+        <x:v>Adventure</x:v>
+      </x:c>
+      <x:c r="F101" s="179" t="str">
+        <x:v>forest; hiking; caves; wildlife; nature</x:v>
+      </x:c>
+      <x:c r="G101" s="179" t="str">
+        <x:v>Outdoor</x:v>
+      </x:c>
+      <x:c r="H101" s="179" t="str">
+        <x:v>AI-generated candidate attraction in Wang Kelian, Perlis. The place name, category, description and visitor details require source verification before production use.</x:v>
+      </x:c>
+      <x:c r="I101" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="J101"/>
+      <x:c r="K101"/>
+      <x:c r="L101"/>
+      <x:c r="M101" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="N101" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="O101" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="P101" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="Q101" s="179" t="str">
+        <x:v>Accessibility information has not been verified. Confirm terrain, steps, seating, toilets and mobility access with an official source before recommending it as elderly-friendly.</x:v>
+      </x:c>
+      <x:c r="R101"/>
+      <x:c r="S101"/>
+      <x:c r="T101" s="179"/>
+      <x:c r="U101" s="179" t="str">
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Perlis%20State%20Park%2C%20Perlis%2C%20Malaysia</x:v>
+      </x:c>
+      <x:c r="V101" s="184" t="n">
+        <x:v>46240</x:v>
+      </x:c>
+      <x:c r="W101" s="179" t="str">
+        <x:v>Unverified</x:v>
+      </x:c>
+      <x:c r="X101" s="185" t="n">
+        <x:f>IF(B101="","",COUNTA(B101:W101)/22)</x:f>
+        <x:v>0.7272727272727273</x:v>
+      </x:c>
+      <x:c r="Y101" s="179" t="str">
+        <x:v>Generated by ChatGPT as a candidate on 2026-08-06. The Google Maps link is for discovery only and is not a verified factual source. Replace it with an official or authoritative source during review.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="102">
+      <x:c r="A102" t="str">
+        <x:v>A099</x:v>
+      </x:c>
+      <x:c r="B102" t="str">
+        <x:v>Padang Besar Market</x:v>
+      </x:c>
+      <x:c r="C102" t="str">
+        <x:v>Perlis</x:v>
+      </x:c>
+      <x:c r="D102" s="179" t="str">
+        <x:v>Padang Besar</x:v>
+      </x:c>
+      <x:c r="E102" s="179" t="str">
+        <x:v>Shopping</x:v>
+      </x:c>
+      <x:c r="F102" s="179" t="str">
+        <x:v>market; shopping; local food; border town; culture</x:v>
+      </x:c>
+      <x:c r="G102" s="179" t="str">
+        <x:v>Both</x:v>
+      </x:c>
+      <x:c r="H102" s="179" t="str">
+        <x:v>AI-generated candidate attraction in Padang Besar, Perlis. The place name, category, description and visitor details require source verification before production use.</x:v>
+      </x:c>
+      <x:c r="I102" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="J102"/>
+      <x:c r="K102"/>
+      <x:c r="L102"/>
+      <x:c r="M102" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="N102" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="O102" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="P102" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="Q102" s="179" t="str">
+        <x:v>Accessibility information has not been verified. Confirm terrain, steps, seating, toilets and mobility access with an official source before recommending it as elderly-friendly.</x:v>
+      </x:c>
+      <x:c r="R102"/>
+      <x:c r="S102"/>
+      <x:c r="T102" s="179"/>
+      <x:c r="U102" s="179" t="str">
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Padang%20Besar%20Market%2C%20Perlis%2C%20Malaysia</x:v>
+      </x:c>
+      <x:c r="V102" s="184" t="n">
+        <x:v>46240</x:v>
+      </x:c>
+      <x:c r="W102" s="179" t="str">
+        <x:v>Unverified</x:v>
+      </x:c>
+      <x:c r="X102" s="185" t="n">
+        <x:f>IF(B102="","",COUNTA(B102:W102)/22)</x:f>
+        <x:v>0.7272727272727273</x:v>
+      </x:c>
+      <x:c r="Y102" s="179" t="str">
+        <x:v>Generated by ChatGPT as a candidate on 2026-08-06. The Google Maps link is for discovery only and is not a verified factual source. Replace it with an official or authoritative source during review.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="103">
+      <x:c r="A103" t="str">
+        <x:v>A100</x:v>
+      </x:c>
+      <x:c r="B103" t="str">
+        <x:v>Kota Kayang Museum</x:v>
+      </x:c>
+      <x:c r="C103" t="str">
+        <x:v>Perlis</x:v>
+      </x:c>
+      <x:c r="D103" s="179" t="str">
+        <x:v>Kuala Perlis</x:v>
+      </x:c>
+      <x:c r="E103" s="179" t="str">
+        <x:v>Museum and Gallery</x:v>
+      </x:c>
+      <x:c r="F103" s="179" t="str">
+        <x:v>museum; history; archaeology; heritage; culture</x:v>
+      </x:c>
+      <x:c r="G103" s="179" t="str">
+        <x:v>Both</x:v>
+      </x:c>
+      <x:c r="H103" s="179" t="str">
+        <x:v>AI-generated candidate attraction in Kuala Perlis, Perlis. The place name, category, description and visitor details require source verification before production use.</x:v>
+      </x:c>
+      <x:c r="I103" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="J103"/>
+      <x:c r="K103"/>
+      <x:c r="L103"/>
+      <x:c r="M103" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="N103" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="O103" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="P103" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="Q103" s="179" t="str">
+        <x:v>Accessibility information has not been verified. Confirm terrain, steps, seating, toilets and mobility access with an official source before recommending it as elderly-friendly.</x:v>
+      </x:c>
+      <x:c r="R103"/>
+      <x:c r="S103"/>
+      <x:c r="T103" s="179"/>
+      <x:c r="U103" s="179" t="str">
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Kota%20Kayang%20Museum%2C%20Perlis%2C%20Malaysia</x:v>
+      </x:c>
+      <x:c r="V103" s="184" t="n">
+        <x:v>46240</x:v>
+      </x:c>
+      <x:c r="W103" s="179" t="str">
+        <x:v>Unverified</x:v>
+      </x:c>
+      <x:c r="X103" s="185" t="n">
+        <x:f>IF(B103="","",COUNTA(B103:W103)/22)</x:f>
+        <x:v>0.7272727272727273</x:v>
+      </x:c>
+      <x:c r="Y103" s="179" t="str">
+        <x:v>Generated by ChatGPT as a candidate on 2026-08-06. The Google Maps link is for discovery only and is not a verified factual source. Replace it with an official or authoritative source during review.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="104">
+      <x:c r="A104" t="str">
+        <x:v>A101</x:v>
+      </x:c>
+      <x:c r="B104" t="str">
+        <x:v>Tasik Melati Recreational Park</x:v>
+      </x:c>
+      <x:c r="C104" t="str">
+        <x:v>Perlis</x:v>
+      </x:c>
+      <x:c r="D104" s="179" t="str">
+        <x:v>Kangar</x:v>
+      </x:c>
+      <x:c r="E104" s="179" t="str">
+        <x:v>Park and Recreation</x:v>
+      </x:c>
+      <x:c r="F104" s="179" t="str">
+        <x:v>lake; walking; relaxation; family; nature</x:v>
+      </x:c>
+      <x:c r="G104" s="179" t="str">
+        <x:v>Outdoor</x:v>
+      </x:c>
+      <x:c r="H104" s="179" t="str">
+        <x:v>AI-generated candidate attraction in Kangar, Perlis. The place name, category, description and visitor details require source verification before production use.</x:v>
+      </x:c>
+      <x:c r="I104" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="J104"/>
+      <x:c r="K104"/>
+      <x:c r="L104"/>
+      <x:c r="M104" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="N104" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="O104" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="P104" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="Q104" s="179" t="str">
+        <x:v>Accessibility information has not been verified. Confirm terrain, steps, seating, toilets and mobility access with an official source before recommending it as elderly-friendly.</x:v>
+      </x:c>
+      <x:c r="R104"/>
+      <x:c r="S104"/>
+      <x:c r="T104" s="179"/>
+      <x:c r="U104" s="179" t="str">
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Tasik%20Melati%20Recreational%20Park%2C%20Perlis%2C%20Malaysia</x:v>
+      </x:c>
+      <x:c r="V104" s="184" t="n">
+        <x:v>46240</x:v>
+      </x:c>
+      <x:c r="W104" s="179" t="str">
+        <x:v>Unverified</x:v>
+      </x:c>
+      <x:c r="X104" s="185" t="n">
+        <x:f>IF(B104="","",COUNTA(B104:W104)/22)</x:f>
+        <x:v>0.7272727272727273</x:v>
+      </x:c>
+      <x:c r="Y104" s="179" t="str">
+        <x:v>Generated by ChatGPT as a candidate on 2026-08-06. The Google Maps link is for discovery only and is not a verified factual source. Replace it with an official or authoritative source during review.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="105">
+      <x:c r="A105" t="str">
+        <x:v>A102</x:v>
+      </x:c>
+      <x:c r="B105" t="str">
+        <x:v>Perlis Snake and Reptile Farm</x:v>
+      </x:c>
+      <x:c r="C105" t="str">
+        <x:v>Perlis</x:v>
+      </x:c>
+      <x:c r="D105" s="179" t="str">
+        <x:v>Sungai Batu Pahat</x:v>
+      </x:c>
+      <x:c r="E105" s="179" t="str">
+        <x:v>Wildlife</x:v>
+      </x:c>
+      <x:c r="F105" s="179" t="str">
+        <x:v>reptiles; snakes; family; education; wildlife</x:v>
+      </x:c>
+      <x:c r="G105" s="179" t="str">
+        <x:v>Both</x:v>
+      </x:c>
+      <x:c r="H105" s="179" t="str">
+        <x:v>AI-generated candidate attraction in Sungai Batu Pahat, Perlis. The place name, category, description and visitor details require source verification before production use.</x:v>
+      </x:c>
+      <x:c r="I105" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="J105"/>
+      <x:c r="K105"/>
+      <x:c r="L105"/>
+      <x:c r="M105" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="N105" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="O105" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="P105" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="Q105" s="179" t="str">
+        <x:v>Accessibility information has not been verified. Confirm terrain, steps, seating, toilets and mobility access with an official source before recommending it as elderly-friendly.</x:v>
+      </x:c>
+      <x:c r="R105"/>
+      <x:c r="S105"/>
+      <x:c r="T105" s="179"/>
+      <x:c r="U105" s="179" t="str">
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Perlis%20Snake%20and%20Reptile%20Farm%2C%20Perlis%2C%20Malaysia</x:v>
+      </x:c>
+      <x:c r="V105" s="184" t="n">
+        <x:v>46240</x:v>
+      </x:c>
+      <x:c r="W105" s="179" t="str">
+        <x:v>Unverified</x:v>
+      </x:c>
+      <x:c r="X105" s="185" t="n">
+        <x:f>IF(B105="","",COUNTA(B105:W105)/22)</x:f>
+        <x:v>0.7272727272727273</x:v>
+      </x:c>
+      <x:c r="Y105" s="179" t="str">
+        <x:v>Generated by ChatGPT as a candidate on 2026-08-06. The Google Maps link is for discovery only and is not a verified factual source. Replace it with an official or authoritative source during review.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="106">
+      <x:c r="A106" t="str">
+        <x:v>A103</x:v>
+      </x:c>
+      <x:c r="B106" t="str">
+        <x:v>Al-Hussain Mosque</x:v>
+      </x:c>
+      <x:c r="C106" t="str">
+        <x:v>Perlis</x:v>
+      </x:c>
+      <x:c r="D106" s="179" t="str">
+        <x:v>Kuala Perlis</x:v>
+      </x:c>
+      <x:c r="E106" s="179" t="str">
+        <x:v>Religious Site</x:v>
+      </x:c>
+      <x:c r="F106" s="179" t="str">
+        <x:v>mosque; architecture; religion; sunset; photography</x:v>
+      </x:c>
+      <x:c r="G106" s="179" t="str">
+        <x:v>Both</x:v>
+      </x:c>
+      <x:c r="H106" s="179" t="str">
+        <x:v>AI-generated candidate attraction in Kuala Perlis, Perlis. The place name, category, description and visitor details require source verification before production use.</x:v>
+      </x:c>
+      <x:c r="I106" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="J106"/>
+      <x:c r="K106"/>
+      <x:c r="L106"/>
+      <x:c r="M106" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="N106" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="O106" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="P106" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="Q106" s="179" t="str">
+        <x:v>Accessibility information has not been verified. Confirm terrain, steps, seating, toilets and mobility access with an official source before recommending it as elderly-friendly.</x:v>
+      </x:c>
+      <x:c r="R106"/>
+      <x:c r="S106"/>
+      <x:c r="T106" s="179"/>
+      <x:c r="U106" s="179" t="str">
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Al-Hussain%20Mosque%2C%20Perlis%2C%20Malaysia</x:v>
+      </x:c>
+      <x:c r="V106" s="184" t="n">
+        <x:v>46240</x:v>
+      </x:c>
+      <x:c r="W106" s="179" t="str">
+        <x:v>Unverified</x:v>
+      </x:c>
+      <x:c r="X106" s="185" t="n">
+        <x:f>IF(B106="","",COUNTA(B106:W106)/22)</x:f>
+        <x:v>0.7272727272727273</x:v>
+      </x:c>
+      <x:c r="Y106" s="179" t="str">
+        <x:v>Generated by ChatGPT as a candidate on 2026-08-06. The Google Maps link is for discovery only and is not a verified factual source. Replace it with an official or authoritative source during review.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="107">
+      <x:c r="A107" t="str">
+        <x:v>A104</x:v>
+      </x:c>
+      <x:c r="B107" t="str">
+        <x:v>Bukit Ayer Recreational Forest</x:v>
+      </x:c>
+      <x:c r="C107" t="str">
+        <x:v>Perlis</x:v>
+      </x:c>
+      <x:c r="D107" s="179" t="str">
+        <x:v>Sungai Batu Pahat</x:v>
+      </x:c>
+      <x:c r="E107" s="179" t="str">
+        <x:v>Nature</x:v>
+      </x:c>
+      <x:c r="F107" s="179" t="str">
+        <x:v>forest; waterfall; picnic; relaxation; family</x:v>
+      </x:c>
+      <x:c r="G107" s="179" t="str">
+        <x:v>Outdoor</x:v>
+      </x:c>
+      <x:c r="H107" s="179" t="str">
+        <x:v>AI-generated candidate attraction in Sungai Batu Pahat, Perlis. The place name, category, description and visitor details require source verification before production use.</x:v>
+      </x:c>
+      <x:c r="I107" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="J107"/>
+      <x:c r="K107"/>
+      <x:c r="L107"/>
+      <x:c r="M107" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="N107" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="O107" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="P107" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="Q107" s="179" t="str">
+        <x:v>Accessibility information has not been verified. Confirm terrain, steps, seating, toilets and mobility access with an official source before recommending it as elderly-friendly.</x:v>
+      </x:c>
+      <x:c r="R107"/>
+      <x:c r="S107"/>
+      <x:c r="T107" s="179"/>
+      <x:c r="U107" s="179" t="str">
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Bukit%20Ayer%20Recreational%20Forest%2C%20Perlis%2C%20Malaysia</x:v>
+      </x:c>
+      <x:c r="V107" s="184" t="n">
+        <x:v>46240</x:v>
+      </x:c>
+      <x:c r="W107" s="179" t="str">
+        <x:v>Unverified</x:v>
+      </x:c>
+      <x:c r="X107" s="185" t="n">
+        <x:f>IF(B107="","",COUNTA(B107:W107)/22)</x:f>
+        <x:v>0.7272727272727273</x:v>
+      </x:c>
+      <x:c r="Y107" s="179" t="str">
+        <x:v>Generated by ChatGPT as a candidate on 2026-08-06. The Google Maps link is for discovery only and is not a verified factual source. Replace it with an official or authoritative source during review.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="108">
+      <x:c r="A108" t="str">
+        <x:v>A105</x:v>
+      </x:c>
+      <x:c r="B108" t="str">
+        <x:v>Tunku Abdul Rahman Park</x:v>
+      </x:c>
+      <x:c r="C108" t="str">
+        <x:v>Sabah</x:v>
+      </x:c>
+      <x:c r="D108" s="179" t="str">
+        <x:v>Kota Kinabalu</x:v>
+      </x:c>
+      <x:c r="E108" s="179" t="str">
+        <x:v>Beach and Island</x:v>
+      </x:c>
+      <x:c r="F108" s="179" t="str">
+        <x:v>island; beach; snorkelling; relaxation; marine life</x:v>
+      </x:c>
+      <x:c r="G108" s="179" t="str">
+        <x:v>Outdoor</x:v>
+      </x:c>
+      <x:c r="H108" s="179" t="str">
+        <x:v>AI-generated candidate attraction in Kota Kinabalu, Sabah. The place name, category, description and visitor details require source verification before production use.</x:v>
+      </x:c>
+      <x:c r="I108" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="J108"/>
+      <x:c r="K108"/>
+      <x:c r="L108"/>
+      <x:c r="M108" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="N108" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="O108" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="P108" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="Q108" s="179" t="str">
+        <x:v>Accessibility information has not been verified. Confirm terrain, steps, seating, toilets and mobility access with an official source before recommending it as elderly-friendly.</x:v>
+      </x:c>
+      <x:c r="R108"/>
+      <x:c r="S108"/>
+      <x:c r="T108" s="179"/>
+      <x:c r="U108" s="179" t="str">
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Tunku%20Abdul%20Rahman%20Park%2C%20Sabah%2C%20Malaysia</x:v>
+      </x:c>
+      <x:c r="V108" s="184" t="n">
+        <x:v>46240</x:v>
+      </x:c>
+      <x:c r="W108" s="179" t="str">
+        <x:v>Unverified</x:v>
+      </x:c>
+      <x:c r="X108" s="185" t="n">
+        <x:f>IF(B108="","",COUNTA(B108:W108)/22)</x:f>
+        <x:v>0.7272727272727273</x:v>
+      </x:c>
+      <x:c r="Y108" s="179" t="str">
+        <x:v>Generated by ChatGPT as a candidate on 2026-08-06. The Google Maps link is for discovery only and is not a verified factual source. Replace it with an official or authoritative source during review.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="109">
+      <x:c r="A109" t="str">
+        <x:v>A106</x:v>
+      </x:c>
+      <x:c r="B109" t="str">
+        <x:v>Sepilok Orangutan Rehabilitation Centre</x:v>
+      </x:c>
+      <x:c r="C109" t="str">
+        <x:v>Sabah</x:v>
+      </x:c>
+      <x:c r="D109" s="179" t="str">
+        <x:v>Sandakan</x:v>
+      </x:c>
+      <x:c r="E109" s="179" t="str">
+        <x:v>Wildlife</x:v>
+      </x:c>
+      <x:c r="F109" s="179" t="str">
+        <x:v>orangutan; conservation; wildlife; education; nature</x:v>
+      </x:c>
+      <x:c r="G109" s="179" t="str">
+        <x:v>Both</x:v>
+      </x:c>
+      <x:c r="H109" s="179" t="str">
+        <x:v>AI-generated candidate attraction in Sandakan, Sabah. The place name, category, description and visitor details require source verification before production use.</x:v>
+      </x:c>
+      <x:c r="I109" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="J109"/>
+      <x:c r="K109"/>
+      <x:c r="L109"/>
+      <x:c r="M109" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="N109" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="O109" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="P109" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="Q109" s="179" t="str">
+        <x:v>Accessibility information has not been verified. Confirm terrain, steps, seating, toilets and mobility access with an official source before recommending it as elderly-friendly.</x:v>
+      </x:c>
+      <x:c r="R109"/>
+      <x:c r="S109"/>
+      <x:c r="T109" s="179"/>
+      <x:c r="U109" s="179" t="str">
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Sepilok%20Orangutan%20Rehabilitation%20Centre%2C%20Sabah%2C%20Malaysia</x:v>
+      </x:c>
+      <x:c r="V109" s="184" t="n">
+        <x:v>46240</x:v>
+      </x:c>
+      <x:c r="W109" s="179" t="str">
+        <x:v>Unverified</x:v>
+      </x:c>
+      <x:c r="X109" s="185" t="n">
+        <x:f>IF(B109="","",COUNTA(B109:W109)/22)</x:f>
+        <x:v>0.7272727272727273</x:v>
+      </x:c>
+      <x:c r="Y109" s="179" t="str">
+        <x:v>Generated by ChatGPT as a candidate on 2026-08-06. The Google Maps link is for discovery only and is not a verified factual source. Replace it with an official or authoritative source during review.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="110">
+      <x:c r="A110" t="str">
+        <x:v>A107</x:v>
+      </x:c>
+      <x:c r="B110" t="str">
+        <x:v>Sabah State Museum</x:v>
+      </x:c>
+      <x:c r="C110" t="str">
+        <x:v>Sabah</x:v>
+      </x:c>
+      <x:c r="D110" s="179" t="str">
+        <x:v>Kota Kinabalu</x:v>
+      </x:c>
+      <x:c r="E110" s="179" t="str">
+        <x:v>Museum and Gallery</x:v>
+      </x:c>
+      <x:c r="F110" s="179" t="str">
+        <x:v>museum; history; culture; heritage; indoor</x:v>
+      </x:c>
+      <x:c r="G110" s="179" t="str">
+        <x:v>Both</x:v>
+      </x:c>
+      <x:c r="H110" s="179" t="str">
+        <x:v>AI-generated candidate attraction in Kota Kinabalu, Sabah. The place name, category, description and visitor details require source verification before production use.</x:v>
+      </x:c>
+      <x:c r="I110" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="J110"/>
+      <x:c r="K110"/>
+      <x:c r="L110"/>
+      <x:c r="M110" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="N110" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="O110" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="P110" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="Q110" s="179" t="str">
+        <x:v>Accessibility information has not been verified. Confirm terrain, steps, seating, toilets and mobility access with an official source before recommending it as elderly-friendly.</x:v>
+      </x:c>
+      <x:c r="R110"/>
+      <x:c r="S110"/>
+      <x:c r="T110" s="179"/>
+      <x:c r="U110" s="179" t="str">
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Sabah%20State%20Museum%2C%20Sabah%2C%20Malaysia</x:v>
+      </x:c>
+      <x:c r="V110" s="184" t="n">
+        <x:v>46240</x:v>
+      </x:c>
+      <x:c r="W110" s="179" t="str">
+        <x:v>Unverified</x:v>
+      </x:c>
+      <x:c r="X110" s="185" t="n">
+        <x:f>IF(B110="","",COUNTA(B110:W110)/22)</x:f>
+        <x:v>0.7272727272727273</x:v>
+      </x:c>
+      <x:c r="Y110" s="179" t="str">
+        <x:v>Generated by ChatGPT as a candidate on 2026-08-06. The Google Maps link is for discovery only and is not a verified factual source. Replace it with an official or authoritative source during review.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="111">
+      <x:c r="A111" t="str">
+        <x:v>A108</x:v>
+      </x:c>
+      <x:c r="B111" t="str">
+        <x:v>Mari Mari Cultural Village</x:v>
+      </x:c>
+      <x:c r="C111" t="str">
+        <x:v>Sabah</x:v>
+      </x:c>
+      <x:c r="D111" s="179" t="str">
+        <x:v>Kota Kinabalu</x:v>
+      </x:c>
+      <x:c r="E111" s="179" t="str">
+        <x:v>Culture</x:v>
+      </x:c>
+      <x:c r="F111" s="179" t="str">
+        <x:v>indigenous culture; heritage; performance; food; education</x:v>
+      </x:c>
+      <x:c r="G111" s="179" t="str">
+        <x:v>Both</x:v>
+      </x:c>
+      <x:c r="H111" s="179" t="str">
+        <x:v>AI-generated candidate attraction in Kota Kinabalu, Sabah. The place name, category, description and visitor details require source verification before production use.</x:v>
+      </x:c>
+      <x:c r="I111" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="J111"/>
+      <x:c r="K111"/>
+      <x:c r="L111"/>
+      <x:c r="M111" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="N111" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="O111" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="P111" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="Q111" s="179" t="str">
+        <x:v>Accessibility information has not been verified. Confirm terrain, steps, seating, toilets and mobility access with an official source before recommending it as elderly-friendly.</x:v>
+      </x:c>
+      <x:c r="R111"/>
+      <x:c r="S111"/>
+      <x:c r="T111" s="179"/>
+      <x:c r="U111" s="179" t="str">
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Mari%20Mari%20Cultural%20Village%2C%20Sabah%2C%20Malaysia</x:v>
+      </x:c>
+      <x:c r="V111" s="184" t="n">
+        <x:v>46240</x:v>
+      </x:c>
+      <x:c r="W111" s="179" t="str">
+        <x:v>Unverified</x:v>
+      </x:c>
+      <x:c r="X111" s="185" t="n">
+        <x:f>IF(B111="","",COUNTA(B111:W111)/22)</x:f>
+        <x:v>0.7272727272727273</x:v>
+      </x:c>
+      <x:c r="Y111" s="179" t="str">
+        <x:v>Generated by ChatGPT as a candidate on 2026-08-06. The Google Maps link is for discovery only and is not a verified factual source. Replace it with an official or authoritative source during review.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="112">
+      <x:c r="A112" t="str">
+        <x:v>A109</x:v>
+      </x:c>
+      <x:c r="B112" t="str">
+        <x:v>Poring Hot Spring</x:v>
+      </x:c>
+      <x:c r="C112" t="str">
+        <x:v>Sabah</x:v>
+      </x:c>
+      <x:c r="D112" s="179" t="str">
+        <x:v>Ranau</x:v>
+      </x:c>
+      <x:c r="E112" s="179" t="str">
+        <x:v>Wellness and Relaxation</x:v>
+      </x:c>
+      <x:c r="F112" s="179" t="str">
+        <x:v>hot springs; relaxation; nature; canopy walk; wellness</x:v>
+      </x:c>
+      <x:c r="G112" s="179" t="str">
+        <x:v>Outdoor</x:v>
+      </x:c>
+      <x:c r="H112" s="179" t="str">
+        <x:v>AI-generated candidate attraction in Ranau, Sabah. The place name, category, description and visitor details require source verification before production use.</x:v>
+      </x:c>
+      <x:c r="I112" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="J112"/>
+      <x:c r="K112"/>
+      <x:c r="L112"/>
+      <x:c r="M112" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="N112" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="O112" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="P112" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="Q112" s="179" t="str">
+        <x:v>Accessibility information has not been verified. Confirm terrain, steps, seating, toilets and mobility access with an official source before recommending it as elderly-friendly.</x:v>
+      </x:c>
+      <x:c r="R112"/>
+      <x:c r="S112"/>
+      <x:c r="T112" s="179"/>
+      <x:c r="U112" s="179" t="str">
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Poring%20Hot%20Spring%2C%20Sabah%2C%20Malaysia</x:v>
+      </x:c>
+      <x:c r="V112" s="184" t="n">
+        <x:v>46240</x:v>
+      </x:c>
+      <x:c r="W112" s="179" t="str">
+        <x:v>Unverified</x:v>
+      </x:c>
+      <x:c r="X112" s="185" t="n">
+        <x:f>IF(B112="","",COUNTA(B112:W112)/22)</x:f>
+        <x:v>0.7272727272727273</x:v>
+      </x:c>
+      <x:c r="Y112" s="179" t="str">
+        <x:v>Generated by ChatGPT as a candidate on 2026-08-06. The Google Maps link is for discovery only and is not a verified factual source. Replace it with an official or authoritative source during review.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="113">
+      <x:c r="A113" t="str">
+        <x:v>A110</x:v>
+      </x:c>
+      <x:c r="B113" t="str">
+        <x:v>Danum Valley Conservation Area</x:v>
+      </x:c>
+      <x:c r="C113" t="str">
+        <x:v>Sabah</x:v>
+      </x:c>
+      <x:c r="D113" s="179" t="str">
+        <x:v>Lahad Datu</x:v>
+      </x:c>
+      <x:c r="E113" s="179" t="str">
+        <x:v>Nature</x:v>
+      </x:c>
+      <x:c r="F113" s="179" t="str">
+        <x:v>rainforest; wildlife; conservation; hiking; nature</x:v>
+      </x:c>
+      <x:c r="G113" s="179" t="str">
+        <x:v>Outdoor</x:v>
+      </x:c>
+      <x:c r="H113" s="179" t="str">
+        <x:v>AI-generated candidate attraction in Lahad Datu, Sabah. The place name, category, description and visitor details require source verification before production use.</x:v>
+      </x:c>
+      <x:c r="I113" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="J113"/>
+      <x:c r="K113"/>
+      <x:c r="L113"/>
+      <x:c r="M113" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="N113" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="O113" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="P113" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="Q113" s="179" t="str">
+        <x:v>Accessibility information has not been verified. Confirm terrain, steps, seating, toilets and mobility access with an official source before recommending it as elderly-friendly.</x:v>
+      </x:c>
+      <x:c r="R113"/>
+      <x:c r="S113"/>
+      <x:c r="T113" s="179"/>
+      <x:c r="U113" s="179" t="str">
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Danum%20Valley%20Conservation%20Area%2C%20Sabah%2C%20Malaysia</x:v>
+      </x:c>
+      <x:c r="V113" s="184" t="n">
+        <x:v>46240</x:v>
+      </x:c>
+      <x:c r="W113" s="179" t="str">
+        <x:v>Unverified</x:v>
+      </x:c>
+      <x:c r="X113" s="185" t="n">
+        <x:f>IF(B113="","",COUNTA(B113:W113)/22)</x:f>
+        <x:v>0.7272727272727273</x:v>
+      </x:c>
+      <x:c r="Y113" s="179" t="str">
+        <x:v>Generated by ChatGPT as a candidate on 2026-08-06. The Google Maps link is for discovery only and is not a verified factual source. Replace it with an official or authoritative source during review.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="114">
+      <x:c r="A114" t="str">
+        <x:v>A111</x:v>
+      </x:c>
+      <x:c r="B114" t="str">
+        <x:v>Tip of Borneo</x:v>
+      </x:c>
+      <x:c r="C114" t="str">
+        <x:v>Sabah</x:v>
+      </x:c>
+      <x:c r="D114" s="179" t="str">
+        <x:v>Kudat</x:v>
+      </x:c>
+      <x:c r="E114" s="179" t="str">
+        <x:v>Nature</x:v>
+      </x:c>
+      <x:c r="F114" s="179" t="str">
+        <x:v>coast; scenery; sunset; photography; relaxation</x:v>
+      </x:c>
+      <x:c r="G114" s="179" t="str">
+        <x:v>Outdoor</x:v>
+      </x:c>
+      <x:c r="H114" s="179" t="str">
+        <x:v>AI-generated candidate attraction in Kudat, Sabah. The place name, category, description and visitor details require source verification before production use.</x:v>
+      </x:c>
+      <x:c r="I114" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="J114"/>
+      <x:c r="K114"/>
+      <x:c r="L114"/>
+      <x:c r="M114" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="N114" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="O114" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="P114" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="Q114" s="179" t="str">
+        <x:v>Accessibility information has not been verified. Confirm terrain, steps, seating, toilets and mobility access with an official source before recommending it as elderly-friendly.</x:v>
+      </x:c>
+      <x:c r="R114"/>
+      <x:c r="S114"/>
+      <x:c r="T114" s="179"/>
+      <x:c r="U114" s="179" t="str">
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Tip%20of%20Borneo%2C%20Sabah%2C%20Malaysia</x:v>
+      </x:c>
+      <x:c r="V114" s="184" t="n">
+        <x:v>46240</x:v>
+      </x:c>
+      <x:c r="W114" s="179" t="str">
+        <x:v>Unverified</x:v>
+      </x:c>
+      <x:c r="X114" s="185" t="n">
+        <x:f>IF(B114="","",COUNTA(B114:W114)/22)</x:f>
+        <x:v>0.7272727272727273</x:v>
+      </x:c>
+      <x:c r="Y114" s="179" t="str">
+        <x:v>Generated by ChatGPT as a candidate on 2026-08-06. The Google Maps link is for discovery only and is not a verified factual source. Replace it with an official or authoritative source during review.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="115">
+      <x:c r="A115" t="str">
+        <x:v>A112</x:v>
+      </x:c>
+      <x:c r="B115" t="str">
+        <x:v>Lok Kawi Wildlife Park</x:v>
+      </x:c>
+      <x:c r="C115" t="str">
+        <x:v>Sabah</x:v>
+      </x:c>
+      <x:c r="D115" s="179" t="str">
+        <x:v>Penampang</x:v>
+      </x:c>
+      <x:c r="E115" s="179" t="str">
+        <x:v>Wildlife</x:v>
+      </x:c>
+      <x:c r="F115" s="179" t="str">
+        <x:v>wildlife; animals; family; children; education</x:v>
+      </x:c>
+      <x:c r="G115" s="179" t="str">
+        <x:v>Outdoor</x:v>
+      </x:c>
+      <x:c r="H115" s="179" t="str">
+        <x:v>AI-generated candidate attraction in Penampang, Sabah. The place name, category, description and visitor details require source verification before production use.</x:v>
+      </x:c>
+      <x:c r="I115" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="J115"/>
+      <x:c r="K115"/>
+      <x:c r="L115"/>
+      <x:c r="M115" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="N115" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="O115" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="P115" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="Q115" s="179" t="str">
+        <x:v>Accessibility information has not been verified. Confirm terrain, steps, seating, toilets and mobility access with an official source before recommending it as elderly-friendly.</x:v>
+      </x:c>
+      <x:c r="R115"/>
+      <x:c r="S115"/>
+      <x:c r="T115" s="179"/>
+      <x:c r="U115" s="179" t="str">
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Lok%20Kawi%20Wildlife%20Park%2C%20Sabah%2C%20Malaysia</x:v>
+      </x:c>
+      <x:c r="V115" s="184" t="n">
+        <x:v>46240</x:v>
+      </x:c>
+      <x:c r="W115" s="179" t="str">
+        <x:v>Unverified</x:v>
+      </x:c>
+      <x:c r="X115" s="185" t="n">
+        <x:f>IF(B115="","",COUNTA(B115:W115)/22)</x:f>
+        <x:v>0.7272727272727273</x:v>
+      </x:c>
+      <x:c r="Y115" s="179" t="str">
+        <x:v>Generated by ChatGPT as a candidate on 2026-08-06. The Google Maps link is for discovery only and is not a verified factual source. Replace it with an official or authoritative source during review.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="116">
+      <x:c r="A116" t="str">
+        <x:v>A113</x:v>
+      </x:c>
+      <x:c r="B116" t="str">
+        <x:v>Sarawak Cultural Village</x:v>
+      </x:c>
+      <x:c r="C116" t="str">
+        <x:v>Sarawak</x:v>
+      </x:c>
+      <x:c r="D116" s="179" t="str">
+        <x:v>Kuching</x:v>
+      </x:c>
+      <x:c r="E116" s="179" t="str">
+        <x:v>Culture</x:v>
+      </x:c>
+      <x:c r="F116" s="179" t="str">
+        <x:v>culture; indigenous heritage; performance; family; education</x:v>
+      </x:c>
+      <x:c r="G116" s="179" t="str">
+        <x:v>Both</x:v>
+      </x:c>
+      <x:c r="H116" s="179" t="str">
+        <x:v>AI-generated candidate attraction in Kuching, Sarawak. The place name, category, description and visitor details require source verification before production use.</x:v>
+      </x:c>
+      <x:c r="I116" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="J116"/>
+      <x:c r="K116"/>
+      <x:c r="L116"/>
+      <x:c r="M116" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="N116" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="O116" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="P116" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="Q116" s="179" t="str">
+        <x:v>Accessibility information has not been verified. Confirm terrain, steps, seating, toilets and mobility access with an official source before recommending it as elderly-friendly.</x:v>
+      </x:c>
+      <x:c r="R116"/>
+      <x:c r="S116"/>
+      <x:c r="T116" s="179"/>
+      <x:c r="U116" s="179" t="str">
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Sarawak%20Cultural%20Village%2C%20Sarawak%2C%20Malaysia</x:v>
+      </x:c>
+      <x:c r="V116" s="184" t="n">
+        <x:v>46240</x:v>
+      </x:c>
+      <x:c r="W116" s="179" t="str">
+        <x:v>Unverified</x:v>
+      </x:c>
+      <x:c r="X116" s="185" t="n">
+        <x:f>IF(B116="","",COUNTA(B116:W116)/22)</x:f>
+        <x:v>0.7272727272727273</x:v>
+      </x:c>
+      <x:c r="Y116" s="179" t="str">
+        <x:v>Generated by ChatGPT as a candidate on 2026-08-06. The Google Maps link is for discovery only and is not a verified factual source. Replace it with an official or authoritative source during review.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="117">
+      <x:c r="A117" t="str">
+        <x:v>A114</x:v>
+      </x:c>
+      <x:c r="B117" t="str">
+        <x:v>Semenggoh Wildlife Centre</x:v>
+      </x:c>
+      <x:c r="C117" t="str">
+        <x:v>Sarawak</x:v>
+      </x:c>
+      <x:c r="D117" s="179" t="str">
+        <x:v>Kuching</x:v>
+      </x:c>
+      <x:c r="E117" s="179" t="str">
+        <x:v>Wildlife</x:v>
+      </x:c>
+      <x:c r="F117" s="179" t="str">
+        <x:v>orangutan; conservation; wildlife; nature; education</x:v>
+      </x:c>
+      <x:c r="G117" s="179" t="str">
+        <x:v>Outdoor</x:v>
+      </x:c>
+      <x:c r="H117" s="179" t="str">
+        <x:v>AI-generated candidate attraction in Kuching, Sarawak. The place name, category, description and visitor details require source verification before production use.</x:v>
+      </x:c>
+      <x:c r="I117" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="J117"/>
+      <x:c r="K117"/>
+      <x:c r="L117"/>
+      <x:c r="M117" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="N117" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="O117" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="P117" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="Q117" s="179" t="str">
+        <x:v>Accessibility information has not been verified. Confirm terrain, steps, seating, toilets and mobility access with an official source before recommending it as elderly-friendly.</x:v>
+      </x:c>
+      <x:c r="R117"/>
+      <x:c r="S117"/>
+      <x:c r="T117" s="179"/>
+      <x:c r="U117" s="179" t="str">
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Semenggoh%20Wildlife%20Centre%2C%20Sarawak%2C%20Malaysia</x:v>
+      </x:c>
+      <x:c r="V117" s="184" t="n">
+        <x:v>46240</x:v>
+      </x:c>
+      <x:c r="W117" s="179" t="str">
+        <x:v>Unverified</x:v>
+      </x:c>
+      <x:c r="X117" s="185" t="n">
+        <x:f>IF(B117="","",COUNTA(B117:W117)/22)</x:f>
+        <x:v>0.7272727272727273</x:v>
+      </x:c>
+      <x:c r="Y117" s="179" t="str">
+        <x:v>Generated by ChatGPT as a candidate on 2026-08-06. The Google Maps link is for discovery only and is not a verified factual source. Replace it with an official or authoritative source during review.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="118">
+      <x:c r="A118" t="str">
+        <x:v>A115</x:v>
+      </x:c>
+      <x:c r="B118" t="str">
+        <x:v>Kuching Waterfront</x:v>
+      </x:c>
+      <x:c r="C118" t="str">
+        <x:v>Sarawak</x:v>
+      </x:c>
+      <x:c r="D118" s="179" t="str">
+        <x:v>Kuching</x:v>
+      </x:c>
+      <x:c r="E118" s="179" t="str">
+        <x:v>Urban Attraction</x:v>
+      </x:c>
+      <x:c r="F118" s="179" t="str">
+        <x:v>waterfront; walking; relaxation; food; heritage</x:v>
+      </x:c>
+      <x:c r="G118" s="179" t="str">
+        <x:v>Outdoor</x:v>
+      </x:c>
+      <x:c r="H118" s="179" t="str">
+        <x:v>AI-generated candidate attraction in Kuching, Sarawak. The place name, category, description and visitor details require source verification before production use.</x:v>
+      </x:c>
+      <x:c r="I118" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="J118"/>
+      <x:c r="K118"/>
+      <x:c r="L118"/>
+      <x:c r="M118" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="N118" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="O118" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="P118" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="Q118" s="179" t="str">
+        <x:v>Accessibility information has not been verified. Confirm terrain, steps, seating, toilets and mobility access with an official source before recommending it as elderly-friendly.</x:v>
+      </x:c>
+      <x:c r="R118"/>
+      <x:c r="S118"/>
+      <x:c r="T118" s="179"/>
+      <x:c r="U118" s="179" t="str">
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Kuching%20Waterfront%2C%20Sarawak%2C%20Malaysia</x:v>
+      </x:c>
+      <x:c r="V118" s="184" t="n">
+        <x:v>46240</x:v>
+      </x:c>
+      <x:c r="W118" s="179" t="str">
+        <x:v>Unverified</x:v>
+      </x:c>
+      <x:c r="X118" s="185" t="n">
+        <x:f>IF(B118="","",COUNTA(B118:W118)/22)</x:f>
+        <x:v>0.7272727272727273</x:v>
+      </x:c>
+      <x:c r="Y118" s="179" t="str">
+        <x:v>Generated by ChatGPT as a candidate on 2026-08-06. The Google Maps link is for discovery only and is not a verified factual source. Replace it with an official or authoritative source during review.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="119">
+      <x:c r="A119" t="str">
+        <x:v>A116</x:v>
+      </x:c>
+      <x:c r="B119" t="str">
+        <x:v>Fort Margherita</x:v>
+      </x:c>
+      <x:c r="C119" t="str">
+        <x:v>Sarawak</x:v>
+      </x:c>
+      <x:c r="D119" s="179" t="str">
+        <x:v>Kuching</x:v>
+      </x:c>
+      <x:c r="E119" s="179" t="str">
+        <x:v>Heritage and History</x:v>
+      </x:c>
+      <x:c r="F119" s="179" t="str">
+        <x:v>fort; history; museum; heritage; architecture</x:v>
+      </x:c>
+      <x:c r="G119" s="179" t="str">
+        <x:v>Both</x:v>
+      </x:c>
+      <x:c r="H119" s="179" t="str">
+        <x:v>AI-generated candidate attraction in Kuching, Sarawak. The place name, category, description and visitor details require source verification before production use.</x:v>
+      </x:c>
+      <x:c r="I119" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="J119"/>
+      <x:c r="K119"/>
+      <x:c r="L119"/>
+      <x:c r="M119" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="N119" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="O119" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="P119" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="Q119" s="179" t="str">
+        <x:v>Accessibility information has not been verified. Confirm terrain, steps, seating, toilets and mobility access with an official source before recommending it as elderly-friendly.</x:v>
+      </x:c>
+      <x:c r="R119"/>
+      <x:c r="S119"/>
+      <x:c r="T119" s="179"/>
+      <x:c r="U119" s="179" t="str">
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Fort%20Margherita%2C%20Sarawak%2C%20Malaysia</x:v>
+      </x:c>
+      <x:c r="V119" s="184" t="n">
+        <x:v>46240</x:v>
+      </x:c>
+      <x:c r="W119" s="179" t="str">
+        <x:v>Unverified</x:v>
+      </x:c>
+      <x:c r="X119" s="185" t="n">
+        <x:f>IF(B119="","",COUNTA(B119:W119)/22)</x:f>
+        <x:v>0.7272727272727273</x:v>
+      </x:c>
+      <x:c r="Y119" s="179" t="str">
+        <x:v>Generated by ChatGPT as a candidate on 2026-08-06. The Google Maps link is for discovery only and is not a verified factual source. Replace it with an official or authoritative source during review.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="120">
+      <x:c r="A120" t="str">
+        <x:v>A117</x:v>
+      </x:c>
+      <x:c r="B120" t="str">
+        <x:v>Niah National Park</x:v>
+      </x:c>
+      <x:c r="C120" t="str">
+        <x:v>Sarawak</x:v>
+      </x:c>
+      <x:c r="D120" s="179" t="str">
+        <x:v>Miri</x:v>
+      </x:c>
+      <x:c r="E120" s="179" t="str">
+        <x:v>Adventure</x:v>
+      </x:c>
+      <x:c r="F120" s="179" t="str">
+        <x:v>cave; archaeology; hiking; rainforest; heritage</x:v>
+      </x:c>
+      <x:c r="G120" s="179" t="str">
+        <x:v>Outdoor</x:v>
+      </x:c>
+      <x:c r="H120" s="179" t="str">
+        <x:v>AI-generated candidate attraction in Miri, Sarawak. The place name, category, description and visitor details require source verification before production use.</x:v>
+      </x:c>
+      <x:c r="I120" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="J120"/>
+      <x:c r="K120"/>
+      <x:c r="L120"/>
+      <x:c r="M120" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="N120" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="O120" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="P120" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="Q120" s="179" t="str">
+        <x:v>Accessibility information has not been verified. Confirm terrain, steps, seating, toilets and mobility access with an official source before recommending it as elderly-friendly.</x:v>
+      </x:c>
+      <x:c r="R120"/>
+      <x:c r="S120"/>
+      <x:c r="T120" s="179"/>
+      <x:c r="U120" s="179" t="str">
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Niah%20National%20Park%2C%20Sarawak%2C%20Malaysia</x:v>
+      </x:c>
+      <x:c r="V120" s="184" t="n">
+        <x:v>46240</x:v>
+      </x:c>
+      <x:c r="W120" s="179" t="str">
+        <x:v>Unverified</x:v>
+      </x:c>
+      <x:c r="X120" s="185" t="n">
+        <x:f>IF(B120="","",COUNTA(B120:W120)/22)</x:f>
+        <x:v>0.7272727272727273</x:v>
+      </x:c>
+      <x:c r="Y120" s="179" t="str">
+        <x:v>Generated by ChatGPT as a candidate on 2026-08-06. The Google Maps link is for discovery only and is not a verified factual source. Replace it with an official or authoritative source during review.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="121">
+      <x:c r="A121" t="str">
+        <x:v>A118</x:v>
+      </x:c>
+      <x:c r="B121" t="str">
+        <x:v>Kubah National Park</x:v>
+      </x:c>
+      <x:c r="C121" t="str">
+        <x:v>Sarawak</x:v>
+      </x:c>
+      <x:c r="D121" s="179" t="str">
+        <x:v>Kuching</x:v>
+      </x:c>
+      <x:c r="E121" s="179" t="str">
+        <x:v>Nature</x:v>
+      </x:c>
+      <x:c r="F121" s="179" t="str">
+        <x:v>rainforest; hiking; waterfall; wildlife; nature</x:v>
+      </x:c>
+      <x:c r="G121" s="179" t="str">
+        <x:v>Outdoor</x:v>
+      </x:c>
+      <x:c r="H121" s="179" t="str">
+        <x:v>AI-generated candidate attraction in Kuching, Sarawak. The place name, category, description and visitor details require source verification before production use.</x:v>
+      </x:c>
+      <x:c r="I121" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="J121"/>
+      <x:c r="K121"/>
+      <x:c r="L121"/>
+      <x:c r="M121" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="N121" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="O121" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="P121" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="Q121" s="179" t="str">
+        <x:v>Accessibility information has not been verified. Confirm terrain, steps, seating, toilets and mobility access with an official source before recommending it as elderly-friendly.</x:v>
+      </x:c>
+      <x:c r="R121"/>
+      <x:c r="S121"/>
+      <x:c r="T121" s="179"/>
+      <x:c r="U121" s="179" t="str">
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Kubah%20National%20Park%2C%20Sarawak%2C%20Malaysia</x:v>
+      </x:c>
+      <x:c r="V121" s="184" t="n">
+        <x:v>46240</x:v>
+      </x:c>
+      <x:c r="W121" s="179" t="str">
+        <x:v>Unverified</x:v>
+      </x:c>
+      <x:c r="X121" s="185" t="n">
+        <x:f>IF(B121="","",COUNTA(B121:W121)/22)</x:f>
+        <x:v>0.7272727272727273</x:v>
+      </x:c>
+      <x:c r="Y121" s="179" t="str">
+        <x:v>Generated by ChatGPT as a candidate on 2026-08-06. The Google Maps link is for discovery only and is not a verified factual source. Replace it with an official or authoritative source during review.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="122">
+      <x:c r="A122" t="str">
+        <x:v>A119</x:v>
+      </x:c>
+      <x:c r="B122" t="str">
+        <x:v>Fairy Cave</x:v>
+      </x:c>
+      <x:c r="C122" t="str">
+        <x:v>Sarawak</x:v>
+      </x:c>
+      <x:c r="D122" s="179" t="str">
+        <x:v>Bau</x:v>
+      </x:c>
+      <x:c r="E122" s="179" t="str">
+        <x:v>Adventure</x:v>
+      </x:c>
+      <x:c r="F122" s="179" t="str">
+        <x:v>cave; limestone; hiking; nature; photography</x:v>
+      </x:c>
+      <x:c r="G122" s="179" t="str">
+        <x:v>Outdoor</x:v>
+      </x:c>
+      <x:c r="H122" s="179" t="str">
+        <x:v>AI-generated candidate attraction in Bau, Sarawak. The place name, category, description and visitor details require source verification before production use.</x:v>
+      </x:c>
+      <x:c r="I122" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="J122"/>
+      <x:c r="K122"/>
+      <x:c r="L122"/>
+      <x:c r="M122" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="N122" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="O122" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="P122" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="Q122" s="179" t="str">
+        <x:v>Accessibility information has not been verified. Confirm terrain, steps, seating, toilets and mobility access with an official source before recommending it as elderly-friendly.</x:v>
+      </x:c>
+      <x:c r="R122"/>
+      <x:c r="S122"/>
+      <x:c r="T122" s="179"/>
+      <x:c r="U122" s="179" t="str">
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Fairy%20Cave%2C%20Sarawak%2C%20Malaysia</x:v>
+      </x:c>
+      <x:c r="V122" s="184" t="n">
+        <x:v>46240</x:v>
+      </x:c>
+      <x:c r="W122" s="179" t="str">
+        <x:v>Unverified</x:v>
+      </x:c>
+      <x:c r="X122" s="185" t="n">
+        <x:f>IF(B122="","",COUNTA(B122:W122)/22)</x:f>
+        <x:v>0.7272727272727273</x:v>
+      </x:c>
+      <x:c r="Y122" s="179" t="str">
+        <x:v>Generated by ChatGPT as a candidate on 2026-08-06. The Google Maps link is for discovery only and is not a verified factual source. Replace it with an official or authoritative source during review.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="123">
+      <x:c r="A123" t="str">
+        <x:v>A120</x:v>
+      </x:c>
+      <x:c r="B123" t="str">
+        <x:v>Cat Museum</x:v>
+      </x:c>
+      <x:c r="C123" t="str">
+        <x:v>Sarawak</x:v>
+      </x:c>
+      <x:c r="D123" s="179" t="str">
+        <x:v>Kuching</x:v>
+      </x:c>
+      <x:c r="E123" s="179" t="str">
+        <x:v>Museum and Gallery</x:v>
+      </x:c>
+      <x:c r="F123" s="179" t="str">
+        <x:v>museum; cats; family; culture; indoor</x:v>
+      </x:c>
+      <x:c r="G123" s="179" t="str">
+        <x:v>Indoor</x:v>
+      </x:c>
+      <x:c r="H123" s="179" t="str">
+        <x:v>AI-generated candidate attraction in Kuching, Sarawak. The place name, category, description and visitor details require source verification before production use.</x:v>
+      </x:c>
+      <x:c r="I123" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="J123"/>
+      <x:c r="K123"/>
+      <x:c r="L123"/>
+      <x:c r="M123" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="N123" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="O123" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="P123" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="Q123" s="179" t="str">
+        <x:v>Accessibility information has not been verified. Confirm terrain, steps, seating, toilets and mobility access with an official source before recommending it as elderly-friendly.</x:v>
+      </x:c>
+      <x:c r="R123"/>
+      <x:c r="S123"/>
+      <x:c r="T123" s="179"/>
+      <x:c r="U123" s="179" t="str">
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Cat%20Museum%2C%20Sarawak%2C%20Malaysia</x:v>
+      </x:c>
+      <x:c r="V123" s="184" t="n">
+        <x:v>46240</x:v>
+      </x:c>
+      <x:c r="W123" s="179" t="str">
+        <x:v>Unverified</x:v>
+      </x:c>
+      <x:c r="X123" s="185" t="n">
+        <x:f>IF(B123="","",COUNTA(B123:W123)/22)</x:f>
+        <x:v>0.7272727272727273</x:v>
+      </x:c>
+      <x:c r="Y123" s="179" t="str">
+        <x:v>Generated by ChatGPT as a candidate on 2026-08-06. The Google Maps link is for discovery only and is not a verified factual source. Replace it with an official or authoritative source during review.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="124">
+      <x:c r="A124" t="str">
+        <x:v>A121</x:v>
+      </x:c>
+      <x:c r="B124" t="str">
+        <x:v>i-City Theme Park</x:v>
+      </x:c>
+      <x:c r="C124" t="str">
+        <x:v>Selangor</x:v>
+      </x:c>
+      <x:c r="D124" s="179" t="str">
+        <x:v>Shah Alam</x:v>
+      </x:c>
+      <x:c r="E124" s="179" t="str">
+        <x:v>Theme Park</x:v>
+      </x:c>
+      <x:c r="F124" s="179" t="str">
+        <x:v>theme park; lights; family; children; night activity</x:v>
+      </x:c>
+      <x:c r="G124" s="179" t="str">
+        <x:v>Both</x:v>
+      </x:c>
+      <x:c r="H124" s="179" t="str">
+        <x:v>AI-generated candidate attraction in Shah Alam, Selangor. The place name, category, description and visitor details require source verification before production use.</x:v>
+      </x:c>
+      <x:c r="I124" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="J124"/>
+      <x:c r="K124"/>
+      <x:c r="L124"/>
+      <x:c r="M124" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="N124" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="O124" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="P124" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="Q124" s="179" t="str">
+        <x:v>Accessibility information has not been verified. Confirm terrain, steps, seating, toilets and mobility access with an official source before recommending it as elderly-friendly.</x:v>
+      </x:c>
+      <x:c r="R124"/>
+      <x:c r="S124"/>
+      <x:c r="T124" s="179"/>
+      <x:c r="U124" s="179" t="str">
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=i-City%20Theme%20Park%2C%20Selangor%2C%20Malaysia</x:v>
+      </x:c>
+      <x:c r="V124" s="184" t="n">
+        <x:v>46240</x:v>
+      </x:c>
+      <x:c r="W124" s="179" t="str">
+        <x:v>Unverified</x:v>
+      </x:c>
+      <x:c r="X124" s="185" t="n">
+        <x:f>IF(B124="","",COUNTA(B124:W124)/22)</x:f>
+        <x:v>0.7272727272727273</x:v>
+      </x:c>
+      <x:c r="Y124" s="179" t="str">
+        <x:v>Generated by ChatGPT as a candidate on 2026-08-06. The Google Maps link is for discovery only and is not a verified factual source. Replace it with an official or authoritative source during review.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="125">
+      <x:c r="A125" t="str">
+        <x:v>A122</x:v>
+      </x:c>
+      <x:c r="B125" t="str">
+        <x:v>Sky Mirror Kuala Selangor</x:v>
+      </x:c>
+      <x:c r="C125" t="str">
+        <x:v>Selangor</x:v>
+      </x:c>
+      <x:c r="D125" s="179" t="str">
+        <x:v>Kuala Selangor</x:v>
+      </x:c>
+      <x:c r="E125" s="179" t="str">
+        <x:v>Nature</x:v>
+      </x:c>
+      <x:c r="F125" s="179" t="str">
+        <x:v>sandbank; photography; boat trip; nature; scenery</x:v>
+      </x:c>
+      <x:c r="G125" s="179" t="str">
+        <x:v>Outdoor</x:v>
+      </x:c>
+      <x:c r="H125" s="179" t="str">
+        <x:v>AI-generated candidate attraction in Kuala Selangor, Selangor. The place name, category, description and visitor details require source verification before production use.</x:v>
+      </x:c>
+      <x:c r="I125" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="J125"/>
+      <x:c r="K125"/>
+      <x:c r="L125"/>
+      <x:c r="M125" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="N125" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="O125" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="P125" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="Q125" s="179" t="str">
+        <x:v>Accessibility information has not been verified. Confirm terrain, steps, seating, toilets and mobility access with an official source before recommending it as elderly-friendly.</x:v>
+      </x:c>
+      <x:c r="R125"/>
+      <x:c r="S125"/>
+      <x:c r="T125" s="179"/>
+      <x:c r="U125" s="179" t="str">
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Sky%20Mirror%20Kuala%20Selangor%2C%20Selangor%2C%20Malaysia</x:v>
+      </x:c>
+      <x:c r="V125" s="184" t="n">
+        <x:v>46240</x:v>
+      </x:c>
+      <x:c r="W125" s="179" t="str">
+        <x:v>Unverified</x:v>
+      </x:c>
+      <x:c r="X125" s="185" t="n">
+        <x:f>IF(B125="","",COUNTA(B125:W125)/22)</x:f>
+        <x:v>0.7272727272727273</x:v>
+      </x:c>
+      <x:c r="Y125" s="179" t="str">
+        <x:v>Generated by ChatGPT as a candidate on 2026-08-06. The Google Maps link is for discovery only and is not a verified factual source. Replace it with an official or authoritative source during review.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="126">
+      <x:c r="A126" t="str">
+        <x:v>A123</x:v>
+      </x:c>
+      <x:c r="B126" t="str">
+        <x:v>Kuala Selangor Nature Park</x:v>
+      </x:c>
+      <x:c r="C126" t="str">
+        <x:v>Selangor</x:v>
+      </x:c>
+      <x:c r="D126" s="179" t="str">
+        <x:v>Kuala Selangor</x:v>
+      </x:c>
+      <x:c r="E126" s="179" t="str">
+        <x:v>Nature</x:v>
+      </x:c>
+      <x:c r="F126" s="179" t="str">
+        <x:v>mangrove; birdwatching; walking; wildlife; relaxation</x:v>
+      </x:c>
+      <x:c r="G126" s="179" t="str">
+        <x:v>Outdoor</x:v>
+      </x:c>
+      <x:c r="H126" s="179" t="str">
+        <x:v>AI-generated candidate attraction in Kuala Selangor, Selangor. The place name, category, description and visitor details require source verification before production use.</x:v>
+      </x:c>
+      <x:c r="I126" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="J126"/>
+      <x:c r="K126"/>
+      <x:c r="L126"/>
+      <x:c r="M126" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="N126" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="O126" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="P126" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="Q126" s="179" t="str">
+        <x:v>Accessibility information has not been verified. Confirm terrain, steps, seating, toilets and mobility access with an official source before recommending it as elderly-friendly.</x:v>
+      </x:c>
+      <x:c r="R126"/>
+      <x:c r="S126"/>
+      <x:c r="T126" s="179"/>
+      <x:c r="U126" s="179" t="str">
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Kuala%20Selangor%20Nature%20Park%2C%20Selangor%2C%20Malaysia</x:v>
+      </x:c>
+      <x:c r="V126" s="184" t="n">
+        <x:v>46240</x:v>
+      </x:c>
+      <x:c r="W126" s="179" t="str">
+        <x:v>Unverified</x:v>
+      </x:c>
+      <x:c r="X126" s="185" t="n">
+        <x:f>IF(B126="","",COUNTA(B126:W126)/22)</x:f>
+        <x:v>0.7272727272727273</x:v>
+      </x:c>
+      <x:c r="Y126" s="179" t="str">
+        <x:v>Generated by ChatGPT as a candidate on 2026-08-06. The Google Maps link is for discovery only and is not a verified factual source. Replace it with an official or authoritative source during review.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="127">
+      <x:c r="A127" t="str">
+        <x:v>A124</x:v>
+      </x:c>
+      <x:c r="B127" t="str">
+        <x:v>Sekinchan Paddy Fields</x:v>
+      </x:c>
+      <x:c r="C127" t="str">
+        <x:v>Selangor</x:v>
+      </x:c>
+      <x:c r="D127" s="179" t="str">
+        <x:v>Sekinchan</x:v>
+      </x:c>
+      <x:c r="E127" s="179" t="str">
+        <x:v>Nature</x:v>
+      </x:c>
+      <x:c r="F127" s="179" t="str">
+        <x:v>paddy fields; scenery; photography; rural culture; relaxation</x:v>
+      </x:c>
+      <x:c r="G127" s="179" t="str">
+        <x:v>Outdoor</x:v>
+      </x:c>
+      <x:c r="H127" s="179" t="str">
+        <x:v>AI-generated candidate attraction in Sekinchan, Selangor. The place name, category, description and visitor details require source verification before production use.</x:v>
+      </x:c>
+      <x:c r="I127" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="J127"/>
+      <x:c r="K127"/>
+      <x:c r="L127"/>
+      <x:c r="M127" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="N127" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="O127" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="P127" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="Q127" s="179" t="str">
+        <x:v>Accessibility information has not been verified. Confirm terrain, steps, seating, toilets and mobility access with an official source before recommending it as elderly-friendly.</x:v>
+      </x:c>
+      <x:c r="R127"/>
+      <x:c r="S127"/>
+      <x:c r="T127" s="179"/>
+      <x:c r="U127" s="179" t="str">
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Sekinchan%20Paddy%20Fields%2C%20Selangor%2C%20Malaysia</x:v>
+      </x:c>
+      <x:c r="V127" s="184" t="n">
+        <x:v>46240</x:v>
+      </x:c>
+      <x:c r="W127" s="179" t="str">
+        <x:v>Unverified</x:v>
+      </x:c>
+      <x:c r="X127" s="185" t="n">
+        <x:f>IF(B127="","",COUNTA(B127:W127)/22)</x:f>
+        <x:v>0.7272727272727273</x:v>
+      </x:c>
+      <x:c r="Y127" s="179" t="str">
+        <x:v>Generated by ChatGPT as a candidate on 2026-08-06. The Google Maps link is for discovery only and is not a verified factual source. Replace it with an official or authoritative source during review.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="128">
+      <x:c r="A128" t="str">
+        <x:v>A125</x:v>
+      </x:c>
+      <x:c r="B128" t="str">
+        <x:v>Sultan Salahuddin Abdul Aziz Shah Mosque</x:v>
+      </x:c>
+      <x:c r="C128" t="str">
+        <x:v>Selangor</x:v>
+      </x:c>
+      <x:c r="D128" s="179" t="str">
+        <x:v>Shah Alam</x:v>
+      </x:c>
+      <x:c r="E128" s="179" t="str">
+        <x:v>Religious Site</x:v>
+      </x:c>
+      <x:c r="F128" s="179" t="str">
+        <x:v>mosque; architecture; religion; photography; culture</x:v>
+      </x:c>
+      <x:c r="G128" s="179" t="str">
+        <x:v>Both</x:v>
+      </x:c>
+      <x:c r="H128" s="179" t="str">
+        <x:v>AI-generated candidate attraction in Shah Alam, Selangor. The place name, category, description and visitor details require source verification before production use.</x:v>
+      </x:c>
+      <x:c r="I128" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="J128"/>
+      <x:c r="K128"/>
+      <x:c r="L128"/>
+      <x:c r="M128" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="N128" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="O128" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="P128" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="Q128" s="179" t="str">
+        <x:v>Accessibility information has not been verified. Confirm terrain, steps, seating, toilets and mobility access with an official source before recommending it as elderly-friendly.</x:v>
+      </x:c>
+      <x:c r="R128"/>
+      <x:c r="S128"/>
+      <x:c r="T128" s="179"/>
+      <x:c r="U128" s="179" t="str">
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Sultan%20Salahuddin%20Abdul%20Aziz%20Shah%20Mosque%2C%20Selangor%2C%20Malaysia</x:v>
+      </x:c>
+      <x:c r="V128" s="184" t="n">
+        <x:v>46240</x:v>
+      </x:c>
+      <x:c r="W128" s="179" t="str">
+        <x:v>Unverified</x:v>
+      </x:c>
+      <x:c r="X128" s="185" t="n">
+        <x:f>IF(B128="","",COUNTA(B128:W128)/22)</x:f>
+        <x:v>0.7272727272727273</x:v>
+      </x:c>
+      <x:c r="Y128" s="179" t="str">
+        <x:v>Generated by ChatGPT as a candidate on 2026-08-06. The Google Maps link is for discovery only and is not a verified factual source. Replace it with an official or authoritative source during review.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="129">
+      <x:c r="A129" t="str">
+        <x:v>A126</x:v>
+      </x:c>
+      <x:c r="B129" t="str">
+        <x:v>Farm in the City</x:v>
+      </x:c>
+      <x:c r="C129" t="str">
+        <x:v>Selangor</x:v>
+      </x:c>
+      <x:c r="D129" s="179" t="str">
+        <x:v>Seri Kembangan</x:v>
+      </x:c>
+      <x:c r="E129" s="179" t="str">
+        <x:v>Family Attraction</x:v>
+      </x:c>
+      <x:c r="F129" s="179" t="str">
+        <x:v>animals; farm; family; children; education</x:v>
+      </x:c>
+      <x:c r="G129" s="179" t="str">
+        <x:v>Both</x:v>
+      </x:c>
+      <x:c r="H129" s="179" t="str">
+        <x:v>AI-generated candidate attraction in Seri Kembangan, Selangor. The place name, category, description and visitor details require source verification before production use.</x:v>
+      </x:c>
+      <x:c r="I129" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="J129"/>
+      <x:c r="K129"/>
+      <x:c r="L129"/>
+      <x:c r="M129" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="N129" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="O129" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="P129" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="Q129" s="179" t="str">
+        <x:v>Accessibility information has not been verified. Confirm terrain, steps, seating, toilets and mobility access with an official source before recommending it as elderly-friendly.</x:v>
+      </x:c>
+      <x:c r="R129"/>
+      <x:c r="S129"/>
+      <x:c r="T129" s="179"/>
+      <x:c r="U129" s="179" t="str">
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Farm%20in%20the%20City%2C%20Selangor%2C%20Malaysia</x:v>
+      </x:c>
+      <x:c r="V129" s="184" t="n">
+        <x:v>46240</x:v>
+      </x:c>
+      <x:c r="W129" s="179" t="str">
+        <x:v>Unverified</x:v>
+      </x:c>
+      <x:c r="X129" s="185" t="n">
+        <x:f>IF(B129="","",COUNTA(B129:W129)/22)</x:f>
+        <x:v>0.7272727272727273</x:v>
+      </x:c>
+      <x:c r="Y129" s="179" t="str">
+        <x:v>Generated by ChatGPT as a candidate on 2026-08-06. The Google Maps link is for discovery only and is not a verified factual source. Replace it with an official or authoritative source during review.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="130">
+      <x:c r="A130" t="str">
+        <x:v>A127</x:v>
+      </x:c>
+      <x:c r="B130" t="str">
+        <x:v>National Botanical Garden Shah Alam</x:v>
+      </x:c>
+      <x:c r="C130" t="str">
+        <x:v>Selangor</x:v>
+      </x:c>
+      <x:c r="D130" s="179" t="str">
+        <x:v>Shah Alam</x:v>
+      </x:c>
+      <x:c r="E130" s="179" t="str">
+        <x:v>Park and Recreation</x:v>
+      </x:c>
+      <x:c r="F130" s="179" t="str">
+        <x:v>garden; nature; walking; family; relaxation</x:v>
+      </x:c>
+      <x:c r="G130" s="179" t="str">
+        <x:v>Outdoor</x:v>
+      </x:c>
+      <x:c r="H130" s="179" t="str">
+        <x:v>AI-generated candidate attraction in Shah Alam, Selangor. The place name, category, description and visitor details require source verification before production use.</x:v>
+      </x:c>
+      <x:c r="I130" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="J130"/>
+      <x:c r="K130"/>
+      <x:c r="L130"/>
+      <x:c r="M130" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="N130" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="O130" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="P130" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="Q130" s="179" t="str">
+        <x:v>Accessibility information has not been verified. Confirm terrain, steps, seating, toilets and mobility access with an official source before recommending it as elderly-friendly.</x:v>
+      </x:c>
+      <x:c r="R130"/>
+      <x:c r="S130"/>
+      <x:c r="T130" s="179"/>
+      <x:c r="U130" s="179" t="str">
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=National%20Botanical%20Garden%20Shah%20Alam%2C%20Selangor%2C%20Malaysia</x:v>
+      </x:c>
+      <x:c r="V130" s="184" t="n">
+        <x:v>46240</x:v>
+      </x:c>
+      <x:c r="W130" s="179" t="str">
+        <x:v>Unverified</x:v>
+      </x:c>
+      <x:c r="X130" s="185" t="n">
+        <x:f>IF(B130="","",COUNTA(B130:W130)/22)</x:f>
+        <x:v>0.7272727272727273</x:v>
+      </x:c>
+      <x:c r="Y130" s="179" t="str">
+        <x:v>Generated by ChatGPT as a candidate on 2026-08-06. The Google Maps link is for discovery only and is not a verified factual source. Replace it with an official or authoritative source during review.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="131">
+      <x:c r="A131" t="str">
+        <x:v>A128</x:v>
+      </x:c>
+      <x:c r="B131" t="str">
+        <x:v>Redang Island</x:v>
+      </x:c>
+      <x:c r="C131" t="str">
+        <x:v>Terengganu</x:v>
+      </x:c>
+      <x:c r="D131" s="179" t="str">
+        <x:v>Kuala Nerus</x:v>
+      </x:c>
+      <x:c r="E131" s="179" t="str">
+        <x:v>Beach and Island</x:v>
+      </x:c>
+      <x:c r="F131" s="179" t="str">
+        <x:v>island; beach; snorkelling; diving; relaxation</x:v>
+      </x:c>
+      <x:c r="G131" s="179" t="str">
+        <x:v>Outdoor</x:v>
+      </x:c>
+      <x:c r="H131" s="179" t="str">
+        <x:v>AI-generated candidate attraction in Kuala Nerus, Terengganu. The place name, category, description and visitor details require source verification before production use.</x:v>
+      </x:c>
+      <x:c r="I131" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="J131"/>
+      <x:c r="K131"/>
+      <x:c r="L131"/>
+      <x:c r="M131" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="N131" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="O131" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="P131" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="Q131" s="179" t="str">
+        <x:v>Accessibility information has not been verified. Confirm terrain, steps, seating, toilets and mobility access with an official source before recommending it as elderly-friendly.</x:v>
+      </x:c>
+      <x:c r="R131"/>
+      <x:c r="S131"/>
+      <x:c r="T131" s="179"/>
+      <x:c r="U131" s="179" t="str">
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Redang%20Island%2C%20Terengganu%2C%20Malaysia</x:v>
+      </x:c>
+      <x:c r="V131" s="184" t="n">
+        <x:v>46240</x:v>
+      </x:c>
+      <x:c r="W131" s="179" t="str">
+        <x:v>Unverified</x:v>
+      </x:c>
+      <x:c r="X131" s="185" t="n">
+        <x:f>IF(B131="","",COUNTA(B131:W131)/22)</x:f>
+        <x:v>0.7272727272727273</x:v>
+      </x:c>
+      <x:c r="Y131" s="179" t="str">
+        <x:v>Generated by ChatGPT as a candidate on 2026-08-06. The Google Maps link is for discovery only and is not a verified factual source. Replace it with an official or authoritative source during review.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="132">
+      <x:c r="A132" t="str">
+        <x:v>A129</x:v>
+      </x:c>
+      <x:c r="B132" t="str">
+        <x:v>Perhentian Islands</x:v>
+      </x:c>
+      <x:c r="C132" t="str">
+        <x:v>Terengganu</x:v>
+      </x:c>
+      <x:c r="D132" s="179" t="str">
+        <x:v>Besut</x:v>
+      </x:c>
+      <x:c r="E132" s="179" t="str">
+        <x:v>Beach and Island</x:v>
+      </x:c>
+      <x:c r="F132" s="179" t="str">
+        <x:v>island; beach; snorkelling; diving; relaxation</x:v>
+      </x:c>
+      <x:c r="G132" s="179" t="str">
+        <x:v>Outdoor</x:v>
+      </x:c>
+      <x:c r="H132" s="179" t="str">
+        <x:v>AI-generated candidate attraction in Besut, Terengganu. The place name, category, description and visitor details require source verification before production use.</x:v>
+      </x:c>
+      <x:c r="I132" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="J132"/>
+      <x:c r="K132"/>
+      <x:c r="L132"/>
+      <x:c r="M132" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="N132" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="O132" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="P132" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="Q132" s="179" t="str">
+        <x:v>Accessibility information has not been verified. Confirm terrain, steps, seating, toilets and mobility access with an official source before recommending it as elderly-friendly.</x:v>
+      </x:c>
+      <x:c r="R132"/>
+      <x:c r="S132"/>
+      <x:c r="T132" s="179"/>
+      <x:c r="U132" s="179" t="str">
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Perhentian%20Islands%2C%20Terengganu%2C%20Malaysia</x:v>
+      </x:c>
+      <x:c r="V132" s="184" t="n">
+        <x:v>46240</x:v>
+      </x:c>
+      <x:c r="W132" s="179" t="str">
+        <x:v>Unverified</x:v>
+      </x:c>
+      <x:c r="X132" s="185" t="n">
+        <x:f>IF(B132="","",COUNTA(B132:W132)/22)</x:f>
+        <x:v>0.7272727272727273</x:v>
+      </x:c>
+      <x:c r="Y132" s="179" t="str">
+        <x:v>Generated by ChatGPT as a candidate on 2026-08-06. The Google Maps link is for discovery only and is not a verified factual source. Replace it with an official or authoritative source during review.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="133">
+      <x:c r="A133" t="str">
+        <x:v>A130</x:v>
+      </x:c>
+      <x:c r="B133" t="str">
+        <x:v>Islamic Civilisation Park</x:v>
+      </x:c>
+      <x:c r="C133" t="str">
+        <x:v>Terengganu</x:v>
+      </x:c>
+      <x:c r="D133" s="179" t="str">
+        <x:v>Kuala Terengganu</x:v>
+      </x:c>
+      <x:c r="E133" s="179" t="str">
+        <x:v>Family Attraction</x:v>
+      </x:c>
+      <x:c r="F133" s="179" t="str">
+        <x:v>Islamic architecture; monuments; family; culture; education</x:v>
+      </x:c>
+      <x:c r="G133" s="179" t="str">
+        <x:v>Both</x:v>
+      </x:c>
+      <x:c r="H133" s="179" t="str">
+        <x:v>AI-generated candidate attraction in Kuala Terengganu, Terengganu. The place name, category, description and visitor details require source verification before production use.</x:v>
+      </x:c>
+      <x:c r="I133" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="J133"/>
+      <x:c r="K133"/>
+      <x:c r="L133"/>
+      <x:c r="M133" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="N133" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="O133" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="P133" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="Q133" s="179" t="str">
+        <x:v>Accessibility information has not been verified. Confirm terrain, steps, seating, toilets and mobility access with an official source before recommending it as elderly-friendly.</x:v>
+      </x:c>
+      <x:c r="R133"/>
+      <x:c r="S133"/>
+      <x:c r="T133" s="179"/>
+      <x:c r="U133" s="179" t="str">
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Islamic%20Civilisation%20Park%2C%20Terengganu%2C%20Malaysia</x:v>
+      </x:c>
+      <x:c r="V133" s="184" t="n">
+        <x:v>46240</x:v>
+      </x:c>
+      <x:c r="W133" s="179" t="str">
+        <x:v>Unverified</x:v>
+      </x:c>
+      <x:c r="X133" s="185" t="n">
+        <x:f>IF(B133="","",COUNTA(B133:W133)/22)</x:f>
+        <x:v>0.7272727272727273</x:v>
+      </x:c>
+      <x:c r="Y133" s="179" t="str">
+        <x:v>Generated by ChatGPT as a candidate on 2026-08-06. The Google Maps link is for discovery only and is not a verified factual source. Replace it with an official or authoritative source during review.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="134">
+      <x:c r="A134" t="str">
+        <x:v>A131</x:v>
+      </x:c>
+      <x:c r="B134" t="str">
+        <x:v>Terengganu State Museum</x:v>
+      </x:c>
+      <x:c r="C134" t="str">
+        <x:v>Terengganu</x:v>
+      </x:c>
+      <x:c r="D134" s="179" t="str">
+        <x:v>Kuala Terengganu</x:v>
+      </x:c>
+      <x:c r="E134" s="179" t="str">
+        <x:v>Museum and Gallery</x:v>
+      </x:c>
+      <x:c r="F134" s="179" t="str">
+        <x:v>museum; culture; heritage; history; indoor</x:v>
+      </x:c>
+      <x:c r="G134" s="179" t="str">
+        <x:v>Both</x:v>
+      </x:c>
+      <x:c r="H134" s="179" t="str">
+        <x:v>AI-generated candidate attraction in Kuala Terengganu, Terengganu. The place name, category, description and visitor details require source verification before production use.</x:v>
+      </x:c>
+      <x:c r="I134" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="J134"/>
+      <x:c r="K134"/>
+      <x:c r="L134"/>
+      <x:c r="M134" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="N134" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="O134" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="P134" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="Q134" s="179" t="str">
+        <x:v>Accessibility information has not been verified. Confirm terrain, steps, seating, toilets and mobility access with an official source before recommending it as elderly-friendly.</x:v>
+      </x:c>
+      <x:c r="R134"/>
+      <x:c r="S134"/>
+      <x:c r="T134" s="179"/>
+      <x:c r="U134" s="179" t="str">
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Terengganu%20State%20Museum%2C%20Terengganu%2C%20Malaysia</x:v>
+      </x:c>
+      <x:c r="V134" s="184" t="n">
+        <x:v>46240</x:v>
+      </x:c>
+      <x:c r="W134" s="179" t="str">
+        <x:v>Unverified</x:v>
+      </x:c>
+      <x:c r="X134" s="185" t="n">
+        <x:f>IF(B134="","",COUNTA(B134:W134)/22)</x:f>
+        <x:v>0.7272727272727273</x:v>
+      </x:c>
+      <x:c r="Y134" s="179" t="str">
+        <x:v>Generated by ChatGPT as a candidate on 2026-08-06. The Google Maps link is for discovery only and is not a verified factual source. Replace it with an official or authoritative source during review.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="135">
+      <x:c r="A135" t="str">
+        <x:v>A132</x:v>
+      </x:c>
+      <x:c r="B135" t="str">
+        <x:v>Crystal Mosque</x:v>
+      </x:c>
+      <x:c r="C135" t="str">
+        <x:v>Terengganu</x:v>
+      </x:c>
+      <x:c r="D135" s="179" t="str">
+        <x:v>Kuala Terengganu</x:v>
+      </x:c>
+      <x:c r="E135" s="179" t="str">
+        <x:v>Religious Site</x:v>
+      </x:c>
+      <x:c r="F135" s="179" t="str">
+        <x:v>mosque; architecture; religion; photography; waterfront</x:v>
+      </x:c>
+      <x:c r="G135" s="179" t="str">
+        <x:v>Both</x:v>
+      </x:c>
+      <x:c r="H135" s="179" t="str">
+        <x:v>AI-generated candidate attraction in Kuala Terengganu, Terengganu. The place name, category, description and visitor details require source verification before production use.</x:v>
+      </x:c>
+      <x:c r="I135" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="J135"/>
+      <x:c r="K135"/>
+      <x:c r="L135"/>
+      <x:c r="M135" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="N135" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="O135" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="P135" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="Q135" s="179" t="str">
+        <x:v>Accessibility information has not been verified. Confirm terrain, steps, seating, toilets and mobility access with an official source before recommending it as elderly-friendly.</x:v>
+      </x:c>
+      <x:c r="R135"/>
+      <x:c r="S135"/>
+      <x:c r="T135" s="179"/>
+      <x:c r="U135" s="179" t="str">
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Crystal%20Mosque%2C%20Terengganu%2C%20Malaysia</x:v>
+      </x:c>
+      <x:c r="V135" s="184" t="n">
+        <x:v>46240</x:v>
+      </x:c>
+      <x:c r="W135" s="179" t="str">
+        <x:v>Unverified</x:v>
+      </x:c>
+      <x:c r="X135" s="185" t="n">
+        <x:f>IF(B135="","",COUNTA(B135:W135)/22)</x:f>
+        <x:v>0.7272727272727273</x:v>
+      </x:c>
+      <x:c r="Y135" s="179" t="str">
+        <x:v>Generated by ChatGPT as a candidate on 2026-08-06. The Google Maps link is for discovery only and is not a verified factual source. Replace it with an official or authoritative source during review.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="136">
+      <x:c r="A136" t="str">
+        <x:v>A133</x:v>
+      </x:c>
+      <x:c r="B136" t="str">
+        <x:v>Kenyir Lake</x:v>
+      </x:c>
+      <x:c r="C136" t="str">
+        <x:v>Terengganu</x:v>
+      </x:c>
+      <x:c r="D136" s="179" t="str">
+        <x:v>Hulu Terengganu</x:v>
+      </x:c>
+      <x:c r="E136" s="179" t="str">
+        <x:v>Nature</x:v>
+      </x:c>
+      <x:c r="F136" s="179" t="str">
+        <x:v>lake; boat trip; fishing; nature; relaxation; adventure</x:v>
+      </x:c>
+      <x:c r="G136" s="179" t="str">
+        <x:v>Outdoor</x:v>
+      </x:c>
+      <x:c r="H136" s="179" t="str">
+        <x:v>AI-generated candidate attraction in Hulu Terengganu, Terengganu. The place name, category, description and visitor details require source verification before production use.</x:v>
+      </x:c>
+      <x:c r="I136" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="J136"/>
+      <x:c r="K136"/>
+      <x:c r="L136"/>
+      <x:c r="M136" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="N136" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="O136" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="P136" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="Q136" s="179" t="str">
+        <x:v>Accessibility information has not been verified. Confirm terrain, steps, seating, toilets and mobility access with an official source before recommending it as elderly-friendly.</x:v>
+      </x:c>
+      <x:c r="R136"/>
+      <x:c r="S136"/>
+      <x:c r="T136" s="179"/>
+      <x:c r="U136" s="179" t="str">
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Kenyir%20Lake%2C%20Terengganu%2C%20Malaysia</x:v>
+      </x:c>
+      <x:c r="V136" s="184" t="n">
+        <x:v>46240</x:v>
+      </x:c>
+      <x:c r="W136" s="179" t="str">
+        <x:v>Unverified</x:v>
+      </x:c>
+      <x:c r="X136" s="185" t="n">
+        <x:f>IF(B136="","",COUNTA(B136:W136)/22)</x:f>
+        <x:v>0.7272727272727273</x:v>
+      </x:c>
+      <x:c r="Y136" s="179" t="str">
+        <x:v>Generated by ChatGPT as a candidate on 2026-08-06. The Google Maps link is for discovery only and is not a verified factual source. Replace it with an official or authoritative source during review.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="137">
+      <x:c r="A137" t="str">
+        <x:v>A134</x:v>
+      </x:c>
+      <x:c r="B137" t="str">
+        <x:v>Rantau Abang Turtle Information Centre</x:v>
+      </x:c>
+      <x:c r="C137" t="str">
+        <x:v>Terengganu</x:v>
+      </x:c>
+      <x:c r="D137" s="179" t="str">
+        <x:v>Dungun</x:v>
+      </x:c>
+      <x:c r="E137" s="179" t="str">
+        <x:v>Wildlife</x:v>
+      </x:c>
+      <x:c r="F137" s="179" t="str">
+        <x:v>turtles; conservation; education; wildlife; family</x:v>
+      </x:c>
+      <x:c r="G137" s="179" t="str">
+        <x:v>Both</x:v>
+      </x:c>
+      <x:c r="H137" s="179" t="str">
+        <x:v>AI-generated candidate attraction in Dungun, Terengganu. The place name, category, description and visitor details require source verification before production use.</x:v>
+      </x:c>
+      <x:c r="I137" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="J137"/>
+      <x:c r="K137"/>
+      <x:c r="L137"/>
+      <x:c r="M137" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="N137" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="O137" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="P137" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="Q137" s="179" t="str">
+        <x:v>Accessibility information has not been verified. Confirm terrain, steps, seating, toilets and mobility access with an official source before recommending it as elderly-friendly.</x:v>
+      </x:c>
+      <x:c r="R137"/>
+      <x:c r="S137"/>
+      <x:c r="T137" s="179"/>
+      <x:c r="U137" s="179" t="str">
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Rantau%20Abang%20Turtle%20Information%20Centre%2C%20Terengganu%2C%20Malaysia</x:v>
+      </x:c>
+      <x:c r="V137" s="184" t="n">
+        <x:v>46240</x:v>
+      </x:c>
+      <x:c r="W137" s="179" t="str">
+        <x:v>Unverified</x:v>
+      </x:c>
+      <x:c r="X137" s="185" t="n">
+        <x:f>IF(B137="","",COUNTA(B137:W137)/22)</x:f>
+        <x:v>0.7272727272727273</x:v>
+      </x:c>
+      <x:c r="Y137" s="179" t="str">
+        <x:v>Generated by ChatGPT as a candidate on 2026-08-06. The Google Maps link is for discovery only and is not a verified factual source. Replace it with an official or authoritative source during review.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="138">
+      <x:c r="A138" t="str">
+        <x:v>A135</x:v>
+      </x:c>
+      <x:c r="B138" t="str">
+        <x:v>Kampung Cina Kuala Terengganu</x:v>
+      </x:c>
+      <x:c r="C138" t="str">
+        <x:v>Terengganu</x:v>
+      </x:c>
+      <x:c r="D138" s="179" t="str">
+        <x:v>Kuala Terengganu</x:v>
+      </x:c>
+      <x:c r="E138" s="179" t="str">
+        <x:v>Heritage and History</x:v>
+      </x:c>
+      <x:c r="F138" s="179" t="str">
+        <x:v>heritage; culture; food; architecture; walking</x:v>
+      </x:c>
+      <x:c r="G138" s="179" t="str">
+        <x:v>Outdoor</x:v>
+      </x:c>
+      <x:c r="H138" s="179" t="str">
+        <x:v>AI-generated candidate attraction in Kuala Terengganu, Terengganu. The place name, category, description and visitor details require source verification before production use.</x:v>
+      </x:c>
+      <x:c r="I138" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="J138"/>
+      <x:c r="K138"/>
+      <x:c r="L138"/>
+      <x:c r="M138" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="N138" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="O138" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="P138" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="Q138" s="179" t="str">
+        <x:v>Accessibility information has not been verified. Confirm terrain, steps, seating, toilets and mobility access with an official source before recommending it as elderly-friendly.</x:v>
+      </x:c>
+      <x:c r="R138"/>
+      <x:c r="S138"/>
+      <x:c r="T138" s="179"/>
+      <x:c r="U138" s="179" t="str">
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Kampung%20Cina%20Kuala%20Terengganu%2C%20Terengganu%2C%20Malaysia</x:v>
+      </x:c>
+      <x:c r="V138" s="184" t="n">
+        <x:v>46240</x:v>
+      </x:c>
+      <x:c r="W138" s="179" t="str">
+        <x:v>Unverified</x:v>
+      </x:c>
+      <x:c r="X138" s="185" t="n">
+        <x:f>IF(B138="","",COUNTA(B138:W138)/22)</x:f>
+        <x:v>0.7272727272727273</x:v>
+      </x:c>
+      <x:c r="Y138" s="179" t="str">
+        <x:v>Generated by ChatGPT as a candidate on 2026-08-06. The Google Maps link is for discovery only and is not a verified factual source. Replace it with an official or authoritative source during review.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="139">
+      <x:c r="A139" t="str">
+        <x:v>A136</x:v>
+      </x:c>
+      <x:c r="B139" t="str">
+        <x:v>Petronas Twin Towers</x:v>
+      </x:c>
+      <x:c r="C139" t="str">
+        <x:v>Kuala Lumpur</x:v>
+      </x:c>
+      <x:c r="D139" s="179" t="str">
+        <x:v>Kuala Lumpur City Centre</x:v>
+      </x:c>
+      <x:c r="E139" s="179" t="str">
+        <x:v>Urban Attraction</x:v>
+      </x:c>
+      <x:c r="F139" s="179" t="str">
+        <x:v>architecture; city view; shopping; photography; landmark</x:v>
+      </x:c>
+      <x:c r="G139" s="179" t="str">
+        <x:v>Both</x:v>
+      </x:c>
+      <x:c r="H139" s="179" t="str">
+        <x:v>AI-generated candidate attraction in Kuala Lumpur City Centre, Kuala Lumpur. The place name, category, description and visitor details require source verification before production use.</x:v>
+      </x:c>
+      <x:c r="I139" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="J139"/>
+      <x:c r="K139"/>
+      <x:c r="L139"/>
+      <x:c r="M139" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="N139" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="O139" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="P139" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="Q139" s="179" t="str">
+        <x:v>Accessibility information has not been verified. Confirm terrain, steps, seating, toilets and mobility access with an official source before recommending it as elderly-friendly.</x:v>
+      </x:c>
+      <x:c r="R139"/>
+      <x:c r="S139"/>
+      <x:c r="T139" s="179"/>
+      <x:c r="U139" s="179" t="str">
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Petronas%20Twin%20Towers%2C%20Kuala%20Lumpur%2C%20Malaysia</x:v>
+      </x:c>
+      <x:c r="V139" s="184" t="n">
+        <x:v>46240</x:v>
+      </x:c>
+      <x:c r="W139" s="179" t="str">
+        <x:v>Unverified</x:v>
+      </x:c>
+      <x:c r="X139" s="185" t="n">
+        <x:f>IF(B139="","",COUNTA(B139:W139)/22)</x:f>
+        <x:v>0.7272727272727273</x:v>
+      </x:c>
+      <x:c r="Y139" s="179" t="str">
+        <x:v>Generated by ChatGPT as a candidate on 2026-08-06. The Google Maps link is for discovery only and is not a verified factual source. Replace it with an official or authoritative source during review.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="140">
+      <x:c r="A140" t="str">
+        <x:v>A137</x:v>
+      </x:c>
+      <x:c r="B140" t="str">
+        <x:v>KLCC Park</x:v>
+      </x:c>
+      <x:c r="C140" t="str">
+        <x:v>Kuala Lumpur</x:v>
+      </x:c>
+      <x:c r="D140" s="179" t="str">
+        <x:v>Kuala Lumpur City Centre</x:v>
+      </x:c>
+      <x:c r="E140" s="179" t="str">
+        <x:v>Park and Recreation</x:v>
+      </x:c>
+      <x:c r="F140" s="179" t="str">
+        <x:v>urban park; walking; relaxation; family; scenery</x:v>
+      </x:c>
+      <x:c r="G140" s="179" t="str">
+        <x:v>Outdoor</x:v>
+      </x:c>
+      <x:c r="H140" s="179" t="str">
+        <x:v>AI-generated candidate attraction in Kuala Lumpur City Centre, Kuala Lumpur. The place name, category, description and visitor details require source verification before production use.</x:v>
+      </x:c>
+      <x:c r="I140" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="J140"/>
+      <x:c r="K140"/>
+      <x:c r="L140"/>
+      <x:c r="M140" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="N140" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="O140" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="P140" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="Q140" s="179" t="str">
+        <x:v>Accessibility information has not been verified. Confirm terrain, steps, seating, toilets and mobility access with an official source before recommending it as elderly-friendly.</x:v>
+      </x:c>
+      <x:c r="R140"/>
+      <x:c r="S140"/>
+      <x:c r="T140" s="179"/>
+      <x:c r="U140" s="179" t="str">
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=KLCC%20Park%2C%20Kuala%20Lumpur%2C%20Malaysia</x:v>
+      </x:c>
+      <x:c r="V140" s="184" t="n">
+        <x:v>46240</x:v>
+      </x:c>
+      <x:c r="W140" s="179" t="str">
+        <x:v>Unverified</x:v>
+      </x:c>
+      <x:c r="X140" s="185" t="n">
+        <x:f>IF(B140="","",COUNTA(B140:W140)/22)</x:f>
+        <x:v>0.7272727272727273</x:v>
+      </x:c>
+      <x:c r="Y140" s="179" t="str">
+        <x:v>Generated by ChatGPT as a candidate on 2026-08-06. The Google Maps link is for discovery only and is not a verified factual source. Replace it with an official or authoritative source during review.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="141">
+      <x:c r="A141" t="str">
+        <x:v>A138</x:v>
+      </x:c>
+      <x:c r="B141" t="str">
+        <x:v>Aquaria KLCC</x:v>
+      </x:c>
+      <x:c r="C141" t="str">
+        <x:v>Kuala Lumpur</x:v>
+      </x:c>
+      <x:c r="D141" s="179" t="str">
+        <x:v>Kuala Lumpur City Centre</x:v>
+      </x:c>
+      <x:c r="E141" s="179" t="str">
+        <x:v>Family Attraction</x:v>
+      </x:c>
+      <x:c r="F141" s="179" t="str">
+        <x:v>aquarium; marine life; family; children; indoor</x:v>
+      </x:c>
+      <x:c r="G141" s="179" t="str">
+        <x:v>Indoor</x:v>
+      </x:c>
+      <x:c r="H141" s="179" t="str">
+        <x:v>AI-generated candidate attraction in Kuala Lumpur City Centre, Kuala Lumpur. The place name, category, description and visitor details require source verification before production use.</x:v>
+      </x:c>
+      <x:c r="I141" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="J141"/>
+      <x:c r="K141"/>
+      <x:c r="L141"/>
+      <x:c r="M141" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="N141" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="O141" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="P141" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="Q141" s="179" t="str">
+        <x:v>Accessibility information has not been verified. Confirm terrain, steps, seating, toilets and mobility access with an official source before recommending it as elderly-friendly.</x:v>
+      </x:c>
+      <x:c r="R141"/>
+      <x:c r="S141"/>
+      <x:c r="T141" s="179"/>
+      <x:c r="U141" s="179" t="str">
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Aquaria%20KLCC%2C%20Kuala%20Lumpur%2C%20Malaysia</x:v>
+      </x:c>
+      <x:c r="V141" s="184" t="n">
+        <x:v>46240</x:v>
+      </x:c>
+      <x:c r="W141" s="179" t="str">
+        <x:v>Unverified</x:v>
+      </x:c>
+      <x:c r="X141" s="185" t="n">
+        <x:f>IF(B141="","",COUNTA(B141:W141)/22)</x:f>
+        <x:v>0.7272727272727273</x:v>
+      </x:c>
+      <x:c r="Y141" s="179" t="str">
+        <x:v>Generated by ChatGPT as a candidate on 2026-08-06. The Google Maps link is for discovery only and is not a verified factual source. Replace it with an official or authoritative source during review.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="142">
+      <x:c r="A142" t="str">
+        <x:v>A139</x:v>
+      </x:c>
+      <x:c r="B142" t="str">
+        <x:v>Central Market Kuala Lumpur</x:v>
+      </x:c>
+      <x:c r="C142" t="str">
+        <x:v>Kuala Lumpur</x:v>
+      </x:c>
+      <x:c r="D142" s="179" t="str">
+        <x:v>City Centre</x:v>
+      </x:c>
+      <x:c r="E142" s="179" t="str">
+        <x:v>Shopping</x:v>
+      </x:c>
+      <x:c r="F142" s="179" t="str">
+        <x:v>market; handicrafts; shopping; culture; local food</x:v>
+      </x:c>
+      <x:c r="G142" s="179" t="str">
+        <x:v>Indoor</x:v>
+      </x:c>
+      <x:c r="H142" s="179" t="str">
+        <x:v>AI-generated candidate attraction in City Centre, Kuala Lumpur. The place name, category, description and visitor details require source verification before production use.</x:v>
+      </x:c>
+      <x:c r="I142" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="J142"/>
+      <x:c r="K142"/>
+      <x:c r="L142"/>
+      <x:c r="M142" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="N142" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="O142" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="P142" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="Q142" s="179" t="str">
+        <x:v>Accessibility information has not been verified. Confirm terrain, steps, seating, toilets and mobility access with an official source before recommending it as elderly-friendly.</x:v>
+      </x:c>
+      <x:c r="R142"/>
+      <x:c r="S142"/>
+      <x:c r="T142" s="179"/>
+      <x:c r="U142" s="179" t="str">
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Central%20Market%20Kuala%20Lumpur%2C%20Kuala%20Lumpur%2C%20Malaysia</x:v>
+      </x:c>
+      <x:c r="V142" s="184" t="n">
+        <x:v>46240</x:v>
+      </x:c>
+      <x:c r="W142" s="179" t="str">
+        <x:v>Unverified</x:v>
+      </x:c>
+      <x:c r="X142" s="185" t="n">
+        <x:f>IF(B142="","",COUNTA(B142:W142)/22)</x:f>
+        <x:v>0.7272727272727273</x:v>
+      </x:c>
+      <x:c r="Y142" s="179" t="str">
+        <x:v>Generated by ChatGPT as a candidate on 2026-08-06. The Google Maps link is for discovery only and is not a verified factual source. Replace it with an official or authoritative source during review.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="143">
+      <x:c r="A143" t="str">
+        <x:v>A140</x:v>
+      </x:c>
+      <x:c r="B143" t="str">
+        <x:v>Perdana Botanical Gardens</x:v>
+      </x:c>
+      <x:c r="C143" t="str">
+        <x:v>Kuala Lumpur</x:v>
+      </x:c>
+      <x:c r="D143" s="179" t="str">
+        <x:v>Lake Gardens</x:v>
+      </x:c>
+      <x:c r="E143" s="179" t="str">
+        <x:v>Wellness and Relaxation</x:v>
+      </x:c>
+      <x:c r="F143" s="179" t="str">
+        <x:v>garden; walking; relaxation; nature; family</x:v>
+      </x:c>
+      <x:c r="G143" s="179" t="str">
+        <x:v>Outdoor</x:v>
+      </x:c>
+      <x:c r="H143" s="179" t="str">
+        <x:v>AI-generated candidate attraction in Lake Gardens, Kuala Lumpur. The place name, category, description and visitor details require source verification before production use.</x:v>
+      </x:c>
+      <x:c r="I143" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="J143"/>
+      <x:c r="K143"/>
+      <x:c r="L143"/>
+      <x:c r="M143" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="N143" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="O143" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="P143" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="Q143" s="179" t="str">
+        <x:v>Accessibility information has not been verified. Confirm terrain, steps, seating, toilets and mobility access with an official source before recommending it as elderly-friendly.</x:v>
+      </x:c>
+      <x:c r="R143"/>
+      <x:c r="S143"/>
+      <x:c r="T143" s="179"/>
+      <x:c r="U143" s="179" t="str">
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Perdana%20Botanical%20Gardens%2C%20Kuala%20Lumpur%2C%20Malaysia</x:v>
+      </x:c>
+      <x:c r="V143" s="184" t="n">
+        <x:v>46240</x:v>
+      </x:c>
+      <x:c r="W143" s="179" t="str">
+        <x:v>Unverified</x:v>
+      </x:c>
+      <x:c r="X143" s="185" t="n">
+        <x:f>IF(B143="","",COUNTA(B143:W143)/22)</x:f>
+        <x:v>0.7272727272727273</x:v>
+      </x:c>
+      <x:c r="Y143" s="179" t="str">
+        <x:v>Generated by ChatGPT as a candidate on 2026-08-06. The Google Maps link is for discovery only and is not a verified factual source. Replace it with an official or authoritative source during review.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="144">
+      <x:c r="A144" t="str">
+        <x:v>A141</x:v>
+      </x:c>
+      <x:c r="B144" t="str">
+        <x:v>Islamic Arts Museum Malaysia</x:v>
+      </x:c>
+      <x:c r="C144" t="str">
+        <x:v>Kuala Lumpur</x:v>
+      </x:c>
+      <x:c r="D144" s="179" t="str">
+        <x:v>Lake Gardens</x:v>
+      </x:c>
+      <x:c r="E144" s="179" t="str">
+        <x:v>Museum and Gallery</x:v>
+      </x:c>
+      <x:c r="F144" s="179" t="str">
+        <x:v>museum; Islamic art; culture; architecture; indoor</x:v>
+      </x:c>
+      <x:c r="G144" s="179" t="str">
+        <x:v>Indoor</x:v>
+      </x:c>
+      <x:c r="H144" s="179" t="str">
+        <x:v>AI-generated candidate attraction in Lake Gardens, Kuala Lumpur. The place name, category, description and visitor details require source verification before production use.</x:v>
+      </x:c>
+      <x:c r="I144" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="J144"/>
+      <x:c r="K144"/>
+      <x:c r="L144"/>
+      <x:c r="M144" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="N144" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="O144" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="P144" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="Q144" s="179" t="str">
+        <x:v>Accessibility information has not been verified. Confirm terrain, steps, seating, toilets and mobility access with an official source before recommending it as elderly-friendly.</x:v>
+      </x:c>
+      <x:c r="R144"/>
+      <x:c r="S144"/>
+      <x:c r="T144" s="179"/>
+      <x:c r="U144" s="179" t="str">
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Islamic%20Arts%20Museum%20Malaysia%2C%20Kuala%20Lumpur%2C%20Malaysia</x:v>
+      </x:c>
+      <x:c r="V144" s="184" t="n">
+        <x:v>46240</x:v>
+      </x:c>
+      <x:c r="W144" s="179" t="str">
+        <x:v>Unverified</x:v>
+      </x:c>
+      <x:c r="X144" s="185" t="n">
+        <x:f>IF(B144="","",COUNTA(B144:W144)/22)</x:f>
+        <x:v>0.7272727272727273</x:v>
+      </x:c>
+      <x:c r="Y144" s="179" t="str">
+        <x:v>Generated by ChatGPT as a candidate on 2026-08-06. The Google Maps link is for discovery only and is not a verified factual source. Replace it with an official or authoritative source during review.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="145">
+      <x:c r="A145" t="str">
+        <x:v>A142</x:v>
+      </x:c>
+      <x:c r="B145" t="str">
+        <x:v>National Museum of Malaysia</x:v>
+      </x:c>
+      <x:c r="C145" t="str">
+        <x:v>Kuala Lumpur</x:v>
+      </x:c>
+      <x:c r="D145" s="179" t="str">
+        <x:v>Brickfields</x:v>
+      </x:c>
+      <x:c r="E145" s="179" t="str">
+        <x:v>Museum and Gallery</x:v>
+      </x:c>
+      <x:c r="F145" s="179" t="str">
+        <x:v>museum; Malaysian history; culture; heritage; indoor</x:v>
+      </x:c>
+      <x:c r="G145" s="179" t="str">
+        <x:v>Indoor</x:v>
+      </x:c>
+      <x:c r="H145" s="179" t="str">
+        <x:v>AI-generated candidate attraction in Brickfields, Kuala Lumpur. The place name, category, description and visitor details require source verification before production use.</x:v>
+      </x:c>
+      <x:c r="I145" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="J145"/>
+      <x:c r="K145"/>
+      <x:c r="L145"/>
+      <x:c r="M145" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="N145" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="O145" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="P145" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="Q145" s="179" t="str">
+        <x:v>Accessibility information has not been verified. Confirm terrain, steps, seating, toilets and mobility access with an official source before recommending it as elderly-friendly.</x:v>
+      </x:c>
+      <x:c r="R145"/>
+      <x:c r="S145"/>
+      <x:c r="T145" s="179"/>
+      <x:c r="U145" s="179" t="str">
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=National%20Museum%20of%20Malaysia%2C%20Kuala%20Lumpur%2C%20Malaysia</x:v>
+      </x:c>
+      <x:c r="V145" s="184" t="n">
+        <x:v>46240</x:v>
+      </x:c>
+      <x:c r="W145" s="179" t="str">
+        <x:v>Unverified</x:v>
+      </x:c>
+      <x:c r="X145" s="185" t="n">
+        <x:f>IF(B145="","",COUNTA(B145:W145)/22)</x:f>
+        <x:v>0.7272727272727273</x:v>
+      </x:c>
+      <x:c r="Y145" s="179" t="str">
+        <x:v>Generated by ChatGPT as a candidate on 2026-08-06. The Google Maps link is for discovery only and is not a verified factual source. Replace it with an official or authoritative source during review.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="146">
+      <x:c r="A146" t="str">
+        <x:v>A143</x:v>
+      </x:c>
+      <x:c r="B146" t="str">
+        <x:v>Thean Hou Temple</x:v>
+      </x:c>
+      <x:c r="C146" t="str">
+        <x:v>Kuala Lumpur</x:v>
+      </x:c>
+      <x:c r="D146" s="179" t="str">
+        <x:v>Seputeh</x:v>
+      </x:c>
+      <x:c r="E146" s="179" t="str">
+        <x:v>Religious Site</x:v>
+      </x:c>
+      <x:c r="F146" s="179" t="str">
+        <x:v>temple; architecture; culture; religion; photography</x:v>
+      </x:c>
+      <x:c r="G146" s="179" t="str">
+        <x:v>Both</x:v>
+      </x:c>
+      <x:c r="H146" s="179" t="str">
+        <x:v>AI-generated candidate attraction in Seputeh, Kuala Lumpur. The place name, category, description and visitor details require source verification before production use.</x:v>
+      </x:c>
+      <x:c r="I146" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="J146"/>
+      <x:c r="K146"/>
+      <x:c r="L146"/>
+      <x:c r="M146" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="N146" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="O146" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="P146" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="Q146" s="179" t="str">
+        <x:v>Accessibility information has not been verified. Confirm terrain, steps, seating, toilets and mobility access with an official source before recommending it as elderly-friendly.</x:v>
+      </x:c>
+      <x:c r="R146"/>
+      <x:c r="S146"/>
+      <x:c r="T146" s="179"/>
+      <x:c r="U146" s="179" t="str">
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Thean%20Hou%20Temple%2C%20Kuala%20Lumpur%2C%20Malaysia</x:v>
+      </x:c>
+      <x:c r="V146" s="184" t="n">
+        <x:v>46240</x:v>
+      </x:c>
+      <x:c r="W146" s="179" t="str">
+        <x:v>Unverified</x:v>
+      </x:c>
+      <x:c r="X146" s="185" t="n">
+        <x:f>IF(B146="","",COUNTA(B146:W146)/22)</x:f>
+        <x:v>0.7272727272727273</x:v>
+      </x:c>
+      <x:c r="Y146" s="179" t="str">
+        <x:v>Generated by ChatGPT as a candidate on 2026-08-06. The Google Maps link is for discovery only and is not a verified factual source. Replace it with an official or authoritative source during review.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="147">
+      <x:c r="A147" t="str">
+        <x:v>A144</x:v>
+      </x:c>
+      <x:c r="B147" t="str">
+        <x:v>Jalan Alor</x:v>
+      </x:c>
+      <x:c r="C147" t="str">
+        <x:v>Kuala Lumpur</x:v>
+      </x:c>
+      <x:c r="D147" s="179" t="str">
+        <x:v>Bukit Bintang</x:v>
+      </x:c>
+      <x:c r="E147" s="179" t="str">
+        <x:v>Food</x:v>
+      </x:c>
+      <x:c r="F147" s="179" t="str">
+        <x:v>street food; local food; night activity; culture; walking</x:v>
+      </x:c>
+      <x:c r="G147" s="179" t="str">
+        <x:v>Outdoor</x:v>
+      </x:c>
+      <x:c r="H147" s="179" t="str">
+        <x:v>AI-generated candidate attraction in Bukit Bintang, Kuala Lumpur. The place name, category, description and visitor details require source verification before production use.</x:v>
+      </x:c>
+      <x:c r="I147" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="J147"/>
+      <x:c r="K147"/>
+      <x:c r="L147"/>
+      <x:c r="M147" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="N147" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="O147" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="P147" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="Q147" s="179" t="str">
+        <x:v>Accessibility information has not been verified. Confirm terrain, steps, seating, toilets and mobility access with an official source before recommending it as elderly-friendly.</x:v>
+      </x:c>
+      <x:c r="R147"/>
+      <x:c r="S147"/>
+      <x:c r="T147" s="179"/>
+      <x:c r="U147" s="179" t="str">
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Jalan%20Alor%2C%20Kuala%20Lumpur%2C%20Malaysia</x:v>
+      </x:c>
+      <x:c r="V147" s="184" t="n">
+        <x:v>46240</x:v>
+      </x:c>
+      <x:c r="W147" s="179" t="str">
+        <x:v>Unverified</x:v>
+      </x:c>
+      <x:c r="X147" s="185" t="n">
+        <x:f>IF(B147="","",COUNTA(B147:W147)/22)</x:f>
+        <x:v>0.7272727272727273</x:v>
+      </x:c>
+      <x:c r="Y147" s="179" t="str">
+        <x:v>Generated by ChatGPT as a candidate on 2026-08-06. The Google Maps link is for discovery only and is not a verified factual source. Replace it with an official or authoritative source during review.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="148">
+      <x:c r="A148" t="str">
+        <x:v>A145</x:v>
+      </x:c>
+      <x:c r="B148" t="str">
+        <x:v>Putra Mosque</x:v>
+      </x:c>
+      <x:c r="C148" t="str">
+        <x:v>W.P. Putrajaya</x:v>
+      </x:c>
+      <x:c r="D148" s="179" t="str">
+        <x:v>Putrajaya</x:v>
+      </x:c>
+      <x:c r="E148" s="179" t="str">
+        <x:v>Religious Site</x:v>
+      </x:c>
+      <x:c r="F148" s="179" t="str">
+        <x:v>mosque; architecture; religion; lakeside; photography</x:v>
+      </x:c>
+      <x:c r="G148" s="179" t="str">
+        <x:v>Both</x:v>
+      </x:c>
+      <x:c r="H148" s="179" t="str">
+        <x:v>AI-generated candidate attraction in Putrajaya, W.P. Putrajaya. The place name, category, description and visitor details require source verification before production use.</x:v>
+      </x:c>
+      <x:c r="I148" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="J148"/>
+      <x:c r="K148"/>
+      <x:c r="L148"/>
+      <x:c r="M148" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="N148" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="O148" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="P148" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="Q148" s="179" t="str">
+        <x:v>Accessibility information has not been verified. Confirm terrain, steps, seating, toilets and mobility access with an official source before recommending it as elderly-friendly.</x:v>
+      </x:c>
+      <x:c r="R148"/>
+      <x:c r="S148"/>
+      <x:c r="T148" s="179"/>
+      <x:c r="U148" s="179" t="str">
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Putra%20Mosque%2C%20W.P.%20Putrajaya%2C%20Malaysia</x:v>
+      </x:c>
+      <x:c r="V148" s="184" t="n">
+        <x:v>46240</x:v>
+      </x:c>
+      <x:c r="W148" s="179" t="str">
+        <x:v>Unverified</x:v>
+      </x:c>
+      <x:c r="X148" s="185" t="n">
+        <x:f>IF(B148="","",COUNTA(B148:W148)/22)</x:f>
+        <x:v>0.7272727272727273</x:v>
+      </x:c>
+      <x:c r="Y148" s="179" t="str">
+        <x:v>Generated by ChatGPT as a candidate on 2026-08-06. The Google Maps link is for discovery only and is not a verified factual source. Replace it with an official or authoritative source during review.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="149">
+      <x:c r="A149" t="str">
+        <x:v>A146</x:v>
+      </x:c>
+      <x:c r="B149" t="str">
+        <x:v>Putrajaya Botanical Garden</x:v>
+      </x:c>
+      <x:c r="C149" t="str">
+        <x:v>W.P. Putrajaya</x:v>
+      </x:c>
+      <x:c r="D149" s="179" t="str">
+        <x:v>Putrajaya</x:v>
+      </x:c>
+      <x:c r="E149" s="179" t="str">
+        <x:v>Wellness and Relaxation</x:v>
+      </x:c>
+      <x:c r="F149" s="179" t="str">
+        <x:v>garden; walking; cycling; relaxation; nature</x:v>
+      </x:c>
+      <x:c r="G149" s="179" t="str">
+        <x:v>Outdoor</x:v>
+      </x:c>
+      <x:c r="H149" s="179" t="str">
+        <x:v>AI-generated candidate attraction in Putrajaya, W.P. Putrajaya. The place name, category, description and visitor details require source verification before production use.</x:v>
+      </x:c>
+      <x:c r="I149" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="J149"/>
+      <x:c r="K149"/>
+      <x:c r="L149"/>
+      <x:c r="M149" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="N149" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="O149" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="P149" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="Q149" s="179" t="str">
+        <x:v>Accessibility information has not been verified. Confirm terrain, steps, seating, toilets and mobility access with an official source before recommending it as elderly-friendly.</x:v>
+      </x:c>
+      <x:c r="R149"/>
+      <x:c r="S149"/>
+      <x:c r="T149" s="179"/>
+      <x:c r="U149" s="179" t="str">
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Putrajaya%20Botanical%20Garden%2C%20W.P.%20Putrajaya%2C%20Malaysia</x:v>
+      </x:c>
+      <x:c r="V149" s="184" t="n">
+        <x:v>46240</x:v>
+      </x:c>
+      <x:c r="W149" s="179" t="str">
+        <x:v>Unverified</x:v>
+      </x:c>
+      <x:c r="X149" s="185" t="n">
+        <x:f>IF(B149="","",COUNTA(B149:W149)/22)</x:f>
+        <x:v>0.7272727272727273</x:v>
+      </x:c>
+      <x:c r="Y149" s="179" t="str">
+        <x:v>Generated by ChatGPT as a candidate on 2026-08-06. The Google Maps link is for discovery only and is not a verified factual source. Replace it with an official or authoritative source during review.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="150">
+      <x:c r="A150" t="str">
+        <x:v>A147</x:v>
+      </x:c>
+      <x:c r="B150" t="str">
+        <x:v>Putrajaya Lake</x:v>
+      </x:c>
+      <x:c r="C150" t="str">
+        <x:v>W.P. Putrajaya</x:v>
+      </x:c>
+      <x:c r="D150" s="179" t="str">
+        <x:v>Putrajaya</x:v>
+      </x:c>
+      <x:c r="E150" s="179" t="str">
+        <x:v>Park and Recreation</x:v>
+      </x:c>
+      <x:c r="F150" s="179" t="str">
+        <x:v>lake; scenery; walking; relaxation; recreation</x:v>
+      </x:c>
+      <x:c r="G150" s="179" t="str">
+        <x:v>Outdoor</x:v>
+      </x:c>
+      <x:c r="H150" s="179" t="str">
+        <x:v>AI-generated candidate attraction in Putrajaya, W.P. Putrajaya. The place name, category, description and visitor details require source verification before production use.</x:v>
+      </x:c>
+      <x:c r="I150" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="J150"/>
+      <x:c r="K150"/>
+      <x:c r="L150"/>
+      <x:c r="M150" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="N150" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="O150" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="P150" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="Q150" s="179" t="str">
+        <x:v>Accessibility information has not been verified. Confirm terrain, steps, seating, toilets and mobility access with an official source before recommending it as elderly-friendly.</x:v>
+      </x:c>
+      <x:c r="R150"/>
+      <x:c r="S150"/>
+      <x:c r="T150" s="179"/>
+      <x:c r="U150" s="179" t="str">
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Putrajaya%20Lake%2C%20W.P.%20Putrajaya%2C%20Malaysia</x:v>
+      </x:c>
+      <x:c r="V150" s="184" t="n">
+        <x:v>46240</x:v>
+      </x:c>
+      <x:c r="W150" s="179" t="str">
+        <x:v>Unverified</x:v>
+      </x:c>
+      <x:c r="X150" s="185" t="n">
+        <x:f>IF(B150="","",COUNTA(B150:W150)/22)</x:f>
+        <x:v>0.7272727272727273</x:v>
+      </x:c>
+      <x:c r="Y150" s="179" t="str">
+        <x:v>Generated by ChatGPT as a candidate on 2026-08-06. The Google Maps link is for discovery only and is not a verified factual source. Replace it with an official or authoritative source during review.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="151">
+      <x:c r="A151" t="str">
+        <x:v>A148</x:v>
+      </x:c>
+      <x:c r="B151" t="str">
+        <x:v>Cruise Tasik Putrajaya</x:v>
+      </x:c>
+      <x:c r="C151" t="str">
+        <x:v>W.P. Putrajaya</x:v>
+      </x:c>
+      <x:c r="D151" s="179" t="str">
+        <x:v>Putrajaya</x:v>
+      </x:c>
+      <x:c r="E151" s="179" t="str">
+        <x:v>Urban Attraction</x:v>
+      </x:c>
+      <x:c r="F151" s="179" t="str">
+        <x:v>lake cruise; sightseeing; relaxation; architecture; family</x:v>
+      </x:c>
+      <x:c r="G151" s="179" t="str">
+        <x:v>Outdoor</x:v>
+      </x:c>
+      <x:c r="H151" s="179" t="str">
+        <x:v>AI-generated candidate attraction in Putrajaya, W.P. Putrajaya. The place name, category, description and visitor details require source verification before production use.</x:v>
+      </x:c>
+      <x:c r="I151" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="J151"/>
+      <x:c r="K151"/>
+      <x:c r="L151"/>
+      <x:c r="M151" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="N151" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="O151" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="P151" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="Q151" s="179" t="str">
+        <x:v>Accessibility information has not been verified. Confirm terrain, steps, seating, toilets and mobility access with an official source before recommending it as elderly-friendly.</x:v>
+      </x:c>
+      <x:c r="R151"/>
+      <x:c r="S151"/>
+      <x:c r="T151" s="179"/>
+      <x:c r="U151" s="179" t="str">
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Cruise%20Tasik%20Putrajaya%2C%20W.P.%20Putrajaya%2C%20Malaysia</x:v>
+      </x:c>
+      <x:c r="V151" s="184" t="n">
+        <x:v>46240</x:v>
+      </x:c>
+      <x:c r="W151" s="179" t="str">
+        <x:v>Unverified</x:v>
+      </x:c>
+      <x:c r="X151" s="185" t="n">
+        <x:f>IF(B151="","",COUNTA(B151:W151)/22)</x:f>
+        <x:v>0.7272727272727273</x:v>
+      </x:c>
+      <x:c r="Y151" s="179" t="str">
+        <x:v>Generated by ChatGPT as a candidate on 2026-08-06. The Google Maps link is for discovery only and is not a verified factual source. Replace it with an official or authoritative source during review.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="152">
+      <x:c r="A152" t="str">
+        <x:v>A149</x:v>
+      </x:c>
+      <x:c r="B152" t="str">
+        <x:v>Moroccan Pavilion Putrajaya</x:v>
+      </x:c>
+      <x:c r="C152" t="str">
+        <x:v>W.P. Putrajaya</x:v>
+      </x:c>
+      <x:c r="D152" s="179" t="str">
+        <x:v>Putrajaya</x:v>
+      </x:c>
+      <x:c r="E152" s="179" t="str">
+        <x:v>Culture</x:v>
+      </x:c>
+      <x:c r="F152" s="179" t="str">
+        <x:v>architecture; culture; photography; garden; indoor</x:v>
+      </x:c>
+      <x:c r="G152" s="179" t="str">
+        <x:v>Both</x:v>
+      </x:c>
+      <x:c r="H152" s="179" t="str">
+        <x:v>AI-generated candidate attraction in Putrajaya, W.P. Putrajaya. The place name, category, description and visitor details require source verification before production use.</x:v>
+      </x:c>
+      <x:c r="I152" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="J152"/>
+      <x:c r="K152"/>
+      <x:c r="L152"/>
+      <x:c r="M152" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="N152" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="O152" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="P152" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="Q152" s="179" t="str">
+        <x:v>Accessibility information has not been verified. Confirm terrain, steps, seating, toilets and mobility access with an official source before recommending it as elderly-friendly.</x:v>
+      </x:c>
+      <x:c r="R152"/>
+      <x:c r="S152"/>
+      <x:c r="T152" s="179"/>
+      <x:c r="U152" s="179" t="str">
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Moroccan%20Pavilion%20Putrajaya%2C%20W.P.%20Putrajaya%2C%20Malaysia</x:v>
+      </x:c>
+      <x:c r="V152" s="184" t="n">
+        <x:v>46240</x:v>
+      </x:c>
+      <x:c r="W152" s="179" t="str">
+        <x:v>Unverified</x:v>
+      </x:c>
+      <x:c r="X152" s="185" t="n">
+        <x:f>IF(B152="","",COUNTA(B152:W152)/22)</x:f>
+        <x:v>0.7272727272727273</x:v>
+      </x:c>
+      <x:c r="Y152" s="179" t="str">
+        <x:v>Generated by ChatGPT as a candidate on 2026-08-06. The Google Maps link is for discovery only and is not a verified factual source. Replace it with an official or authoritative source during review.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="153">
+      <x:c r="A153" t="str">
+        <x:v>A150</x:v>
+      </x:c>
+      <x:c r="B153" t="str">
+        <x:v>Millennium Monument</x:v>
+      </x:c>
+      <x:c r="C153" t="str">
+        <x:v>W.P. Putrajaya</x:v>
+      </x:c>
+      <x:c r="D153" s="179" t="str">
+        <x:v>Putrajaya</x:v>
+      </x:c>
+      <x:c r="E153" s="179" t="str">
+        <x:v>Heritage and History</x:v>
+      </x:c>
+      <x:c r="F153" s="179" t="str">
+        <x:v>monument; history; lakeside; walking; photography</x:v>
+      </x:c>
+      <x:c r="G153" s="179" t="str">
+        <x:v>Outdoor</x:v>
+      </x:c>
+      <x:c r="H153" s="179" t="str">
+        <x:v>AI-generated candidate attraction in Putrajaya, W.P. Putrajaya. The place name, category, description and visitor details require source verification before production use.</x:v>
+      </x:c>
+      <x:c r="I153" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="J153"/>
+      <x:c r="K153"/>
+      <x:c r="L153"/>
+      <x:c r="M153" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="N153" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="O153" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="P153" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="Q153" s="179" t="str">
+        <x:v>Accessibility information has not been verified. Confirm terrain, steps, seating, toilets and mobility access with an official source before recommending it as elderly-friendly.</x:v>
+      </x:c>
+      <x:c r="R153"/>
+      <x:c r="S153"/>
+      <x:c r="T153" s="179"/>
+      <x:c r="U153" s="179" t="str">
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Millennium%20Monument%2C%20W.P.%20Putrajaya%2C%20Malaysia</x:v>
+      </x:c>
+      <x:c r="V153" s="184" t="n">
+        <x:v>46240</x:v>
+      </x:c>
+      <x:c r="W153" s="179" t="str">
+        <x:v>Unverified</x:v>
+      </x:c>
+      <x:c r="X153" s="185" t="n">
+        <x:f>IF(B153="","",COUNTA(B153:W153)/22)</x:f>
+        <x:v>0.7272727272727273</x:v>
+      </x:c>
+      <x:c r="Y153" s="179" t="str">
+        <x:v>Generated by ChatGPT as a candidate on 2026-08-06. The Google Maps link is for discovery only and is not a verified factual source. Replace it with an official or authoritative source during review.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="154">
+      <x:c r="A154" t="str">
+        <x:v>A151</x:v>
+      </x:c>
+      <x:c r="B154" t="str">
+        <x:v>Seri Wawasan Bridge</x:v>
+      </x:c>
+      <x:c r="C154" t="str">
+        <x:v>W.P. Putrajaya</x:v>
+      </x:c>
+      <x:c r="D154" s="179" t="str">
+        <x:v>Putrajaya</x:v>
+      </x:c>
+      <x:c r="E154" s="179" t="str">
+        <x:v>Urban Attraction</x:v>
+      </x:c>
+      <x:c r="F154" s="179" t="str">
+        <x:v>bridge; architecture; night view; photography; sightseeing</x:v>
+      </x:c>
+      <x:c r="G154" s="179" t="str">
+        <x:v>Outdoor</x:v>
+      </x:c>
+      <x:c r="H154" s="179" t="str">
+        <x:v>AI-generated candidate attraction in Putrajaya, W.P. Putrajaya. The place name, category, description and visitor details require source verification before production use.</x:v>
+      </x:c>
+      <x:c r="I154" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="J154"/>
+      <x:c r="K154"/>
+      <x:c r="L154"/>
+      <x:c r="M154" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="N154" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="O154" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="P154" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="Q154" s="179" t="str">
+        <x:v>Accessibility information has not been verified. Confirm terrain, steps, seating, toilets and mobility access with an official source before recommending it as elderly-friendly.</x:v>
+      </x:c>
+      <x:c r="R154"/>
+      <x:c r="S154"/>
+      <x:c r="T154" s="179"/>
+      <x:c r="U154" s="179" t="str">
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Seri%20Wawasan%20Bridge%2C%20W.P.%20Putrajaya%2C%20Malaysia</x:v>
+      </x:c>
+      <x:c r="V154" s="184" t="n">
+        <x:v>46240</x:v>
+      </x:c>
+      <x:c r="W154" s="179" t="str">
+        <x:v>Unverified</x:v>
+      </x:c>
+      <x:c r="X154" s="185" t="n">
+        <x:f>IF(B154="","",COUNTA(B154:W154)/22)</x:f>
+        <x:v>0.7272727272727273</x:v>
+      </x:c>
+      <x:c r="Y154" s="179" t="str">
+        <x:v>Generated by ChatGPT as a candidate on 2026-08-06. The Google Maps link is for discovery only and is not a verified factual source. Replace it with an official or authoritative source during review.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="155">
+      <x:c r="A155" t="str">
+        <x:v>A152</x:v>
+      </x:c>
+      <x:c r="B155" t="str">
+        <x:v>Anjung Floria</x:v>
+      </x:c>
+      <x:c r="C155" t="str">
+        <x:v>W.P. Putrajaya</x:v>
+      </x:c>
+      <x:c r="D155" s="179" t="str">
+        <x:v>Putrajaya</x:v>
+      </x:c>
+      <x:c r="E155" s="179" t="str">
+        <x:v>Park and Recreation</x:v>
+      </x:c>
+      <x:c r="F155" s="179" t="str">
+        <x:v>garden; flowers; walking; relaxation; family</x:v>
+      </x:c>
+      <x:c r="G155" s="179" t="str">
+        <x:v>Outdoor</x:v>
+      </x:c>
+      <x:c r="H155" s="179" t="str">
+        <x:v>AI-generated candidate attraction in Putrajaya, W.P. Putrajaya. The place name, category, description and visitor details require source verification before production use.</x:v>
+      </x:c>
+      <x:c r="I155" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="J155"/>
+      <x:c r="K155"/>
+      <x:c r="L155"/>
+      <x:c r="M155" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="N155" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="O155" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="P155" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="Q155" s="179" t="str">
+        <x:v>Accessibility information has not been verified. Confirm terrain, steps, seating, toilets and mobility access with an official source before recommending it as elderly-friendly.</x:v>
+      </x:c>
+      <x:c r="R155"/>
+      <x:c r="S155"/>
+      <x:c r="T155" s="179"/>
+      <x:c r="U155" s="179" t="str">
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Anjung%20Floria%2C%20W.P.%20Putrajaya%2C%20Malaysia</x:v>
+      </x:c>
+      <x:c r="V155" s="184" t="n">
+        <x:v>46240</x:v>
+      </x:c>
+      <x:c r="W155" s="179" t="str">
+        <x:v>Unverified</x:v>
+      </x:c>
+      <x:c r="X155" s="185" t="n">
+        <x:f>IF(B155="","",COUNTA(B155:W155)/22)</x:f>
+        <x:v>0.7272727272727273</x:v>
+      </x:c>
+      <x:c r="Y155" s="179" t="str">
+        <x:v>Generated by ChatGPT as a candidate on 2026-08-06. The Google Maps link is for discovery only and is not a verified factual source. Replace it with an official or authoritative source during review.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="156">
+      <x:c r="A156" t="str">
+        <x:v>A153</x:v>
+      </x:c>
+      <x:c r="B156" t="str">
+        <x:v>Labuan Marine Museum</x:v>
+      </x:c>
+      <x:c r="C156" t="str">
+        <x:v>W.P. Labuan</x:v>
+      </x:c>
+      <x:c r="D156" s="179" t="str">
+        <x:v>Labuan</x:v>
+      </x:c>
+      <x:c r="E156" s="179" t="str">
+        <x:v>Museum and Gallery</x:v>
+      </x:c>
+      <x:c r="F156" s="179" t="str">
+        <x:v>marine museum; aquarium; education; family; indoor</x:v>
+      </x:c>
+      <x:c r="G156" s="179" t="str">
+        <x:v>Indoor</x:v>
+      </x:c>
+      <x:c r="H156" s="179" t="str">
+        <x:v>AI-generated candidate attraction in Labuan, W.P. Labuan. The place name, category, description and visitor details require source verification before production use.</x:v>
+      </x:c>
+      <x:c r="I156" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="J156"/>
+      <x:c r="K156"/>
+      <x:c r="L156"/>
+      <x:c r="M156" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="N156" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="O156" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="P156" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="Q156" s="179" t="str">
+        <x:v>Accessibility information has not been verified. Confirm terrain, steps, seating, toilets and mobility access with an official source before recommending it as elderly-friendly.</x:v>
+      </x:c>
+      <x:c r="R156"/>
+      <x:c r="S156"/>
+      <x:c r="T156" s="179"/>
+      <x:c r="U156" s="179" t="str">
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Labuan%20Marine%20Museum%2C%20W.P.%20Labuan%2C%20Malaysia</x:v>
+      </x:c>
+      <x:c r="V156" s="184" t="n">
+        <x:v>46240</x:v>
+      </x:c>
+      <x:c r="W156" s="179" t="str">
+        <x:v>Unverified</x:v>
+      </x:c>
+      <x:c r="X156" s="185" t="n">
+        <x:f>IF(B156="","",COUNTA(B156:W156)/22)</x:f>
+        <x:v>0.7272727272727273</x:v>
+      </x:c>
+      <x:c r="Y156" s="179" t="str">
+        <x:v>Generated by ChatGPT as a candidate on 2026-08-06. The Google Maps link is for discovery only and is not a verified factual source. Replace it with an official or authoritative source during review.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="157">
+      <x:c r="A157" t="str">
+        <x:v>A154</x:v>
+      </x:c>
+      <x:c r="B157" t="str">
+        <x:v>Chimney Museum</x:v>
+      </x:c>
+      <x:c r="C157" t="str">
+        <x:v>W.P. Labuan</x:v>
+      </x:c>
+      <x:c r="D157" s="179" t="str">
+        <x:v>Tanjung Kubong</x:v>
+      </x:c>
+      <x:c r="E157" s="179" t="str">
+        <x:v>Museum and Gallery</x:v>
+      </x:c>
+      <x:c r="F157" s="179" t="str">
+        <x:v>museum; coal mining; history; heritage; architecture</x:v>
+      </x:c>
+      <x:c r="G157" s="179" t="str">
+        <x:v>Both</x:v>
+      </x:c>
+      <x:c r="H157" s="179" t="str">
+        <x:v>AI-generated candidate attraction in Tanjung Kubong, W.P. Labuan. The place name, category, description and visitor details require source verification before production use.</x:v>
+      </x:c>
+      <x:c r="I157" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="J157"/>
+      <x:c r="K157"/>
+      <x:c r="L157"/>
+      <x:c r="M157" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="N157" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="O157" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="P157" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="Q157" s="179" t="str">
+        <x:v>Accessibility information has not been verified. Confirm terrain, steps, seating, toilets and mobility access with an official source before recommending it as elderly-friendly.</x:v>
+      </x:c>
+      <x:c r="R157"/>
+      <x:c r="S157"/>
+      <x:c r="T157" s="179"/>
+      <x:c r="U157" s="179" t="str">
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Chimney%20Museum%2C%20W.P.%20Labuan%2C%20Malaysia</x:v>
+      </x:c>
+      <x:c r="V157" s="184" t="n">
+        <x:v>46240</x:v>
+      </x:c>
+      <x:c r="W157" s="179" t="str">
+        <x:v>Unverified</x:v>
+      </x:c>
+      <x:c r="X157" s="185" t="n">
+        <x:f>IF(B157="","",COUNTA(B157:W157)/22)</x:f>
+        <x:v>0.7272727272727273</x:v>
+      </x:c>
+      <x:c r="Y157" s="179" t="str">
+        <x:v>Generated by ChatGPT as a candidate on 2026-08-06. The Google Maps link is for discovery only and is not a verified factual source. Replace it with an official or authoritative source during review.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="158">
+      <x:c r="A158" t="str">
+        <x:v>A155</x:v>
+      </x:c>
+      <x:c r="B158" t="str">
+        <x:v>Labuan Bird Park</x:v>
+      </x:c>
+      <x:c r="C158" t="str">
+        <x:v>W.P. Labuan</x:v>
+      </x:c>
+      <x:c r="D158" s="179" t="str">
+        <x:v>Tanjung Kubong</x:v>
+      </x:c>
+      <x:c r="E158" s="179" t="str">
+        <x:v>Wildlife</x:v>
+      </x:c>
+      <x:c r="F158" s="179" t="str">
+        <x:v>birds; wildlife; family; children; education</x:v>
+      </x:c>
+      <x:c r="G158" s="179" t="str">
+        <x:v>Both</x:v>
+      </x:c>
+      <x:c r="H158" s="179" t="str">
+        <x:v>AI-generated candidate attraction in Tanjung Kubong, W.P. Labuan. The place name, category, description and visitor details require source verification before production use.</x:v>
+      </x:c>
+      <x:c r="I158" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="J158"/>
+      <x:c r="K158"/>
+      <x:c r="L158"/>
+      <x:c r="M158" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="N158" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="O158" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="P158" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="Q158" s="179" t="str">
+        <x:v>Accessibility information has not been verified. Confirm terrain, steps, seating, toilets and mobility access with an official source before recommending it as elderly-friendly.</x:v>
+      </x:c>
+      <x:c r="R158"/>
+      <x:c r="S158"/>
+      <x:c r="T158" s="179"/>
+      <x:c r="U158" s="179" t="str">
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Labuan%20Bird%20Park%2C%20W.P.%20Labuan%2C%20Malaysia</x:v>
+      </x:c>
+      <x:c r="V158" s="184" t="n">
+        <x:v>46240</x:v>
+      </x:c>
+      <x:c r="W158" s="179" t="str">
+        <x:v>Unverified</x:v>
+      </x:c>
+      <x:c r="X158" s="185" t="n">
+        <x:f>IF(B158="","",COUNTA(B158:W158)/22)</x:f>
+        <x:v>0.7272727272727273</x:v>
+      </x:c>
+      <x:c r="Y158" s="179" t="str">
+        <x:v>Generated by ChatGPT as a candidate on 2026-08-06. The Google Maps link is for discovery only and is not a verified factual source. Replace it with an official or authoritative source during review.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="159">
+      <x:c r="A159" t="str">
+        <x:v>A156</x:v>
+      </x:c>
+      <x:c r="B159" t="str">
+        <x:v>Peace Park</x:v>
+      </x:c>
+      <x:c r="C159" t="str">
+        <x:v>W.P. Labuan</x:v>
+      </x:c>
+      <x:c r="D159" s="179" t="str">
+        <x:v>Layang-Layangan</x:v>
+      </x:c>
+      <x:c r="E159" s="179" t="str">
+        <x:v>Park and Recreation</x:v>
+      </x:c>
+      <x:c r="F159" s="179" t="str">
+        <x:v>memorial; garden; walking; history; relaxation</x:v>
+      </x:c>
+      <x:c r="G159" s="179" t="str">
+        <x:v>Outdoor</x:v>
+      </x:c>
+      <x:c r="H159" s="179" t="str">
+        <x:v>AI-generated candidate attraction in Layang-Layangan, W.P. Labuan. The place name, category, description and visitor details require source verification before production use.</x:v>
+      </x:c>
+      <x:c r="I159" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="J159"/>
+      <x:c r="K159"/>
+      <x:c r="L159"/>
+      <x:c r="M159" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="N159" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="O159" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="P159" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="Q159" s="179" t="str">
+        <x:v>Accessibility information has not been verified. Confirm terrain, steps, seating, toilets and mobility access with an official source before recommending it as elderly-friendly.</x:v>
+      </x:c>
+      <x:c r="R159"/>
+      <x:c r="S159"/>
+      <x:c r="T159" s="179"/>
+      <x:c r="U159" s="179" t="str">
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Peace%20Park%2C%20W.P.%20Labuan%2C%20Malaysia</x:v>
+      </x:c>
+      <x:c r="V159" s="184" t="n">
+        <x:v>46240</x:v>
+      </x:c>
+      <x:c r="W159" s="179" t="str">
+        <x:v>Unverified</x:v>
+      </x:c>
+      <x:c r="X159" s="185" t="n">
+        <x:f>IF(B159="","",COUNTA(B159:W159)/22)</x:f>
+        <x:v>0.7272727272727273</x:v>
+      </x:c>
+      <x:c r="Y159" s="179" t="str">
+        <x:v>Generated by ChatGPT as a candidate on 2026-08-06. The Google Maps link is for discovery only and is not a verified factual source. Replace it with an official or authoritative source during review.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="160">
+      <x:c r="A160" t="str">
+        <x:v>A157</x:v>
+      </x:c>
+      <x:c r="B160" t="str">
+        <x:v>Surrender Point</x:v>
+      </x:c>
+      <x:c r="C160" t="str">
+        <x:v>W.P. Labuan</x:v>
+      </x:c>
+      <x:c r="D160" s="179" t="str">
+        <x:v>Layang-Layangan</x:v>
+      </x:c>
+      <x:c r="E160" s="179" t="str">
+        <x:v>Heritage and History</x:v>
+      </x:c>
+      <x:c r="F160" s="179" t="str">
+        <x:v>war history; memorial; heritage; education; outdoor</x:v>
+      </x:c>
+      <x:c r="G160" s="179" t="str">
+        <x:v>Outdoor</x:v>
+      </x:c>
+      <x:c r="H160" s="179" t="str">
+        <x:v>AI-generated candidate attraction in Layang-Layangan, W.P. Labuan. The place name, category, description and visitor details require source verification before production use.</x:v>
+      </x:c>
+      <x:c r="I160" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="J160"/>
+      <x:c r="K160"/>
+      <x:c r="L160"/>
+      <x:c r="M160" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="N160" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="O160" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="P160" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="Q160" s="179" t="str">
+        <x:v>Accessibility information has not been verified. Confirm terrain, steps, seating, toilets and mobility access with an official source before recommending it as elderly-friendly.</x:v>
+      </x:c>
+      <x:c r="R160"/>
+      <x:c r="S160"/>
+      <x:c r="T160" s="179"/>
+      <x:c r="U160" s="179" t="str">
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Surrender%20Point%2C%20W.P.%20Labuan%2C%20Malaysia</x:v>
+      </x:c>
+      <x:c r="V160" s="184" t="n">
+        <x:v>46240</x:v>
+      </x:c>
+      <x:c r="W160" s="179" t="str">
+        <x:v>Unverified</x:v>
+      </x:c>
+      <x:c r="X160" s="185" t="n">
+        <x:f>IF(B160="","",COUNTA(B160:W160)/22)</x:f>
+        <x:v>0.7272727272727273</x:v>
+      </x:c>
+      <x:c r="Y160" s="179" t="str">
+        <x:v>Generated by ChatGPT as a candidate on 2026-08-06. The Google Maps link is for discovery only and is not a verified factual source. Replace it with an official or authoritative source during review.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="161">
+      <x:c r="A161" t="str">
+        <x:v>A158</x:v>
+      </x:c>
+      <x:c r="B161" t="str">
+        <x:v>Labuan International Sea Sports Complex</x:v>
+      </x:c>
+      <x:c r="C161" t="str">
+        <x:v>W.P. Labuan</x:v>
+      </x:c>
+      <x:c r="D161" s="179" t="str">
+        <x:v>Labuan</x:v>
+      </x:c>
+      <x:c r="E161" s="179" t="str">
+        <x:v>Family Attraction</x:v>
+      </x:c>
+      <x:c r="F161" s="179" t="str">
+        <x:v>sea sports; recreation; family; waterfront; events</x:v>
+      </x:c>
+      <x:c r="G161" s="179" t="str">
+        <x:v>Both</x:v>
+      </x:c>
+      <x:c r="H161" s="179" t="str">
+        <x:v>AI-generated candidate attraction in Labuan, W.P. Labuan. The place name, category, description and visitor details require source verification before production use.</x:v>
+      </x:c>
+      <x:c r="I161" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="J161"/>
+      <x:c r="K161"/>
+      <x:c r="L161"/>
+      <x:c r="M161" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="N161" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="O161" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="P161" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="Q161" s="179" t="str">
+        <x:v>Accessibility information has not been verified. Confirm terrain, steps, seating, toilets and mobility access with an official source before recommending it as elderly-friendly.</x:v>
+      </x:c>
+      <x:c r="R161"/>
+      <x:c r="S161"/>
+      <x:c r="T161" s="179"/>
+      <x:c r="U161" s="179" t="str">
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Labuan%20International%20Sea%20Sports%20Complex%2C%20W.P.%20Labuan%2C%20Malaysia</x:v>
+      </x:c>
+      <x:c r="V161" s="184" t="n">
+        <x:v>46240</x:v>
+      </x:c>
+      <x:c r="W161" s="179" t="str">
+        <x:v>Unverified</x:v>
+      </x:c>
+      <x:c r="X161" s="185" t="n">
+        <x:f>IF(B161="","",COUNTA(B161:W161)/22)</x:f>
+        <x:v>0.7272727272727273</x:v>
+      </x:c>
+      <x:c r="Y161" s="179" t="str">
+        <x:v>Generated by ChatGPT as a candidate on 2026-08-06. The Google Maps link is for discovery only and is not a verified factual source. Replace it with an official or authoritative source during review.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="162">
+      <x:c r="A162" t="str">
+        <x:v>A159</x:v>
+      </x:c>
+      <x:c r="B162" t="str">
+        <x:v>Patau-Patau Water Village</x:v>
+      </x:c>
+      <x:c r="C162" t="str">
+        <x:v>W.P. Labuan</x:v>
+      </x:c>
+      <x:c r="D162" s="179" t="str">
+        <x:v>Labuan</x:v>
+      </x:c>
+      <x:c r="E162" s="179" t="str">
+        <x:v>Culture</x:v>
+      </x:c>
+      <x:c r="F162" s="179" t="str">
+        <x:v>water village; local culture; heritage; walking; photography</x:v>
+      </x:c>
+      <x:c r="G162" s="179" t="str">
+        <x:v>Outdoor</x:v>
+      </x:c>
+      <x:c r="H162" s="179" t="str">
+        <x:v>AI-generated candidate attraction in Labuan, W.P. Labuan. The place name, category, description and visitor details require source verification before production use.</x:v>
+      </x:c>
+      <x:c r="I162" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="J162"/>
+      <x:c r="K162"/>
+      <x:c r="L162"/>
+      <x:c r="M162" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="N162" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="O162" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="P162" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="Q162" s="179" t="str">
+        <x:v>Accessibility information has not been verified. Confirm terrain, steps, seating, toilets and mobility access with an official source before recommending it as elderly-friendly.</x:v>
+      </x:c>
+      <x:c r="R162"/>
+      <x:c r="S162"/>
+      <x:c r="T162" s="179"/>
+      <x:c r="U162" s="179" t="str">
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Patau-Patau%20Water%20Village%2C%20W.P.%20Labuan%2C%20Malaysia</x:v>
+      </x:c>
+      <x:c r="V162" s="184" t="n">
+        <x:v>46240</x:v>
+      </x:c>
+      <x:c r="W162" s="179" t="str">
+        <x:v>Unverified</x:v>
+      </x:c>
+      <x:c r="X162" s="185" t="n">
+        <x:f>IF(B162="","",COUNTA(B162:W162)/22)</x:f>
+        <x:v>0.7272727272727273</x:v>
+      </x:c>
+      <x:c r="Y162" s="179" t="str">
+        <x:v>Generated by ChatGPT as a candidate on 2026-08-06. The Google Maps link is for discovery only and is not a verified factual source. Replace it with an official or authoritative source during review.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="163">
+      <x:c r="A163" t="str">
+        <x:v>A160</x:v>
+      </x:c>
+      <x:c r="B163" t="str">
+        <x:v>Rusukan Besar Island</x:v>
+      </x:c>
+      <x:c r="C163" t="str">
+        <x:v>W.P. Labuan</x:v>
+      </x:c>
+      <x:c r="D163" s="179" t="str">
+        <x:v>Labuan</x:v>
+      </x:c>
+      <x:c r="E163" s="179" t="str">
+        <x:v>Beach and Island</x:v>
+      </x:c>
+      <x:c r="F163" s="179" t="str">
+        <x:v>island; beach; snorkelling; marine life; relaxation</x:v>
+      </x:c>
+      <x:c r="G163" s="179" t="str">
+        <x:v>Outdoor</x:v>
+      </x:c>
+      <x:c r="H163" s="179" t="str">
+        <x:v>AI-generated candidate attraction in Labuan, W.P. Labuan. The place name, category, description and visitor details require source verification before production use.</x:v>
+      </x:c>
+      <x:c r="I163" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="J163"/>
+      <x:c r="K163"/>
+      <x:c r="L163"/>
+      <x:c r="M163" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="N163" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="O163" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="P163" s="179" t="str">
+        <x:v>Unknown</x:v>
+      </x:c>
+      <x:c r="Q163" s="179" t="str">
+        <x:v>Accessibility information has not been verified. Confirm terrain, steps, seating, toilets and mobility access with an official source before recommending it as elderly-friendly.</x:v>
+      </x:c>
+      <x:c r="R163"/>
+      <x:c r="S163"/>
+      <x:c r="T163" s="179"/>
+      <x:c r="U163" s="179" t="str">
+        <x:v>https://www.google.com/maps/search/?api=1&amp;query=Rusukan%20Besar%20Island%2C%20W.P.%20Labuan%2C%20Malaysia</x:v>
+      </x:c>
+      <x:c r="V163" s="184" t="n">
+        <x:v>46240</x:v>
+      </x:c>
+      <x:c r="W163" s="179" t="str">
+        <x:v>Unverified</x:v>
+      </x:c>
+      <x:c r="X163" s="185" t="n">
+        <x:f>IF(B163="","",COUNTA(B163:W163)/22)</x:f>
+        <x:v>0.7272727272727273</x:v>
+      </x:c>
+      <x:c r="Y163" s="179" t="str">
+        <x:v>Generated by ChatGPT as a candidate on 2026-08-06. The Google Maps link is for discovery only and is not a verified factual source. Replace it with an official or authoritative source during review.</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:Y1"/>
     <x:mergeCell ref="A2:Y2"/>
   </x:mergeCells>
-  <x:dataValidations count="8">
+  <x:dataValidations count="16">
     <x:dataValidation type="list" sqref="C4:C53">
       <x:formula1>'Lists and Codes'!$A$2:$A$17</x:formula1>
     </x:dataValidation>
@@ -4188,10 +12346,34 @@
     <x:dataValidation type="list" sqref="W4:W53">
       <x:formula1>'Lists and Codes'!$F$2:$F$4</x:formula1>
     </x:dataValidation>
+    <x:dataValidation type="list" sqref="C4:C163">
+      <x:formula1>'Lists and Codes'!$A$2:$A$17</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="list" sqref="E4:E163">
+      <x:formula1>'Lists and Codes'!$B$2:$B$17</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="list" sqref="G4:G163">
+      <x:formula1>'Lists and Codes'!$C$2:$C$5</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="list" sqref="I4:I163">
+      <x:formula1>'Lists and Codes'!$D$2:$D$5</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="list" sqref="N4:N163">
+      <x:formula1>'Lists and Codes'!$E$2:$E$6</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="list" sqref="O4:O163">
+      <x:formula1>'Lists and Codes'!$E$2:$E$6</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="list" sqref="P4:P163">
+      <x:formula1>'Lists and Codes'!$E$2:$E$6</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="list" sqref="W4:W163">
+      <x:formula1>'Lists and Codes'!$F$2:$F$4</x:formula1>
+    </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9a07b63bf985456d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra52b257d21a54d64"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4428,7 +12610,7 @@
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="28" t="str">
-        <x:v>Putrajaya</x:v>
+        <x:v>W.P. Putrajaya</x:v>
       </x:c>
       <x:c r="B16" s="29" t="str">
         <x:v>Other</x:v>
@@ -4440,9 +12622,11 @@
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="31" t="str">
-        <x:v>Labuan</x:v>
-      </x:c>
-      <x:c r="B17" s="32"/>
+        <x:v>W.P. Labuan</x:v>
+      </x:c>
+      <x:c r="B17" s="32" t="str">
+        <x:v>Wellness and Relaxation</x:v>
+      </x:c>
       <x:c r="C17" s="32"/>
       <x:c r="D17" s="32"/>
       <x:c r="E17" s="32"/>
@@ -4909,7 +13093,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ref992822b16c49b4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re4e2e0e6b1e64898"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5428,6 +13612,42 @@
 Anything unavailable: accessibility details and current entrance fee</x:v>
       </x:c>
     </x:row>
+    <x:row r="18">
+      <x:c r="A18" s="187" t="str">
+        <x:v>Dataset Version 2 — AI-assisted candidate expansion</x:v>
+      </x:c>
+      <x:c r="B18" s="187"/>
+      <x:c r="C18" s="187"/>
+      <x:c r="D18" s="187"/>
+      <x:c r="E18" s="187"/>
+      <x:c r="F18" s="187"/>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" s="189" t="str">
+        <x:v>Rows marked Unverified were generated as research candidates. Their discovery links, descriptions, fees and accessibility details must be checked against official or authoritative sources before production use. Unknown values are intentionally preserved rather than inferred.</x:v>
+      </x:c>
+      <x:c r="B19" s="189"/>
+      <x:c r="C19" s="189"/>
+      <x:c r="D19" s="189"/>
+      <x:c r="E19" s="189"/>
+      <x:c r="F19" s="189"/>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" s="189"/>
+      <x:c r="B20" s="189"/>
+      <x:c r="C20" s="189"/>
+      <x:c r="D20" s="189"/>
+      <x:c r="E20" s="189"/>
+      <x:c r="F20" s="189"/>
+    </x:row>
+    <x:row r="21">
+      <x:c r="A21" s="189"/>
+      <x:c r="B21" s="189"/>
+      <x:c r="C21" s="189"/>
+      <x:c r="D21" s="189"/>
+      <x:c r="E21" s="189"/>
+      <x:c r="F21" s="189"/>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:F1"/>
@@ -5438,7 +13658,506 @@
     <x:mergeCell ref="C7:F7"/>
     <x:mergeCell ref="A9:F9"/>
     <x:mergeCell ref="A10:F16"/>
+    <x:mergeCell ref="A18:F18"/>
+    <x:mergeCell ref="A19:F21"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="24" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="13" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="13" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="3" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="27" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="13" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="3" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="22" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="13" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1">
+      <x:c r="A1" s="196" t="str">
+        <x:v>Malaysia Tourism Dataset Version 2 — Coverage Summary</x:v>
+      </x:c>
+      <x:c r="B1" s="196"/>
+      <x:c r="C1" s="196"/>
+      <x:c r="D1" s="196"/>
+      <x:c r="E1" s="196"/>
+      <x:c r="F1" s="196"/>
+      <x:c r="G1" s="196"/>
+      <x:c r="H1" s="196"/>
+      <x:c r="I1" s="196"/>
+      <x:c r="J1" s="196"/>
+    </x:row>
+    <x:row r="2">
+      <x:c r="A2" s="197" t="str">
+        <x:v>160 attraction records: 32 previously collected records plus 128 AI-generated research candidates. Unverified candidates require official-source review.</x:v>
+      </x:c>
+      <x:c r="B2" s="197"/>
+      <x:c r="C2" s="197"/>
+      <x:c r="D2" s="197"/>
+      <x:c r="E2" s="197"/>
+      <x:c r="F2" s="197"/>
+      <x:c r="G2" s="197"/>
+      <x:c r="H2" s="197"/>
+      <x:c r="I2" s="197"/>
+      <x:c r="J2" s="197"/>
+    </x:row>
+    <x:row r="3">
+      <x:c r="A3" s="198"/>
+      <x:c r="B3" s="198"/>
+      <x:c r="C3" s="198"/>
+      <x:c r="D3" s="198"/>
+      <x:c r="E3" s="198"/>
+      <x:c r="F3" s="198"/>
+      <x:c r="G3" s="198"/>
+      <x:c r="H3" s="198"/>
+      <x:c r="I3" s="198"/>
+      <x:c r="J3" s="198"/>
+    </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="199" t="str">
+        <x:v>State / Territory</x:v>
+      </x:c>
+      <x:c r="B4" s="199" t="str">
+        <x:v>Attractions</x:v>
+      </x:c>
+      <x:c r="C4" s="199" t="str">
+        <x:v>Target</x:v>
+      </x:c>
+      <x:c r="D4" s="198"/>
+      <x:c r="E4" s="199" t="str">
+        <x:v>Primary Category</x:v>
+      </x:c>
+      <x:c r="F4" s="199" t="str">
+        <x:v>Attractions</x:v>
+      </x:c>
+      <x:c r="G4" s="198"/>
+      <x:c r="H4" s="199" t="str">
+        <x:v>Verification Status</x:v>
+      </x:c>
+      <x:c r="I4" s="199" t="str">
+        <x:v>Attractions</x:v>
+      </x:c>
+      <x:c r="J4" s="198"/>
+    </x:row>
+    <x:row r="5">
+      <x:c r="A5" s="200" t="str">
+        <x:v>Johor</x:v>
+      </x:c>
+      <x:c r="B5" s="200" t="n">
+        <x:f>COUNTIF('Attractions Entry'!$C$4:$C$163,A5)</x:f>
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="C5" s="200" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="D5" s="198"/>
+      <x:c r="E5" s="200" t="str">
+        <x:v>Nature</x:v>
+      </x:c>
+      <x:c r="F5" s="200" t="n">
+        <x:f>COUNTIF('Attractions Entry'!$E$4:$E$163,E5)</x:f>
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="G5" s="198"/>
+      <x:c r="H5" s="200" t="str">
+        <x:v>Verified</x:v>
+      </x:c>
+      <x:c r="I5" s="200" t="n">
+        <x:f>COUNTIF('Attractions Entry'!$W$4:$W$163,H5)</x:f>
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="J5" s="198"/>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" s="200" t="str">
+        <x:v>Kedah</x:v>
+      </x:c>
+      <x:c r="B6" s="200" t="n">
+        <x:f>COUNTIF('Attractions Entry'!$C$4:$C$163,A6)</x:f>
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="C6" s="200" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="D6" s="198"/>
+      <x:c r="E6" s="200" t="str">
+        <x:v>Beach and Island</x:v>
+      </x:c>
+      <x:c r="F6" s="200" t="n">
+        <x:f>COUNTIF('Attractions Entry'!$E$4:$E$163,E6)</x:f>
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="G6" s="198"/>
+      <x:c r="H6" s="200" t="str">
+        <x:v>Partially verified</x:v>
+      </x:c>
+      <x:c r="I6" s="200" t="n">
+        <x:f>COUNTIF('Attractions Entry'!$W$4:$W$163,H6)</x:f>
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="J6" s="198"/>
+    </x:row>
+    <x:row r="7">
+      <x:c r="A7" s="200" t="str">
+        <x:v>Kelantan</x:v>
+      </x:c>
+      <x:c r="B7" s="200" t="n">
+        <x:f>COUNTIF('Attractions Entry'!$C$4:$C$163,A7)</x:f>
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="C7" s="200" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="D7" s="198"/>
+      <x:c r="E7" s="200" t="str">
+        <x:v>Heritage and History</x:v>
+      </x:c>
+      <x:c r="F7" s="200" t="n">
+        <x:f>COUNTIF('Attractions Entry'!$E$4:$E$163,E7)</x:f>
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="G7" s="198"/>
+      <x:c r="H7" s="200" t="str">
+        <x:v>Unverified</x:v>
+      </x:c>
+      <x:c r="I7" s="200" t="n">
+        <x:f>COUNTIF('Attractions Entry'!$W$4:$W$163,H7)</x:f>
+        <x:v>128</x:v>
+      </x:c>
+      <x:c r="J7" s="198"/>
+    </x:row>
+    <x:row r="8">
+      <x:c r="A8" s="200" t="str">
+        <x:v>Melaka</x:v>
+      </x:c>
+      <x:c r="B8" s="200" t="n">
+        <x:f>COUNTIF('Attractions Entry'!$C$4:$C$163,A8)</x:f>
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="C8" s="200" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="D8" s="198"/>
+      <x:c r="E8" s="200" t="str">
+        <x:v>Culture</x:v>
+      </x:c>
+      <x:c r="F8" s="200" t="n">
+        <x:f>COUNTIF('Attractions Entry'!$E$4:$E$163,E8)</x:f>
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="G8" s="198"/>
+      <x:c r="H8" s="200"/>
+      <x:c r="I8" s="200"/>
+      <x:c r="J8" s="198"/>
+    </x:row>
+    <x:row r="9">
+      <x:c r="A9" s="200" t="str">
+        <x:v>Negeri Sembilan</x:v>
+      </x:c>
+      <x:c r="B9" s="200" t="n">
+        <x:f>COUNTIF('Attractions Entry'!$C$4:$C$163,A9)</x:f>
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="C9" s="200" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="D9" s="198"/>
+      <x:c r="E9" s="200" t="str">
+        <x:v>Food</x:v>
+      </x:c>
+      <x:c r="F9" s="200" t="n">
+        <x:f>COUNTIF('Attractions Entry'!$E$4:$E$163,E9)</x:f>
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G9" s="198"/>
+      <x:c r="H9" s="200" t="str">
+        <x:v>Total records</x:v>
+      </x:c>
+      <x:c r="I9" s="200" t="n">
+        <x:v>160</x:v>
+      </x:c>
+      <x:c r="J9" s="198"/>
+    </x:row>
+    <x:row r="10">
+      <x:c r="A10" s="200" t="str">
+        <x:v>Pahang</x:v>
+      </x:c>
+      <x:c r="B10" s="200" t="n">
+        <x:f>COUNTIF('Attractions Entry'!$C$4:$C$163,A10)</x:f>
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="C10" s="200" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="D10" s="198"/>
+      <x:c r="E10" s="200" t="str">
+        <x:v>Adventure</x:v>
+      </x:c>
+      <x:c r="F10" s="200" t="n">
+        <x:f>COUNTIF('Attractions Entry'!$E$4:$E$163,E10)</x:f>
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="G10" s="198"/>
+      <x:c r="H10" s="200" t="str">
+        <x:v>Existing records</x:v>
+      </x:c>
+      <x:c r="I10" s="200" t="n">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="J10" s="198"/>
+    </x:row>
+    <x:row r="11">
+      <x:c r="A11" s="200" t="str">
+        <x:v>Penang</x:v>
+      </x:c>
+      <x:c r="B11" s="200" t="n">
+        <x:f>COUNTIF('Attractions Entry'!$C$4:$C$163,A11)</x:f>
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="C11" s="200" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="D11" s="198"/>
+      <x:c r="E11" s="200" t="str">
+        <x:v>Family Attraction</x:v>
+      </x:c>
+      <x:c r="F11" s="200" t="n">
+        <x:f>COUNTIF('Attractions Entry'!$E$4:$E$163,E11)</x:f>
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="G11" s="198"/>
+      <x:c r="H11" s="200" t="str">
+        <x:v>AI candidates</x:v>
+      </x:c>
+      <x:c r="I11" s="200" t="n">
+        <x:v>128</x:v>
+      </x:c>
+      <x:c r="J11" s="198"/>
+    </x:row>
+    <x:row r="12">
+      <x:c r="A12" s="200" t="str">
+        <x:v>Perak</x:v>
+      </x:c>
+      <x:c r="B12" s="200" t="n">
+        <x:f>COUNTIF('Attractions Entry'!$C$4:$C$163,A12)</x:f>
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="C12" s="200" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="D12" s="198"/>
+      <x:c r="E12" s="200" t="str">
+        <x:v>Theme Park</x:v>
+      </x:c>
+      <x:c r="F12" s="200" t="n">
+        <x:f>COUNTIF('Attractions Entry'!$E$4:$E$163,E12)</x:f>
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="G12" s="198"/>
+      <x:c r="H12" s="198"/>
+      <x:c r="I12" s="198"/>
+      <x:c r="J12" s="198"/>
+    </x:row>
+    <x:row r="13">
+      <x:c r="A13" s="200" t="str">
+        <x:v>Perlis</x:v>
+      </x:c>
+      <x:c r="B13" s="200" t="n">
+        <x:f>COUNTIF('Attractions Entry'!$C$4:$C$163,A13)</x:f>
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="C13" s="200" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="D13" s="198"/>
+      <x:c r="E13" s="200" t="str">
+        <x:v>Wildlife</x:v>
+      </x:c>
+      <x:c r="F13" s="200" t="n">
+        <x:f>COUNTIF('Attractions Entry'!$E$4:$E$163,E13)</x:f>
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="G13" s="198"/>
+      <x:c r="H13" s="198"/>
+      <x:c r="I13" s="198"/>
+      <x:c r="J13" s="198"/>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="200" t="str">
+        <x:v>Sabah</x:v>
+      </x:c>
+      <x:c r="B14" s="200" t="n">
+        <x:f>COUNTIF('Attractions Entry'!$C$4:$C$163,A14)</x:f>
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="C14" s="200" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="D14" s="198"/>
+      <x:c r="E14" s="200" t="str">
+        <x:v>Religious Site</x:v>
+      </x:c>
+      <x:c r="F14" s="200" t="n">
+        <x:f>COUNTIF('Attractions Entry'!$E$4:$E$163,E14)</x:f>
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="G14" s="198"/>
+      <x:c r="H14" s="198"/>
+      <x:c r="I14" s="198"/>
+      <x:c r="J14" s="198"/>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" s="200" t="str">
+        <x:v>Sarawak</x:v>
+      </x:c>
+      <x:c r="B15" s="200" t="n">
+        <x:f>COUNTIF('Attractions Entry'!$C$4:$C$163,A15)</x:f>
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="C15" s="200" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="D15" s="198"/>
+      <x:c r="E15" s="200" t="str">
+        <x:v>Shopping</x:v>
+      </x:c>
+      <x:c r="F15" s="200" t="n">
+        <x:f>COUNTIF('Attractions Entry'!$E$4:$E$163,E15)</x:f>
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="G15" s="198"/>
+      <x:c r="H15" s="198"/>
+      <x:c r="I15" s="198"/>
+      <x:c r="J15" s="198"/>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" s="200" t="str">
+        <x:v>Selangor</x:v>
+      </x:c>
+      <x:c r="B16" s="200" t="n">
+        <x:f>COUNTIF('Attractions Entry'!$C$4:$C$163,A16)</x:f>
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="C16" s="200" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="D16" s="198"/>
+      <x:c r="E16" s="200" t="str">
+        <x:v>Urban Attraction</x:v>
+      </x:c>
+      <x:c r="F16" s="200" t="n">
+        <x:f>COUNTIF('Attractions Entry'!$E$4:$E$163,E16)</x:f>
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="G16" s="198"/>
+      <x:c r="H16" s="198"/>
+      <x:c r="I16" s="198"/>
+      <x:c r="J16" s="198"/>
+    </x:row>
+    <x:row r="17">
+      <x:c r="A17" s="200" t="str">
+        <x:v>Terengganu</x:v>
+      </x:c>
+      <x:c r="B17" s="200" t="n">
+        <x:f>COUNTIF('Attractions Entry'!$C$4:$C$163,A17)</x:f>
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="C17" s="200" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="D17" s="198"/>
+      <x:c r="E17" s="200" t="str">
+        <x:v>Museum and Gallery</x:v>
+      </x:c>
+      <x:c r="F17" s="200" t="n">
+        <x:f>COUNTIF('Attractions Entry'!$E$4:$E$163,E17)</x:f>
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="G17" s="198"/>
+      <x:c r="H17" s="198"/>
+      <x:c r="I17" s="198"/>
+      <x:c r="J17" s="198"/>
+    </x:row>
+    <x:row r="18">
+      <x:c r="A18" s="200" t="str">
+        <x:v>Kuala Lumpur</x:v>
+      </x:c>
+      <x:c r="B18" s="200" t="n">
+        <x:f>COUNTIF('Attractions Entry'!$C$4:$C$163,A18)</x:f>
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="C18" s="200" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="D18" s="198"/>
+      <x:c r="E18" s="200" t="str">
+        <x:v>Park and Recreation</x:v>
+      </x:c>
+      <x:c r="F18" s="200" t="n">
+        <x:f>COUNTIF('Attractions Entry'!$E$4:$E$163,E18)</x:f>
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="G18" s="198"/>
+      <x:c r="H18" s="198"/>
+      <x:c r="I18" s="198"/>
+      <x:c r="J18" s="198"/>
+    </x:row>
+    <x:row r="19">
+      <x:c r="A19" s="200" t="str">
+        <x:v>W.P. Putrajaya</x:v>
+      </x:c>
+      <x:c r="B19" s="200" t="n">
+        <x:f>COUNTIF('Attractions Entry'!$C$4:$C$163,A19)</x:f>
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="C19" s="200" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="D19" s="198"/>
+      <x:c r="E19" s="200" t="str">
+        <x:v>Wellness and Relaxation</x:v>
+      </x:c>
+      <x:c r="F19" s="200" t="n">
+        <x:f>COUNTIF('Attractions Entry'!$E$4:$E$163,E19)</x:f>
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="G19" s="198"/>
+      <x:c r="H19" s="198"/>
+      <x:c r="I19" s="198"/>
+      <x:c r="J19" s="198"/>
+    </x:row>
+    <x:row r="20">
+      <x:c r="A20" s="200" t="str">
+        <x:v>W.P. Labuan</x:v>
+      </x:c>
+      <x:c r="B20" s="200" t="n">
+        <x:f>COUNTIF('Attractions Entry'!$C$4:$C$163,A20)</x:f>
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="C20" s="200" t="n">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="D20" s="198"/>
+      <x:c r="E20" s="198"/>
+      <x:c r="F20" s="198"/>
+      <x:c r="G20" s="198"/>
+      <x:c r="H20" s="198"/>
+      <x:c r="I20" s="198"/>
+      <x:c r="J20" s="198"/>
+    </x:row>
+  </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="A1:J1"/>
+    <x:mergeCell ref="A2:J2"/>
+  </x:mergeCells>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R22ae4108c7834b1f"/>
+</x:worksheet>
 </file>